--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2C座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4525,7 +4381,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -13419,7 +13275,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -20715,7 +20571,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -29011,7 +28867,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -30023,7 +29879,7 @@
       </c>
       <c r="G638" s="3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H638" s="5" t="n">
@@ -47667,9274 +47523,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>启德海湾 1 - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>390 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>335 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,172万
-$23,526/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,598万
-$29,925/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$1,519万
-$34,764/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$948万
-$30,984/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$951万
-$31,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$974万
-$31,951/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$962万
-$31,227/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,143万
-$26,574/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$970万
-$20,166/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="N6" s="18" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$954万
-$33,111/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,587万
-$31,869/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,593万
-$29,837/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$1,471万
-$33,666/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$1,129万
-$26,433/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$923万
-$30,167/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$926万
-$30,357/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$929万
-$30,456/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$936万
-$30,406/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$1,107万
-$23,010/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$998万
-$34,667/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$2,144万
-$27,698/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,233万
-$23,000/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,452万
-$29,151/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,584万
-$29,665/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$1,122万
-$26,269/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$907万
-$29,631/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$910万
-$29,833/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$913万
-$29,944/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$920万
-$29,886/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$1,059万
-$22,012/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="N8" s="18" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$899万
-$31,212/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$2,715万
-$35,218/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,150万
-$21,455/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,489万
-$29,894/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,271万
-$23,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$856万
-$20,059/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$956万
-$31,232/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$635万
-$20,813/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$972万
-$31,859/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 309呎 (1房)
-$653万
-$21,126/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$809万
-$18,814/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$1,010万
-$20,998/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$994万
-$34,503/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$2,007万
-$25,928/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,138万
-$21,231/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,423万
-$28,572/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,188万
-$22,238/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$958万
-$21,918/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$846万
-$19,822/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$676万
-$22,092/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$632万
-$20,647/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$962万
-$31,554/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$646万
-$20,958/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$891万
-$20,726/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$1,008万
-$20,967/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$988万
-$34,295/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,126万
-$21,000/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,419万
-$28,488/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,239万
-$23,199/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$999万
-$22,856/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$851万
-$19,925/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$670万
-$21,889/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$1,163万
-$38,144/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 306呎 (1房)
-$696万
-$22,732/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 309呎 (1房)
-$615万
-$19,916/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$860万
-$20,000/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$990万
-$20,582/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$672万
-$23,579/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,889万
-$24,403/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,099万
-$20,500/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,415万
-$28,406/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,162万
-$21,753/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$909万
-$20,798/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$836万
-$19,590/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$664万
-$21,693/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$627万
-$20,484/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 306呎 (1房)
-$689万
-$22,516/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 309呎 (1房)
-$613万
-$19,848/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$890万
-$20,695/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$1,007万
-$20,933/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$679万
-$23,569/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,748万
-$22,672/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,085万
-$20,235/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,078万
-$20,185/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$864万
-$19,767/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$839万
-$19,644/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$658万
-$21,487/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$620万
-$20,261/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$550万
-$18,030/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$608万
-$19,756/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$792万
-$18,409/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$998万
-$20,753/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$672万
-$23,579/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,760万
-$22,827/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,080万
-$20,142/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,451万
-$29,145/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,087万
-$20,358/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$857万
-$19,616/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$789万
-$18,485/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$651万
-$21,275/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$596万
-$19,471/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$546万
-$17,892/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$605万
-$19,653/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$876万
-$20,377/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$994万
-$20,674/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$631万
-$22,133/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,807万
-$23,344/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,060万
-$19,778/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,387万
-$27,851/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,114万
-$20,861/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$857万
-$19,606/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$778万
-$18,220/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$542万
-$17,703/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$592万
-$19,350/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$539万
-$17,685/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$602万
-$19,549/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$875万
-$20,344/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$992万
-$20,626/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$553万
-$19,215/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,755万
-$22,679/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,060万
-$19,767/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,383万
-$27,775/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,054万
-$19,745/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$849万
-$19,437/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$786万
-$18,412/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$540万
-$17,663/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$589万
-$19,302/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$540万
-$17,695/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 309呎 (1房)
-$599万
-$19,382/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$873万
-$20,312/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$991万
-$20,595/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$552万
-$19,153/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,967万
-$25,411/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,068万
-$19,925/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,096万
-$20,530/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$922万
-$21,094/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$777万
-$18,187/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$537万
-$17,562/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$585万
-$19,184/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$538万
-$17,639/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$595万
-$19,318/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$777万
-$18,063/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$989万
-$20,557/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$598万
-$20,989/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,774万
-$22,917/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,062万
-$19,817/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,100万
-$22,092/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,034万
-$19,354/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$927万
-$21,215/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$769万
-$18,009/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$536万
-$17,529/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$584万
-$19,134/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$536万
-$17,584/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 309呎 (1房)
-$592万
-$19,162/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$871万
-$20,253/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$978万
-$20,333/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$594万
-$20,853/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,718万
-$22,283/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,047万
-$19,530/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,371万
-$27,532/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,038万
-$19,436/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$838万
-$19,183/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$773万
-$18,103/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$637万
-$20,807/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$581万
-$19,036/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$537万
-$17,597/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$546万
-$17,724/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$869万
-$20,216/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$986万
-$20,491/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$549万
-$19,249/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,851万
-$23,912/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,050万
-$19,590/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,367万
-$27,456/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,027万
-$19,238/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$915万
-$20,934/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$855万
-$20,014/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$530万
-$17,324/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$580万
-$19,003/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$532万
-$17,459/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$590万
-$19,159/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$781万
-$18,172/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$984万
-$20,457/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$549万
-$19,059/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,888万
-$24,393/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,063万
-$19,826/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$1,027万
-$19,238/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$875万
-$20,018/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$855万
-$20,014/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$530万
-$17,324/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$536万
-$17,561/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$534万
-$17,505/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$541万
-$17,562/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$779万
-$18,109/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$984万
-$20,457/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$589万
-$20,441/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,650万
-$21,401/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,025万
-$19,123/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,143万
-$22,994/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$983万
-$18,416/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$829万
-$18,966/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$847万
-$19,845/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$506万
-$16,539/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$504万
-$16,511/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$528万
-$17,321/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$520万
-$16,873/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$859万
-$19,984/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$977万
-$20,316/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$485万
-$16,847/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,660万
-$21,530/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,007万
-$18,795/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$1,079万
-$21,663/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$978万
-$18,324/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$818万
-$18,709/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$846万
-$19,806/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$627万
-$20,497/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$501万
-$16,430/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$525万
-$17,203/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$517万
-$16,779/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$857万
-$19,928/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$973万
-$20,237/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$483万
-$16,785/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,683万
-$21,829/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,021万
-$19,050/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,081万
-$21,746/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$976万
-$18,270/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$818万
-$18,725/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$844万
-$19,770/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$503万
-$16,428/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$504万
-$16,531/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$525万
-$17,223/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$516万
-$16,747/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$855万
-$19,888/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$971万
-$20,191/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$492万
-$17,066/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,626万
-$21,089/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$997万
-$18,601/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$980万
-$18,350/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$806万
-$18,449/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$842万
-$19,721/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$502万
-$16,399/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$499万
-$16,367/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$522万
-$17,108/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$515万
-$16,708/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$853万
-$19,847/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$969万
-$20,150/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N25" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$490万
-$17,017/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,759万
-$22,724/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,001万
-$18,679/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,071万
-$21,545/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$970万
-$18,161/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$799万
-$18,293/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$840万
-$19,660/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$501万
-$16,366/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$498万
-$16,331/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 306呎 (1房)
-$524万
-$17,131/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$514万
-$16,675/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$852万
-$19,805/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$967万
-$20,108/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$479万
-$16,628/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,650万
-$21,401/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$991万
-$18,494/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$996万
-$20,000/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$967万
-$18,110/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$800万
-$18,311/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$837万
-$19,597/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$500万
-$16,330/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$497万
-$16,298/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$519万
-$17,010/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$641万
-$20,805/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$850万
-$19,767/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$965万
-$20,067/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$477万
-$16,576/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,697万
-$21,922/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,002万
-$18,700/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$997万
-$20,016/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$964万
-$18,058/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$796万
-$18,217/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$835万
-$19,560/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$499万
-$16,310/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$500万
-$16,393/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$519万
-$17,026/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$512万
-$16,607/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$861万
-$20,065/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$963万
-$20,025/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="N28" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$476万
-$16,702/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,666万
-$21,606/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$988万
-$18,437/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,001万
-$20,137/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$964万
-$18,058/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$819万
-$18,746/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$835万
-$19,560/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$621万
-$20,307/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$500万
-$16,393/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 306呎 (1房)
-$592万
-$19,337/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$512万
-$16,607/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$848万
-$19,721/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$963万
-$20,025/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$486万
-$16,865/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,681万
-$21,800/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$993万
-$18,522/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$981万
-$19,701/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$954万
-$17,875/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$797万
-$18,231/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$829万
-$19,412/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$496万
-$16,199/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$493万
-$16,161/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$514万
-$16,846/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$508万
-$16,484/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$844万
-$19,619/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$868万
-$18,037/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$472万
-$16,392/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,661万
-$21,460/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$980万
-$18,282/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 498呎 (2房)
-$976万
-$19,606/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$948万
-$17,760/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$792万
-$18,114/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$790万
-$18,501/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$494万
-$16,134/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$491万
-$16,089/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$516万
-$16,925/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$506万
-$16,425/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$842万
-$19,572/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$956万
-$19,865/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$471万
-$16,365/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,608万
-$20,856/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$992万
-$18,498/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$999万
-$20,097/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$954万
-$17,873/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$797万
-$18,243/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$726万
-$16,998/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$498万
-$16,258/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$493万
-$16,167/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$520万
-$17,049/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$505万
-$16,390/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="L32" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$746万
-$17,351/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$846万
-$17,593/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="N32" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$479万
-$16,628/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,660万
-$21,444/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$978万
-$18,241/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$974万
-$19,594/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$939万
-$17,590/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$787万
-$18,011/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$822万
-$19,251/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$490万
-$16,007/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$488万
-$16,003/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$509万
-$16,682/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$502万
-$16,299/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$839万
-$19,507/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$836万
-$17,380/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="N33" s="17" t="inlineStr">
-        <is>
-          <t>N | 285呎 (1房)
-$467万
-$16,400/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,681万
-$21,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$983万
-$18,343/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$985万
-$19,815/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$983万
-$18,404/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$788万
-$18,043/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$714万
-$16,733/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$488万
-$15,941/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$523万
-$17,148/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$510万
-$16,738/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$499万
-$16,205/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="L34" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$837万
-$19,458/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$835万
-$17,356/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="N34" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$465万
-$16,153/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,681万
-$21,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$978万
-$18,239/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$978万
-$19,674/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 534呎 (2房)
-$994万
-$18,609/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (2房)
-$787万
-$18,014/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 427呎 (2房)
-$711万
-$16,656/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$487万
-$15,928/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$520万
-$17,059/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>J | 305呎 (1房)
-$534万
-$17,492/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="K35" s="17" t="inlineStr">
-        <is>
-          <t>K | 308呎 (1房)
-$503万
-$16,328/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="L35" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$729万
-$16,949/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>M | 481呎 (2房)
-$831万
-$17,285/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="N35" s="17" t="inlineStr">
-        <is>
-          <t>N | 288呎 (1房)
-$461万
-$15,997/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>启德海湾 1 - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>268 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>232 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$1,613万
-$34,030/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$1,322万
-$29,369/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,289万
-$27,019/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,289万
-$23,315/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$825万
-$26,883/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$1,132万
-$26,201/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$1,124万
-$26,074/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,429万
-$24,389/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$1,542万
-$32,532/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$1,318万
-$29,284/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,600万
-$33,549/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$823万
-$26,808/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$1,128万
-$26,120/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$1,120万
-$25,998/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 537呎 (2房)
-$1,454万
-$27,073/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,465万
-$25,000/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,559万
-$32,681/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,278万
-$23,105/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$818万
-$26,638/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,250万
-$23,234/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,432万
-$24,437/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$1,064万
-$22,443/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$999万
-$22,196/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,396万
-$29,264/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,208万
-$21,852/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$956万
-$31,140/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$823万
-$19,051/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$812万
-$18,789/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,148万
-$21,338/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,407万
-$24,007/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$993万
-$20,947/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$993万
-$22,062/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,392万
-$29,178/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,229万
-$22,221/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$634万
-$20,645/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$788万
-$18,243/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$807万
-$18,688/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,130万
-$21,000/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,408万
-$24,027/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$988万
-$20,842/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$1,889万
-$41,973/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,388万
-$29,094/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,201万
-$21,723/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$631万
-$20,547/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$811万
-$18,778/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$806万
-$18,653/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,128万
-$20,967/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,348万
-$23,003/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$960万
-$20,245/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$987万
-$21,929/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,384万
-$29,008/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,244万
-$22,503/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$626万
-$20,375/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$770万
-$17,824/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$803万
-$18,590/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,087万
-$20,201/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,298万
-$22,150/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$955万
-$20,141/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$977万
-$21,707/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,368万
-$28,690/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,234万
-$22,311/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$646万
-$21,026/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$760万
-$17,583/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$757万
-$17,568/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 537呎 (2房)
-$1,060万
-$19,739/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,293万
-$22,070/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$978万
-$20,627/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$917万
-$20,373/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,362万
-$28,547/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,221万
-$22,083/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$618万
-$20,124/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$778万
-$18,007/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$759万
-$17,615/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,052万
-$19,548/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,293万
-$22,058/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$938万
-$19,781/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$914万
-$20,318/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,175万
-$21,248/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$602万
-$19,603/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$755万
-$17,468/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$760万
-$17,643/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,067万
-$19,840/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,299万
-$22,162/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$956万
-$20,169/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$912万
-$20,256/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,054万
-$22,092/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,176万
-$21,266/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$588万
-$19,150/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$753万
-$17,431/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$786万
-$18,230/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,049万
-$19,498/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,276万
-$21,776/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$952万
-$20,093/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$909万
-$20,200/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,048万
-$21,966/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,210万
-$21,888/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$585万
-$19,046/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$752万
-$17,396/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$749万
-$17,387/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,061万
-$19,723/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,508万
-$25,741/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$926万
-$19,540/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$906万
-$20,144/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,337万
-$28,031/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,207万
-$21,823/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$605万
-$19,710/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$750万
-$17,361/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$785万
-$18,216/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,036万
-$19,247/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,279万
-$21,821/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$927万
-$19,553/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$904万
-$20,087/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,333万
-$27,945/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,203万
-$21,758/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$602万
-$19,612/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$746万
-$17,269/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$781万
-$18,076/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,055万
-$19,602/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,280万
-$21,838/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$914万
-$19,287/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$901万
-$20,027/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,329万
-$27,862/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,151万
-$20,812/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$599万
-$19,508/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$747万
-$17,292/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$750万
-$17,408/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,026万
-$19,061/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,290万
-$22,014/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$918万
-$19,357/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$898万
-$19,958/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,162万
-$21,016/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$597万
-$19,446/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$739万
-$17,106/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$777万
-$17,981/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$1,026万
-$19,061/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,359万
-$23,188/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$880万
-$18,557/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$862万
-$19,164/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,019万
-$21,358/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,187万
-$21,463/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$512万
-$16,681/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$707万
-$16,370/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$730万
-$16,926/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$982万
-$18,249/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,478万
-$25,217/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$875万
-$18,466/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$974万
-$21,651/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$961万
-$20,143/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,181万
-$21,353/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$616万
-$20,072/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$706万
-$16,338/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$728万
-$16,891/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$976万
-$18,147/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,216万
-$20,746/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$879万
-$18,553/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$884万
-$19,633/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,295万
-$27,153/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,177万
-$21,289/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$503万
-$16,397/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$704万
-$16,306/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$839万
-$19,462/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$973万
-$18,093/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,222万
-$20,846/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$870万
-$18,361/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$848万
-$18,833/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,174万
-$21,226/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$502万
-$16,365/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$703万
-$16,269/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$714万
-$16,528/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$989万
-$18,375/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,200万
-$20,478/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$964万
-$20,333/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$878万
-$19,520/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$999万
-$20,939/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,170万
-$21,161/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$612万
-$19,948/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$701万
-$16,234/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$719万
-$16,691/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$986万
-$18,320/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,206万
-$20,577/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$872万
-$18,392/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$860万
-$19,111/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$937万
-$19,639/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,167万
-$21,098/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$500万
-$16,303/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$700万
-$16,201/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$709万
-$16,441/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$965万
-$17,929/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,193万
-$20,363/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$879万
-$18,546/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$960万
-$21,340/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$931万
-$19,514/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,134万
-$20,510/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$499万
-$16,267/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$698万
-$16,167/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$710万
-$16,471/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$962万
-$17,875/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,227万
-$20,935/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$863万
-$18,205/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$867万
-$19,273/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$984万
-$20,625/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,134万
-$20,510/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$499万
-$16,267/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$790万
-$18,287/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$707万
-$16,411/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 537呎 (2房)
-$962万
-$17,909/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,265万
-$21,587/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$894万
-$18,861/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$865万
-$19,227/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,150万
-$20,803/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$496万
-$16,150/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$695万
-$16,095/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$701万
-$16,222/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$949万
-$17,643/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,188万
-$20,275/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$851万
-$17,956/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$828万
-$18,407/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$992万
-$20,801/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,144万
-$20,685/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$579万
-$18,853/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$693万
-$16,042/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$699万
-$16,225/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$945万
-$17,572/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,179万
-$20,123/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$866万
-$18,264/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$824万
-$18,316/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$914万
-$19,157/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,085万
-$19,617/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$498万
-$16,225/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$700万
-$16,199/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$700万
-$16,248/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$949万
-$17,647/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,173万
-$20,014/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$843万
-$17,778/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$938万
-$20,833/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$907万
-$19,010/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,051万
-$19,013/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$491万
-$16,003/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$721万
-$16,694/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 431呎 (2房)
-$689万
-$15,986/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$930万
-$17,279/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 586呎 (3房)
-$1,172万
-$20,000/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 474呎 (2房)
-$863万
-$18,211/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$848万
-$18,836/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$947万
-$19,849/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,038万
-$18,772/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$490万
-$15,958/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$688万
-$15,928/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 432呎 (2房)
-$754万
-$17,461/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
-        <is>
-          <t>J | 538呎 (2房)
-$969万
-$18,011/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$856万
-$18,334/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-$836万
-$18,584/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$938万
-$19,660/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1,027万
-$18,579/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$489万
-$15,928/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 432呎 (2房)
-$688万
-$15,928/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-$803万
-$20,585/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="J35" s="20" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>启德海湾 1 - 2C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>359 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>37 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>36 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>277 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 483呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$1,070万
-$34,866/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-$1,257万
-$40,032/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$1,349万
-$30,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$952万
-$31,101/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$953万
-$31,246/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$961万
-$31,201/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$970万
-$31,816/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,377万
-$32,023/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M6" s="18" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$957万
-$31,173/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 483呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$1,052万
-$34,257/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-$1,053万
-$33,535/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$1,320万
-$30,062/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$932万
-$30,448/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$929万
-$30,459/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$941万
-$30,539/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$950万
-$31,161/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,350万
-$31,405/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="18" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$936万
-$30,479/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 483呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$1,044万
-$33,997/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-$1,026万
-$32,688/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$958万
-$31,320/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$966万
-$31,685/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$985万
-$31,981/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$989万
-$32,426/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$982万
-$32,000/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,321万
-$26,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,254万
-$26,008/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$978万
-$31,860/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$984万
-$31,225/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$1,173万
-$26,720/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$678万
-$22,144/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$866万
-$28,387/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$875万
-$28,419/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$936万
-$30,679/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,257万
-$29,233/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$637万
-$20,743/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,193万
-$23,480/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,161万
-$24,083/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,350万
-$24,501/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$1,025万
-$33,375/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$1,046万
-$33,206/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$672万
-$21,948/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$923万
-$30,249/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$933万
-$30,279/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$925万
-$30,315/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$631万
-$20,547/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,257万
-$24,748/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$956万
-$31,156/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$960万
-$30,492/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$1,126万
-$25,640/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$666万
-$21,752/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$850万
-$27,856/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$858万
-$27,847/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$915万
-$30,013/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,232万
-$28,644/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$625万
-$20,352/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,187万
-$23,362/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,150万
-$23,855/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$994万
-$32,378/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$1,015万
-$32,232/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$901万
-$20,519/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$639万
-$20,876/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$905万
-$29,575/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$914万
-$29,679/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$908万
-$29,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$596万
-$19,397/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,167万
-$22,969/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,114万
-$23,108/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$935万
-$30,453/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$940万
-$29,848/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$892万
-$20,314/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$633万
-$20,680/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$832万
-$27,279/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$841万
-$27,318/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$897万
-$29,410/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$1,205万
-$28,023/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$589万
-$19,179/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,119万
-$22,024/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,089万
-$22,589/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$716万
-$23,329/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$986万
-$31,289/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$849万
-$19,335/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$627万
-$20,484/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$646万
-$21,098/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$896万
-$29,081/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$647万
-$21,137/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$936万
-$21,807/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$582万
-$18,971/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,107万
-$21,787/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,077万
-$22,340/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$701万
-$22,827/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$704万
-$22,343/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$844万
-$19,221/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$560万
-$18,301/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$568万
-$18,562/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$824万
-$26,747/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$639万
-$20,876/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$925万
-$21,507/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$565万
-$18,401/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,091万
-$21,472/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,061万
-$22,008/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,262万
-$22,900/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$692万
-$22,534/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$672万
-$21,340/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$831万
-$18,925/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$559万
-$18,258/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$567万
-$18,520/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$588万
-$19,091/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$629万
-$20,616/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$909万
-$21,135/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$559万
-$18,202/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,080万
-$21,256/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,051万
-$21,801/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,213万
-$22,011/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$687万
-$22,371/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$690万
-$21,898/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$827万
-$18,834/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$557万
-$18,203/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$566万
-$18,480/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$607万
-$19,701/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$602万
-$19,690/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$882万
-$20,555/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$553万
-$18,000/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,109万
-$21,827/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,041万
-$21,593/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$655万
-$21,336/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$683万
-$21,676/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$823万
-$18,743/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$556万
-$18,167/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$564万
-$18,489/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$618万
-$20,058/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$611万
-$19,961/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$863万
-$20,112/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$547万
-$17,805/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,083万
-$21,315/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,009万
-$20,932/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,210万
-$21,956/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$649万
-$21,134/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$640万
-$20,305/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$818万
-$18,633/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$555万
-$18,124/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$562万
-$18,443/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$616万
-$19,984/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$598万
-$19,542/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$837万
-$19,510/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$540万
-$17,590/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,037万
-$20,409/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,008万
-$20,913/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,199万
-$21,757/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$642万
-$20,906/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$633万
-$20,105/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$791万
-$18,009/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$553万
-$18,078/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$561万
-$18,393/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$590万
-$19,169/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$607万
-$19,830/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$847万
-$19,739/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$534万
-$17,404/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,061万
-$20,882/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,029万
-$21,344/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,169万
-$21,212/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$660万
-$21,511/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$627万
-$19,905/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$786万
-$17,911/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$550万
-$17,974/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$558万
-$18,305/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$577万
-$18,727/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$572万
-$18,686/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$821万
-$19,091/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$528万
-$17,199/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,051万
-$20,685/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,021万
-$21,178/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,158万
-$21,013/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$629万
-$20,482/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$621万
-$19,711/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$782万
-$17,809/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$549万
-$17,941/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$557万
-$18,259/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$575万
-$18,662/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$570万
-$18,621/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$814万
-$18,979/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$521万
-$16,971/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,025万
-$20,173/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$997万
-$20,680/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,147万
-$20,813/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$623万
-$20,287/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$615万
-$19,517/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$778万
-$17,711/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$548万
-$17,899/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$556万
-$18,216/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$573万
-$18,597/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$568万
-$18,616/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$812万
-$18,881/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$520万
-$16,954/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,053万
-$20,724/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$994万
-$20,627/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,102万
-$19,998/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$618万
-$20,130/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$609万
-$19,340/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$773万
-$17,608/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$546万
-$17,853/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$554万
-$18,174/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$571万
-$18,532/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$566万
-$18,490/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$809万
-$18,865/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$520万
-$16,938/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,020万
-$20,085/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$992万
-$20,585/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,091万
-$19,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$653万
-$21,264/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$604万
-$19,168/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$769万
-$17,510/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$545万
-$17,810/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$553万
-$18,065/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$569万
-$18,468/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$564万
-$18,425/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$807万
-$18,763/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$519万
-$16,915/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,091万
-$21,472/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$990万
-$20,539/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,159万
-$21,031/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$611万
-$19,896/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$603万
-$19,137/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$787万
-$17,923/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$544万
-$17,765/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$552万
-$18,092/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$567万
-$18,403/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$562万
-$18,359/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$804万
-$18,748/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$519万
-$16,899/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,044万
-$20,547/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,009万
-$20,929/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,151万
-$20,886/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$649万
-$21,134/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$602万
-$19,105/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$782万
-$17,809/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$542万
-$17,722/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$550万
-$18,033/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$566万
-$18,370/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$560万
-$18,301/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$790万
-$18,367/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$518万
-$16,883/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,068万
-$21,020/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$986万
-$20,456/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,213万
-$22,011/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$607万
-$19,765/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$600万
-$19,048/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$778万
-$17,718/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$541万
-$17,676/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$549万
-$17,990/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$565万
-$18,331/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$559万
-$18,268/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$782万
-$18,179/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$518万
-$16,866/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,093万
-$21,512/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,027万
-$21,303/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,181万
-$21,432/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$604万
-$19,668/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$589万
-$18,698/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$774万
-$17,626/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$536万
-$17,500/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$543万
-$17,810/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$572万
-$18,578/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$549万
-$17,935/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$774万
-$17,998/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$510万
-$16,612/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,033万
-$20,331/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,004万
-$20,826/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,114万
-$20,214/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$639万
-$20,808/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$586万
-$18,610/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$747万
-$17,009/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$534万
-$17,461/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$542万
-$17,709/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$569万
-$18,487/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$546万
-$17,830/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$762万
-$17,719/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$501万
-$16,313/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$1,028万
-$20,236/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$999万
-$20,722/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,103万
-$20,015/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$647万
-$21,068/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$603万
-$19,152/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$741万
-$16,884/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$533万
-$17,415/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$540万
-$17,663/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$548万
-$17,792/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$564万
-$18,502/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$748万
-$17,393/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$498万
-$16,221/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$919万
-$18,087/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$893万
-$18,527/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,099万
-$19,942/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$637万
-$20,743/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$598万
-$18,978/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$732万
-$16,670/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$526万
-$17,196/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$534万
-$17,498/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$540万
-$17,526/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$534万
-$17,444/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L32" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$735万
-$17,088/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$495万
-$16,117/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$889万
-$17,500/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$844万
-$17,502/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,122万
-$20,363/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$570万
-$18,560/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$552万
-$17,517/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$725万
-$16,510/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$518万
-$16,915/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 305呎 (1房)
-$525万
-$17,213/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$531万
-$17,240/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$526万
-$17,190/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$738万
-$17,160/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$491万
-$16,003/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 508呎 (2房)
-$864万
-$17,002/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$820万
-$17,002/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 551呎 (2房)
-$1,060万
-$19,234/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$553万
-$18,007/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$536万
-$17,000/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$725万
-$16,510/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$505万
-$16,503/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$519万
-$16,954/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$524万
-$17,006/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>K | 305呎 (1房)
-$519万
-$17,010/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L34" s="17" t="inlineStr">
-        <is>
-          <t>L | 430呎 (2房)
-$710万
-$16,512/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>M | 307呎 (1房)
-$492万
-$16,020/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 470呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 445呎 (2房)
-$1,066万
-$23,946/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 513呎 (2房)
-$1,313万
-$25,591/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-$725万
-$16,510/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$505万
-$16,503/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$519万
-$16,954/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$524万
-$17,006/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K35" s="17" t="inlineStr">
-        <is>
-          <t>K | 306呎 (1房)
-$519万
-$16,954/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L35" s="17" t="inlineStr">
-        <is>
-          <t>L | 429呎 (2房)
-$710万
-$16,550/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>M | 269呎 (1房)
-$600万
-$22,305/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2C座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +155,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +236,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -47523,4 +47721,9274 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1172万
+$23,526/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1598万
+$29,925/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$1519万
+$34,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$948万
+$30,984/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$951万
+$31,187/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$974万
+$31,951/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$962万
+$31,227/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1143万
+$26,574/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$970万
+$20,166/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$954万
+$33,111/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1587万
+$31,869/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1593万
+$29,837/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$1471万
+$33,666/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$1129万
+$26,433/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$923万
+$30,167/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$926万
+$30,357/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$929万
+$30,456/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$936万
+$30,406/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$1107万
+$23,010/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$998万
+$34,667/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$2144万
+$27,698/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1233万
+$23,000/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1452万
+$29,151/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1584万
+$29,665/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$1122万
+$26,269/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$907万
+$29,631/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$910万
+$29,833/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$913万
+$29,944/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$920万
+$29,886/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$1059万
+$22,012/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="N7" s="22" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$899万
+$31,212/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$2715万
+$35,218/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1150万
+$21,455/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1489万
+$29,894/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1271万
+$23,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$856万
+$20,059/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$956万
+$31,232/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$635万
+$20,813/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$972万
+$31,859/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 309呎 (1房)
+$653万
+$21,126/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$809万
+$18,814/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$1010万
+$20,998/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$994万
+$34,503/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$2007万
+$25,928/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1138万
+$21,231/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1423万
+$28,572/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1188万
+$22,238/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$958万
+$21,918/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$846万
+$19,822/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$676万
+$22,092/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$632万
+$20,647/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$962万
+$31,554/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$646万
+$20,958/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$891万
+$20,726/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$1008万
+$20,967/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$988万
+$34,295/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1126万
+$21,000/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1419万
+$28,488/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1239万
+$23,199/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$999万
+$22,856/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$851万
+$19,925/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$670万
+$21,889/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$1163万
+$38,144/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 306呎 (1房)
+$696万
+$22,732/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 309呎 (1房)
+$615万
+$19,916/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$860万
+$20,000/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$990万
+$20,582/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$672万
+$23,579/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1889万
+$24,403/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1099万
+$20,500/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1415万
+$28,406/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1162万
+$21,753/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$909万
+$20,798/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$836万
+$19,590/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$664万
+$21,693/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$627万
+$20,484/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 306呎 (1房)
+$689万
+$22,516/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 309呎 (1房)
+$613万
+$19,848/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$890万
+$20,695/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$1007万
+$20,933/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$679万
+$23,569/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1748万
+$22,672/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1085万
+$20,235/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1078万
+$20,185/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$864万
+$19,767/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$839万
+$19,644/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$658万
+$21,487/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$620万
+$20,261/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$550万
+$18,030/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$608万
+$19,756/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$792万
+$18,409/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$998万
+$20,753/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$672万
+$23,579/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1760万
+$22,827/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1080万
+$20,142/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1451万
+$29,145/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1087万
+$20,358/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$857万
+$19,616/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$789万
+$18,485/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$651万
+$21,275/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$596万
+$19,471/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$546万
+$17,892/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$605万
+$19,653/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$876万
+$20,377/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$994万
+$20,674/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$631万
+$22,133/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1807万
+$23,344/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1060万
+$19,778/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1387万
+$27,851/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1114万
+$20,861/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$857万
+$19,606/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$778万
+$18,220/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$542万
+$17,703/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$592万
+$19,350/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$539万
+$17,685/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$602万
+$19,549/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$875万
+$20,344/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$992万
+$20,626/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$553万
+$19,215/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1755万
+$22,679/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1060万
+$19,767/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1383万
+$27,775/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1054万
+$19,745/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$849万
+$19,437/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$786万
+$18,412/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$540万
+$17,663/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$589万
+$19,302/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$540万
+$17,695/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 309呎 (1房)
+$599万
+$19,382/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$873万
+$20,312/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$991万
+$20,595/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$552万
+$19,153/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1967万
+$25,411/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1068万
+$19,925/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1096万
+$20,530/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$922万
+$21,094/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$777万
+$18,187/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$537万
+$17,562/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$585万
+$19,184/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$538万
+$17,639/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$595万
+$19,318/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$777万
+$18,063/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$989万
+$20,557/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$598万
+$20,989/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1774万
+$22,917/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1062万
+$19,817/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1100万
+$22,092/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1034万
+$19,354/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$927万
+$21,215/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$769万
+$18,009/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$536万
+$17,529/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$584万
+$19,134/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$536万
+$17,584/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 309呎 (1房)
+$592万
+$19,162/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$871万
+$20,253/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$978万
+$20,333/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$594万
+$20,853/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1718万
+$22,283/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1047万
+$19,530/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1371万
+$27,532/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1038万
+$19,436/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$838万
+$19,183/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$773万
+$18,103/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$637万
+$20,807/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$581万
+$19,036/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$537万
+$17,597/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$546万
+$17,724/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$869万
+$20,216/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$986万
+$20,491/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$549万
+$19,249/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1851万
+$23,912/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1050万
+$19,590/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1367万
+$27,456/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1027万
+$19,238/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$915万
+$20,934/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$855万
+$20,014/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$530万
+$17,324/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$580万
+$19,003/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$532万
+$17,459/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$590万
+$19,159/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$781万
+$18,172/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$984万
+$20,457/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$549万
+$19,059/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1888万
+$24,393/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1063万
+$19,826/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$1027万
+$19,238/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$875万
+$20,018/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$855万
+$20,014/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$530万
+$17,324/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$536万
+$17,561/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$534万
+$17,505/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$541万
+$17,562/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$779万
+$18,109/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$984万
+$20,457/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$589万
+$20,441/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1650万
+$21,401/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1025万
+$19,123/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1143万
+$22,994/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$983万
+$18,416/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$829万
+$18,966/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$847万
+$19,845/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$506万
+$16,539/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$504万
+$16,511/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$528万
+$17,321/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$520万
+$16,873/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$859万
+$19,984/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$977万
+$20,316/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$485万
+$16,847/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1660万
+$21,530/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1007万
+$18,795/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$1079万
+$21,663/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$978万
+$18,324/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$818万
+$18,709/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$846万
+$19,806/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$627万
+$20,497/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$501万
+$16,430/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$525万
+$17,203/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$517万
+$16,779/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$857万
+$19,928/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$973万
+$20,237/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$483万
+$16,785/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1683万
+$21,829/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1021万
+$19,050/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1081万
+$21,746/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$976万
+$18,270/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$818万
+$18,725/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$844万
+$19,770/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$503万
+$16,428/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$504万
+$16,531/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$525万
+$17,223/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$516万
+$16,747/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$855万
+$19,888/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$971万
+$20,191/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$492万
+$17,066/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1626万
+$21,089/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$997万
+$18,601/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$980万
+$18,350/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$806万
+$18,449/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$842万
+$19,721/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$502万
+$16,399/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$499万
+$16,367/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$522万
+$17,108/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$515万
+$16,708/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$853万
+$19,847/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$969万
+$20,150/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$490万
+$17,017/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1759万
+$22,724/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1001万
+$18,679/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1071万
+$21,545/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$970万
+$18,161/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$799万
+$18,293/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$840万
+$19,660/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$501万
+$16,366/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$498万
+$16,331/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 306呎 (1房)
+$524万
+$17,131/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$514万
+$16,675/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$852万
+$19,805/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$967万
+$20,108/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$479万
+$16,628/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1650万
+$21,401/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$991万
+$18,494/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$996万
+$20,000/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$967万
+$18,110/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$800万
+$18,311/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$837万
+$19,597/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$500万
+$16,330/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$497万
+$16,298/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$519万
+$17,010/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$641万
+$20,805/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$850万
+$19,767/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$965万
+$20,067/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$477万
+$16,576/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1697万
+$21,922/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1002万
+$18,700/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$997万
+$20,016/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$964万
+$18,058/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$796万
+$18,217/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$835万
+$19,560/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$499万
+$16,310/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$500万
+$16,393/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$519万
+$17,026/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$512万
+$16,607/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$861万
+$20,065/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$963万
+$20,025/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$476万
+$16,702/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1666万
+$21,606/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$988万
+$18,437/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1001万
+$20,137/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$964万
+$18,058/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$819万
+$18,746/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$835万
+$19,560/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$621万
+$20,307/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$500万
+$16,393/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 306呎 (1房)
+$592万
+$19,337/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$512万
+$16,607/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$848万
+$19,721/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$963万
+$20,025/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$486万
+$16,865/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1681万
+$21,800/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$993万
+$18,522/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$981万
+$19,701/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$954万
+$17,875/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$797万
+$18,231/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$829万
+$19,412/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$496万
+$16,199/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$493万
+$16,161/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$514万
+$16,846/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$508万
+$16,484/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$844万
+$19,619/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$868万
+$18,037/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$472万
+$16,392/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1661万
+$21,460/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$980万
+$18,282/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 498呎 (2房)
+$976万
+$19,606/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$948万
+$17,760/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$792万
+$18,114/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$790万
+$18,501/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$494万
+$16,134/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$491万
+$16,089/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$516万
+$16,925/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$506万
+$16,425/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$842万
+$19,572/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$956万
+$19,865/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$471万
+$16,365/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1608万
+$20,856/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$992万
+$18,498/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$999万
+$20,097/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$954万
+$17,873/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$797万
+$18,243/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$726万
+$16,998/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$498万
+$16,258/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$493万
+$16,167/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$520万
+$17,049/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$505万
+$16,390/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$746万
+$17,351/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$846万
+$17,593/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$479万
+$16,628/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1660万
+$21,444/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$978万
+$18,241/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$974万
+$19,594/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$939万
+$17,590/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$787万
+$18,011/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$822万
+$19,251/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$490万
+$16,007/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$488万
+$16,003/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$509万
+$16,682/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$502万
+$16,299/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$839万
+$19,507/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$836万
+$17,380/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>N | 285呎 (1房)
+$467万
+$16,400/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1681万
+$21,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$983万
+$18,343/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$985万
+$19,815/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$983万
+$18,404/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$788万
+$18,043/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$714万
+$16,733/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$488万
+$15,941/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$523万
+$17,148/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$510万
+$16,738/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$499万
+$16,205/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$837万
+$19,458/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$835万
+$17,356/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$465万
+$16,153/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1681万
+$21,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$978万
+$18,239/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$978万
+$19,674/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 534呎 (2房)
+$994万
+$18,609/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (2房)
+$787万
+$18,014/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 427呎 (2房)
+$711万
+$16,656/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$487万
+$15,928/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$520万
+$17,059/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>J | 305呎 (1房)
+$534万
+$17,492/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>K | 308呎 (1房)
+$503万
+$16,328/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$729万
+$16,949/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>M | 481呎 (2房)
+$831万
+$17,285/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>N | 288呎 (1房)
+$461万
+$15,997/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$1613万
+$34,030/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$1322万
+$29,369/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1289万
+$27,019/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1289万
+$23,315/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$825万
+$26,883/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$1132万
+$26,201/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$1124万
+$26,074/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1429万
+$24,389/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$1542万
+$32,532/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$1318万
+$29,284/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1600万
+$33,549/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$823万
+$26,808/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$1128万
+$26,120/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$1120万
+$25,998/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 537呎 (2房)
+$1454万
+$27,073/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1465万
+$25,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1559万
+$32,681/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1278万
+$23,105/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$818万
+$26,638/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1250万
+$23,234/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1432万
+$24,437/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$1064万
+$22,443/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$999万
+$22,196/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1396万
+$29,264/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1208万
+$21,852/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$956万
+$31,140/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$823万
+$19,051/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$812万
+$18,789/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1148万
+$21,338/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1407万
+$24,007/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$993万
+$20,947/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$993万
+$22,062/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1392万
+$29,178/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1229万
+$22,221/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$634万
+$20,645/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$788万
+$18,243/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$807万
+$18,688/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1130万
+$21,000/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1408万
+$24,027/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$988万
+$20,842/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$1889万
+$41,973/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1388万
+$29,094/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1201万
+$21,723/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$631万
+$20,547/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$811万
+$18,778/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$806万
+$18,653/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1128万
+$20,967/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1348万
+$23,003/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$960万
+$20,245/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$987万
+$21,929/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1384万
+$29,008/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1244万
+$22,503/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$626万
+$20,375/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$770万
+$17,824/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$803万
+$18,590/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1087万
+$20,201/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1298万
+$22,150/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$955万
+$20,141/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$977万
+$21,707/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1368万
+$28,690/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1234万
+$22,311/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$646万
+$21,026/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$760万
+$17,583/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$757万
+$17,568/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 537呎 (2房)
+$1060万
+$19,739/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1293万
+$22,070/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$978万
+$20,627/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$917万
+$20,373/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1362万
+$28,547/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1221万
+$22,083/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$618万
+$20,124/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$778万
+$18,007/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$759万
+$17,615/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1052万
+$19,548/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1293万
+$22,058/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$938万
+$19,781/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$914万
+$20,318/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1175万
+$21,248/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$602万
+$19,603/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$755万
+$17,468/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$760万
+$17,643/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1067万
+$19,840/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1299万
+$22,162/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$956万
+$20,169/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$912万
+$20,256/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1054万
+$22,092/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1176万
+$21,266/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$588万
+$19,150/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$753万
+$17,431/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$786万
+$18,230/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1049万
+$19,498/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1276万
+$21,776/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$952万
+$20,093/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$909万
+$20,200/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1048万
+$21,966/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1210万
+$21,888/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$585万
+$19,046/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$752万
+$17,396/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$749万
+$17,387/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1061万
+$19,723/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1508万
+$25,741/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$926万
+$19,540/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$906万
+$20,144/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1337万
+$28,031/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1207万
+$21,823/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$605万
+$19,710/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$750万
+$17,361/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$785万
+$18,216/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1036万
+$19,247/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1279万
+$21,821/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$927万
+$19,553/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$904万
+$20,087/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1333万
+$27,945/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1203万
+$21,758/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$602万
+$19,612/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$746万
+$17,269/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$781万
+$18,076/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1055万
+$19,602/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1280万
+$21,838/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$914万
+$19,287/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$901万
+$20,027/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1329万
+$27,862/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1151万
+$20,812/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$599万
+$19,508/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$747万
+$17,292/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$750万
+$17,408/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1026万
+$19,061/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1290万
+$22,014/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$918万
+$19,357/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$898万
+$19,958/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1162万
+$21,016/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$597万
+$19,446/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$739万
+$17,106/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$777万
+$17,981/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$1026万
+$19,061/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1359万
+$23,188/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$880万
+$18,557/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$862万
+$19,164/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1019万
+$21,358/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1187万
+$21,463/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$512万
+$16,681/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$707万
+$16,370/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$730万
+$16,926/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$982万
+$18,249/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1478万
+$25,217/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$875万
+$18,466/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$974万
+$21,651/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$961万
+$20,143/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1181万
+$21,353/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$616万
+$20,072/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$706万
+$16,338/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$728万
+$16,891/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$976万
+$18,147/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1216万
+$20,746/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$879万
+$18,553/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$884万
+$19,633/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1295万
+$27,153/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1177万
+$21,289/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$503万
+$16,397/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$704万
+$16,306/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$839万
+$19,462/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$973万
+$18,093/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1222万
+$20,846/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$870万
+$18,361/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$848万
+$18,833/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1174万
+$21,226/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$502万
+$16,365/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$703万
+$16,269/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$714万
+$16,528/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$989万
+$18,375/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1200万
+$20,478/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$964万
+$20,333/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$878万
+$19,520/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$999万
+$20,939/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1170万
+$21,161/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$612万
+$19,948/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$701万
+$16,234/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$719万
+$16,691/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$986万
+$18,320/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1206万
+$20,577/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$872万
+$18,392/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$860万
+$19,111/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$937万
+$19,639/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1167万
+$21,098/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$500万
+$16,303/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$700万
+$16,201/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$709万
+$16,441/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$965万
+$17,929/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1193万
+$20,363/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$879万
+$18,546/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$960万
+$21,340/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$931万
+$19,514/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1134万
+$20,510/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$499万
+$16,267/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$698万
+$16,167/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$710万
+$16,471/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$962万
+$17,875/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1227万
+$20,935/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$863万
+$18,205/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$867万
+$19,273/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$984万
+$20,625/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1134万
+$20,510/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$499万
+$16,267/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$790万
+$18,287/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$707万
+$16,411/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 537呎 (2房)
+$962万
+$17,909/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1265万
+$21,587/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$894万
+$18,861/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$865万
+$19,227/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1150万
+$20,803/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$496万
+$16,150/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$695万
+$16,095/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$701万
+$16,222/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$949万
+$17,643/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1188万
+$20,275/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$851万
+$17,956/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$828万
+$18,407/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$992万
+$20,801/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1144万
+$20,685/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$579万
+$18,853/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$693万
+$16,042/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$699万
+$16,225/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$945万
+$17,572/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1179万
+$20,123/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$866万
+$18,264/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$824万
+$18,316/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$914万
+$19,157/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1085万
+$19,617/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$498万
+$16,225/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$700万
+$16,199/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$700万
+$16,248/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$949万
+$17,647/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1173万
+$20,014/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$843万
+$17,778/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$938万
+$20,833/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$907万
+$19,010/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1051万
+$19,013/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$491万
+$16,003/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$721万
+$16,694/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 431呎 (2房)
+$689万
+$15,986/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$930万
+$17,279/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 586呎 (3房)
+$1172万
+$20,000/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 474呎 (2房)
+$863万
+$18,211/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$848万
+$18,836/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$947万
+$19,849/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1038万
+$18,772/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$490万
+$15,958/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$688万
+$15,928/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 432呎 (2房)
+$754万
+$17,461/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>J | 538呎 (2房)
+$969万
+$18,011/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$856万
+$18,334/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+$836万
+$18,584/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$938万
+$19,660/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1027万
+$18,579/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$489万
+$15,928/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 432呎 (2房)
+$688万
+$15,928/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+$803万
+$20,585/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J34" s="24" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 483呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$1070万
+$34,866/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+$1257万
+$40,032/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$1349万
+$30,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$952万
+$31,101/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$953万
+$31,246/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$961万
+$31,201/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$970万
+$31,816/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1377万
+$32,023/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$957万
+$31,173/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>B | 483呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$1052万
+$34,257/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+$1053万
+$33,535/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$1320万
+$30,062/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$932万
+$30,448/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$929万
+$30,459/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$941万
+$30,539/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$950万
+$31,161/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1350万
+$31,405/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$936万
+$30,479/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 483呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$1044万
+$33,997/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+$1026万
+$32,688/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$958万
+$31,320/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$966万
+$31,685/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$985万
+$31,981/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$989万
+$32,426/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$982万
+$32,000/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1321万
+$26,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1254万
+$26,008/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$978万
+$31,860/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$984万
+$31,225/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$1173万
+$26,720/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$678万
+$22,144/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$866万
+$28,387/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$875万
+$28,419/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$936万
+$30,679/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1257万
+$29,233/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$637万
+$20,743/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1193万
+$23,480/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1161万
+$24,083/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1350万
+$24,501/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$1025万
+$33,375/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$1046万
+$33,206/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$672万
+$21,948/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$923万
+$30,249/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$933万
+$30,279/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$925万
+$30,315/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$631万
+$20,547/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1257万
+$24,748/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$956万
+$31,156/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$960万
+$30,492/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$1126万
+$25,640/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$666万
+$21,752/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$850万
+$27,856/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$858万
+$27,847/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$915万
+$30,013/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1232万
+$28,644/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$625万
+$20,352/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1187万
+$23,362/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1150万
+$23,855/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$994万
+$32,378/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$1015万
+$32,232/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$901万
+$20,519/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$639万
+$20,876/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$905万
+$29,575/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$914万
+$29,679/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$908万
+$29,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$596万
+$19,397/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1167万
+$22,969/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1114万
+$23,108/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$935万
+$30,453/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$940万
+$29,848/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$892万
+$20,314/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$633万
+$20,680/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$832万
+$27,279/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$841万
+$27,318/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$897万
+$29,410/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$1205万
+$28,023/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$589万
+$19,179/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1119万
+$22,024/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1089万
+$22,589/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$716万
+$23,329/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$986万
+$31,289/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$849万
+$19,335/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$627万
+$20,484/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$646万
+$21,098/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$896万
+$29,081/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$647万
+$21,137/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$936万
+$21,807/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$582万
+$18,971/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1107万
+$21,787/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1077万
+$22,340/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$701万
+$22,827/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$704万
+$22,343/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$844万
+$19,221/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$560万
+$18,301/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$568万
+$18,562/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$824万
+$26,747/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$639万
+$20,876/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$925万
+$21,507/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$565万
+$18,401/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1091万
+$21,472/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1061万
+$22,008/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1262万
+$22,900/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$692万
+$22,534/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$672万
+$21,340/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$831万
+$18,925/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$559万
+$18,258/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$567万
+$18,520/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$588万
+$19,091/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$629万
+$20,616/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$909万
+$21,135/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$559万
+$18,202/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1080万
+$21,256/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1051万
+$21,801/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1213万
+$22,011/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$687万
+$22,371/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$690万
+$21,898/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$827万
+$18,834/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$557万
+$18,203/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$566万
+$18,480/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$607万
+$19,701/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$602万
+$19,690/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$882万
+$20,555/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$553万
+$18,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1109万
+$21,827/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1041万
+$21,593/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$655万
+$21,336/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$683万
+$21,676/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$823万
+$18,743/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$556万
+$18,167/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$564万
+$18,489/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$618万
+$20,058/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$611万
+$19,961/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$863万
+$20,112/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$547万
+$17,805/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1083万
+$21,315/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1009万
+$20,932/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1210万
+$21,956/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$649万
+$21,134/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$640万
+$20,305/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$818万
+$18,633/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$555万
+$18,124/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$562万
+$18,443/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$616万
+$19,984/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$598万
+$19,542/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$837万
+$19,510/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$540万
+$17,590/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1037万
+$20,409/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1008万
+$20,913/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1199万
+$21,757/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$642万
+$20,906/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$633万
+$20,105/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$791万
+$18,009/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$553万
+$18,078/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$561万
+$18,393/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$590万
+$19,169/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$607万
+$19,830/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$847万
+$19,739/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$534万
+$17,404/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1061万
+$20,882/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1029万
+$21,344/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1169万
+$21,212/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$660万
+$21,511/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$627万
+$19,905/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$786万
+$17,911/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$550万
+$17,974/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$558万
+$18,305/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$577万
+$18,727/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$572万
+$18,686/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$821万
+$19,091/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$528万
+$17,199/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1051万
+$20,685/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1021万
+$21,178/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1158万
+$21,013/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$629万
+$20,482/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$621万
+$19,711/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$782万
+$17,809/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$549万
+$17,941/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$557万
+$18,259/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$575万
+$18,662/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$570万
+$18,621/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$814万
+$18,979/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$521万
+$16,971/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1025万
+$20,173/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$997万
+$20,680/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1147万
+$20,813/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$623万
+$20,287/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$615万
+$19,517/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$778万
+$17,711/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$548万
+$17,899/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$556万
+$18,216/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$573万
+$18,597/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$568万
+$18,616/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$812万
+$18,881/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$520万
+$16,954/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1053万
+$20,724/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$994万
+$20,627/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1102万
+$19,998/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$618万
+$20,130/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$609万
+$19,340/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$773万
+$17,608/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$546万
+$17,853/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$554万
+$18,174/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$571万
+$18,532/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$566万
+$18,490/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$809万
+$18,865/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$520万
+$16,938/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1020万
+$20,085/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$992万
+$20,585/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1091万
+$19,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$653万
+$21,264/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$604万
+$19,168/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$769万
+$17,510/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$545万
+$17,810/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$553万
+$18,065/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$569万
+$18,468/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$564万
+$18,425/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$807万
+$18,763/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$519万
+$16,915/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1091万
+$21,472/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$990万
+$20,539/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1159万
+$21,031/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$611万
+$19,896/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$603万
+$19,137/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$787万
+$17,923/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$544万
+$17,765/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$552万
+$18,092/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$567万
+$18,403/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$562万
+$18,359/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$804万
+$18,748/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$519万
+$16,899/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1044万
+$20,547/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1009万
+$20,929/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1151万
+$20,886/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$649万
+$21,134/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$602万
+$19,105/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$782万
+$17,809/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$542万
+$17,722/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$550万
+$18,033/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$566万
+$18,370/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$560万
+$18,301/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$790万
+$18,367/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$518万
+$16,883/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1068万
+$21,020/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$986万
+$20,456/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1213万
+$22,011/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$607万
+$19,765/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$600万
+$19,048/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$778万
+$17,718/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$541万
+$17,676/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$549万
+$17,990/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$565万
+$18,331/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$559万
+$18,268/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$782万
+$18,179/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$518万
+$16,866/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1093万
+$21,512/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1027万
+$21,303/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1181万
+$21,432/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$604万
+$19,668/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$589万
+$18,698/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$774万
+$17,626/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$536万
+$17,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$543万
+$17,810/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$572万
+$18,578/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$549万
+$17,935/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$774万
+$17,998/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$510万
+$16,612/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1033万
+$20,331/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1004万
+$20,826/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1114万
+$20,214/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$639万
+$20,808/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$586万
+$18,610/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$747万
+$17,009/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$534万
+$17,461/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$542万
+$17,709/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$569万
+$18,487/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$546万
+$17,830/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$762万
+$17,719/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$501万
+$16,313/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$1028万
+$20,236/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$999万
+$20,722/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1103万
+$20,015/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$647万
+$21,068/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$603万
+$19,152/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$741万
+$16,884/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$533万
+$17,415/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$540万
+$17,663/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$548万
+$17,792/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$564万
+$18,502/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$748万
+$17,393/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$498万
+$16,221/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$919万
+$18,087/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$893万
+$18,527/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1099万
+$19,942/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$637万
+$20,743/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$598万
+$18,978/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$732万
+$16,670/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$526万
+$17,196/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$534万
+$17,498/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$540万
+$17,526/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$534万
+$17,444/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$735万
+$17,088/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$495万
+$16,117/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$889万
+$17,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$844万
+$17,502/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1122万
+$20,363/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$570万
+$18,560/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$552万
+$17,517/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$725万
+$16,510/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$518万
+$16,915/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 305呎 (1房)
+$525万
+$17,213/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$531万
+$17,240/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$526万
+$17,190/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$738万
+$17,160/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$491万
+$16,003/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 508呎 (2房)
+$864万
+$17,002/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$820万
+$17,002/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 551呎 (2房)
+$1060万
+$19,234/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$553万
+$18,007/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$536万
+$17,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$725万
+$16,510/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$505万
+$16,503/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$519万
+$16,954/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$524万
+$17,006/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>K | 305呎 (1房)
+$519万
+$17,010/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>L | 430呎 (2房)
+$710万
+$16,512/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>M | 307呎 (1房)
+$492万
+$16,020/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 470呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 445呎 (2房)
+$1066万
+$23,946/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 513呎 (2房)
+$1313万
+$25,591/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr"/>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+$725万
+$16,510/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$505万
+$16,503/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$519万
+$16,954/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$524万
+$17,006/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>K | 306呎 (1房)
+$519万
+$16,954/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>L | 429呎 (2房)
+$710万
+$16,550/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>M | 269呎 (1房)
+$600万
+$22,305/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -672,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -33625,7 +33625,7 @@
       </c>
       <c r="G714" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H714" s="5" t="n">
@@ -54372,7 +54372,7 @@
           <t>G | 306呎 (1房)
 $672万
 $21,948/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -802,14 +802,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>6007680</v>
+        <v>7724160</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>20860</v>
+        <v>26820</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -926,18 +926,18 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>7199010</v>
+        <v>9255870</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>16742</v>
+        <v>21525</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -988,14 +988,14 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>6059340</v>
+        <v>7790580</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>19673</v>
+        <v>25294</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1050,18 +1050,18 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6139350</v>
+        <v>6431700</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>20129</v>
+        <v>21088</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5992560</v>
+        <v>7704720</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>19648</v>
+        <v>25261</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1174,14 +1174,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>5973030</v>
+        <v>7679610</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>19520</v>
+        <v>25097</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1306,14 +1306,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>9570960</v>
+        <v>12305520</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>21902</v>
+        <v>28159</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1368,18 +1368,18 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>10067400</v>
+        <v>12943800</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>18853</v>
+        <v>24239</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1632,14 +1632,14 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6289920</v>
+        <v>8087040</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>21840</v>
+        <v>28080</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1826,14 +1826,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>5899950</v>
+        <v>7585650</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19156</v>
+        <v>24629</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1888,14 +1888,14 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5852070</v>
+        <v>7524090</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>19187</v>
+        <v>24669</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1950,14 +1950,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>5833170</v>
+        <v>7499790</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>19125</v>
+        <v>24589</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2012,14 +2012,14 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>5815530</v>
+        <v>7477110</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>19005</v>
+        <v>24435</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2074,18 +2074,18 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>7110810</v>
+        <v>9142470</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>16653</v>
+        <v>21411</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>9268560</v>
+        <v>11916720</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>21210</v>
+        <v>27269</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2198,18 +2198,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>10037790</v>
+        <v>12905730</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>18797</v>
+        <v>24168</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2260,14 +2260,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>9998730</v>
+        <v>12855510</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>20078</v>
+        <v>25814</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2462,14 +2462,14 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5663070</v>
+        <v>7281090</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>19663</v>
+        <v>25282</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2656,14 +2656,14 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5799150</v>
+        <v>7456050</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>18828</v>
+        <v>24208</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>5753790</v>
+        <v>7397730</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>18865</v>
+        <v>24255</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2780,14 +2780,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>5732370</v>
+        <v>7370190</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>18795</v>
+        <v>24165</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>5712210</v>
+        <v>7344270</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>18667</v>
+        <v>24001</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2904,18 +2904,18 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>7066710</v>
+        <v>9085770</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>16550</v>
+        <v>21278</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3036,18 +3036,18 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>9979830</v>
+        <v>12831210</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>18689</v>
+        <v>24028</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3098,18 +3098,18 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>9145710</v>
+        <v>11758770</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>18365</v>
+        <v>23612</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3284,14 +3284,14 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>6260310</v>
+        <v>7179482</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>21737</v>
+        <v>24929</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6121710</v>
+        <v>7287750</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>20071</v>
+        <v>23894</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3656,14 +3656,14 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>6020910</v>
+        <v>7167750</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>19676</v>
+        <v>23424</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3912,14 +3912,14 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>9378810</v>
+        <v>12058470</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>18833</v>
+        <v>24214</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4036,14 +4036,14 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>17106390</v>
+        <v>21993930</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>22187</v>
+        <v>28526</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4098,14 +4098,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>6222510</v>
+        <v>7111440</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>21606</v>
+        <v>24692</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4346,14 +4346,14 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>6063120</v>
+        <v>7218000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>19879</v>
+        <v>23666</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4718,18 +4718,18 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K65" s="5" t="n">
-        <v>8964270</v>
+        <v>11525490</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>18001</v>
+        <v>23144</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>7329420</v>
+        <v>8027460</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>24031</v>
+        <v>26320</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5524,18 +5524,18 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>8937810</v>
+        <v>11491470</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>17947</v>
+        <v>23075</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -6338,18 +6338,18 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>8911980</v>
+        <v>11458260</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>17896</v>
+        <v>23009</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -7958,14 +7958,14 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>9143820</v>
+        <v>11756340</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>18361</v>
+        <v>23607</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8764,18 +8764,18 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K130" s="5" t="n">
-        <v>8738100</v>
+        <v>11234700</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>17546</v>
+        <v>22560</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
@@ -9570,18 +9570,18 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>8714160</v>
+        <v>11203920</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>17498</v>
+        <v>22498</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -11996,18 +11996,18 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>8637930</v>
+        <v>11105910</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>17345</v>
+        <v>22301</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -12802,18 +12802,18 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>8613990</v>
+        <v>11075130</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>17297</v>
+        <v>22239</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -25164,18 +25164,18 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>7079940</v>
+        <v>9102780</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>16427</v>
+        <v>21120</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -25226,18 +25226,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>7130970</v>
+        <v>9168390</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>16507</v>
+        <v>21223</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -25288,18 +25288,18 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>5199390</v>
+        <v>6684930</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>16936</v>
+        <v>21775</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N396" s="3" t="inlineStr">
@@ -25474,18 +25474,18 @@
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>8326080</v>
+        <v>10704960</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>18502</v>
+        <v>23789</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N399" s="3" t="inlineStr">
@@ -25536,14 +25536,14 @@
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>10161900</v>
+        <v>13065300</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>21439</v>
+        <v>27564</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
@@ -25730,18 +25730,18 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K403" s="5" t="n">
-        <v>7059150</v>
+        <v>9076050</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>16379</v>
+        <v>21058</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N403" s="3" t="inlineStr">
@@ -25792,18 +25792,18 @@
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K404" s="5" t="n">
-        <v>7108920</v>
+        <v>9140040</v>
       </c>
       <c r="L404" s="5" t="n">
-        <v>16456</v>
+        <v>21158</v>
       </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N404" s="3" t="inlineStr">
@@ -25854,18 +25854,18 @@
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K405" s="5" t="n">
-        <v>5184900</v>
+        <v>6666300</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>16889</v>
+        <v>21714</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N405" s="3" t="inlineStr">
@@ -25986,14 +25986,14 @@
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K407" s="5" t="n">
-        <v>10081890</v>
+        <v>12962430</v>
       </c>
       <c r="L407" s="5" t="n">
-        <v>21136</v>
+        <v>27175</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
@@ -26048,18 +26048,18 @@
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K408" s="5" t="n">
-        <v>8302140</v>
+        <v>10674180</v>
       </c>
       <c r="L408" s="5" t="n">
-        <v>18449</v>
+        <v>23720</v>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N408" s="3" t="inlineStr">
@@ -26110,14 +26110,14 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>9714600</v>
+        <v>12490200</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>20495</v>
+        <v>26351</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -26436,18 +26436,18 @@
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K414" s="5" t="n">
-        <v>5152140</v>
+        <v>6624180</v>
       </c>
       <c r="L414" s="5" t="n">
-        <v>16782</v>
+        <v>21577</v>
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -26560,18 +26560,18 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K416" s="5" t="n">
-        <v>9821070</v>
+        <v>12627090</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>20589</v>
+        <v>26472</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N416" s="3" t="inlineStr">
@@ -27010,18 +27010,18 @@
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K423" s="5" t="n">
-        <v>6022800</v>
+        <v>7217800</v>
       </c>
       <c r="L423" s="5" t="n">
-        <v>19618</v>
+        <v>23511</v>
       </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N423" s="3" t="inlineStr">
@@ -27134,14 +27134,14 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K425" s="5" t="n">
-        <v>8794170</v>
+        <v>11306790</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>18436</v>
+        <v>23704</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -27692,14 +27692,14 @@
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K434" s="5" t="n">
-        <v>8768340</v>
+        <v>11273580</v>
       </c>
       <c r="L434" s="5" t="n">
-        <v>18382</v>
+        <v>23634</v>
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
@@ -28250,14 +28250,14 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K443" s="5" t="n">
-        <v>8743140</v>
+        <v>11241180</v>
       </c>
       <c r="L443" s="5" t="n">
-        <v>18329</v>
+        <v>23566</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
@@ -28808,14 +28808,14 @@
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K452" s="5" t="n">
-        <v>8717310</v>
+        <v>11207970</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>18275</v>
+        <v>23497</v>
       </c>
       <c r="M452" s="3" t="inlineStr">
         <is>
@@ -29366,18 +29366,18 @@
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K461" s="5" t="n">
-        <v>8621550</v>
+        <v>11084850</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>18075</v>
+        <v>23239</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N461" s="3" t="inlineStr">
@@ -29924,18 +29924,18 @@
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K470" s="5" t="n">
-        <v>8578710</v>
+        <v>11029770</v>
       </c>
       <c r="L470" s="5" t="n">
-        <v>17985</v>
+        <v>23123</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
@@ -32164,18 +32164,18 @@
       </c>
       <c r="J506" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K506" s="5" t="n">
-        <v>8423730</v>
+        <v>10830510</v>
       </c>
       <c r="L506" s="5" t="n">
-        <v>17660</v>
+        <v>22705</v>
       </c>
       <c r="M506" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N506" s="3" t="inlineStr">
@@ -32722,18 +32722,18 @@
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K515" s="5" t="n">
-        <v>8397900</v>
+        <v>10797300</v>
       </c>
       <c r="L515" s="5" t="n">
-        <v>17606</v>
+        <v>22636</v>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N515" s="3" t="inlineStr">
@@ -33280,18 +33280,18 @@
       </c>
       <c r="J524" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K524" s="5" t="n">
-        <v>8372700</v>
+        <v>10764900</v>
       </c>
       <c r="L524" s="5" t="n">
-        <v>17553</v>
+        <v>22568</v>
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N524" s="3" t="inlineStr">
@@ -35520,18 +35520,18 @@
       </c>
       <c r="J560" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="K560" s="5" t="n">
-        <v>8159760</v>
+        <v>10491120</v>
       </c>
       <c r="L560" s="5" t="n">
-        <v>17106</v>
+        <v>21994</v>
       </c>
       <c r="M560" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N560" s="3" t="inlineStr">
@@ -41798,18 +41798,18 @@
       </c>
       <c r="J661" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K661" s="5" t="n">
-        <v>6029100</v>
+        <v>7177500</v>
       </c>
       <c r="L661" s="5" t="n">
-        <v>19639</v>
+        <v>23379</v>
       </c>
       <c r="M661" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N661" s="3" t="inlineStr">
@@ -41860,18 +41860,18 @@
       </c>
       <c r="J662" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K662" s="5" t="n">
-        <v>8675100</v>
+        <v>10327500</v>
       </c>
       <c r="L662" s="5" t="n">
-        <v>20175</v>
+        <v>24017</v>
       </c>
       <c r="M662" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N662" s="3" t="inlineStr">
@@ -41922,18 +41922,18 @@
       </c>
       <c r="J663" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K663" s="5" t="n">
-        <v>6113520</v>
+        <v>7278000</v>
       </c>
       <c r="L663" s="5" t="n">
-        <v>20044</v>
+        <v>23862</v>
       </c>
       <c r="M663" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N663" s="3" t="inlineStr">
@@ -41984,18 +41984,18 @@
       </c>
       <c r="J664" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K664" s="5" t="n">
-        <v>6054300</v>
+        <v>7207500</v>
       </c>
       <c r="L664" s="5" t="n">
-        <v>19657</v>
+        <v>23401</v>
       </c>
       <c r="M664" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N664" s="3" t="inlineStr">
@@ -42046,18 +42046,18 @@
       </c>
       <c r="J665" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K665" s="5" t="n">
-        <v>6003900</v>
+        <v>7147500</v>
       </c>
       <c r="L665" s="5" t="n">
-        <v>19685</v>
+        <v>23434</v>
       </c>
       <c r="M665" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N665" s="3" t="inlineStr">
@@ -42108,18 +42108,18 @@
       </c>
       <c r="J666" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K666" s="5" t="n">
-        <v>5995710</v>
+        <v>7137750</v>
       </c>
       <c r="L666" s="5" t="n">
-        <v>19594</v>
+        <v>23326</v>
       </c>
       <c r="M666" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N666" s="3" t="inlineStr">
@@ -42170,18 +42170,18 @@
       </c>
       <c r="J667" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K667" s="5" t="n">
-        <v>8498700</v>
+        <v>10117500</v>
       </c>
       <c r="L667" s="5" t="n">
-        <v>19359</v>
+        <v>23047</v>
       </c>
       <c r="M667" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N667" s="3" t="inlineStr">
@@ -42232,18 +42232,18 @@
       </c>
       <c r="J668" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K668" s="5" t="n">
-        <v>7919100</v>
+        <v>9427500</v>
       </c>
       <c r="L668" s="5" t="n">
-        <v>25220</v>
+        <v>30024</v>
       </c>
       <c r="M668" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N668" s="3" t="inlineStr">
@@ -42294,18 +42294,18 @@
       </c>
       <c r="J669" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K669" s="5" t="n">
-        <v>6743520</v>
+        <v>8028000</v>
       </c>
       <c r="L669" s="5" t="n">
-        <v>21966</v>
+        <v>26150</v>
       </c>
       <c r="M669" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N669" s="3" t="inlineStr">
@@ -42566,18 +42566,18 @@
       </c>
       <c r="J673" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K673" s="5" t="n">
-        <v>5894910</v>
+        <v>7017750</v>
       </c>
       <c r="L673" s="5" t="n">
-        <v>19202</v>
+        <v>22859</v>
       </c>
       <c r="M673" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N673" s="3" t="inlineStr">
@@ -42628,18 +42628,18 @@
       </c>
       <c r="J674" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K674" s="5" t="n">
-        <v>8507520</v>
+        <v>10128000</v>
       </c>
       <c r="L674" s="5" t="n">
-        <v>19785</v>
+        <v>23553</v>
       </c>
       <c r="M674" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N674" s="3" t="inlineStr">
@@ -42690,18 +42690,18 @@
       </c>
       <c r="J675" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K675" s="5" t="n">
-        <v>5987520</v>
+        <v>7128000</v>
       </c>
       <c r="L675" s="5" t="n">
-        <v>19631</v>
+        <v>23370</v>
       </c>
       <c r="M675" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N675" s="3" t="inlineStr">
@@ -42752,18 +42752,18 @@
       </c>
       <c r="J676" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K676" s="5" t="n">
-        <v>5925780</v>
+        <v>7054500</v>
       </c>
       <c r="L676" s="5" t="n">
-        <v>19240</v>
+        <v>22904</v>
       </c>
       <c r="M676" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N676" s="3" t="inlineStr">
@@ -42814,18 +42814,18 @@
       </c>
       <c r="J677" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K677" s="5" t="n">
-        <v>5852700</v>
+        <v>6967500</v>
       </c>
       <c r="L677" s="5" t="n">
-        <v>19189</v>
+        <v>22844</v>
       </c>
       <c r="M677" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N677" s="3" t="inlineStr">
@@ -42876,18 +42876,18 @@
       </c>
       <c r="J678" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K678" s="5" t="n">
-        <v>5869710</v>
+        <v>6987750</v>
       </c>
       <c r="L678" s="5" t="n">
-        <v>19182</v>
+        <v>22836</v>
       </c>
       <c r="M678" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N678" s="3" t="inlineStr">
@@ -42938,18 +42938,18 @@
       </c>
       <c r="J679" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K679" s="5" t="n">
-        <v>8314110</v>
+        <v>9897750</v>
       </c>
       <c r="L679" s="5" t="n">
-        <v>18939</v>
+        <v>22546</v>
       </c>
       <c r="M679" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N679" s="3" t="inlineStr">
@@ -43000,18 +43000,18 @@
       </c>
       <c r="J680" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K680" s="5" t="n">
-        <v>6633900</v>
+        <v>7897500</v>
       </c>
       <c r="L680" s="5" t="n">
-        <v>21127</v>
+        <v>25151</v>
       </c>
       <c r="M680" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N680" s="3" t="inlineStr">
@@ -43062,18 +43062,18 @@
       </c>
       <c r="J681" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K681" s="5" t="n">
-        <v>6625710</v>
+        <v>7887750</v>
       </c>
       <c r="L681" s="5" t="n">
-        <v>21582</v>
+        <v>25693</v>
       </c>
       <c r="M681" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N681" s="3" t="inlineStr">
@@ -43334,18 +43334,18 @@
       </c>
       <c r="J685" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K685" s="5" t="n">
-        <v>6189120</v>
+        <v>7368000</v>
       </c>
       <c r="L685" s="5" t="n">
-        <v>20160</v>
+        <v>24000</v>
       </c>
       <c r="M685" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N685" s="3" t="inlineStr">
@@ -43466,18 +43466,18 @@
       </c>
       <c r="J687" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K687" s="5" t="n">
-        <v>6230700</v>
+        <v>7417500</v>
       </c>
       <c r="L687" s="5" t="n">
-        <v>20429</v>
+        <v>24320</v>
       </c>
       <c r="M687" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N687" s="3" t="inlineStr">
@@ -43528,18 +43528,18 @@
       </c>
       <c r="J688" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K688" s="5" t="n">
-        <v>6205500</v>
+        <v>7387500</v>
       </c>
       <c r="L688" s="5" t="n">
-        <v>20148</v>
+        <v>23985</v>
       </c>
       <c r="M688" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N688" s="3" t="inlineStr">
@@ -43590,18 +43590,18 @@
       </c>
       <c r="J689" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K689" s="5" t="n">
-        <v>6088320</v>
+        <v>7248000</v>
       </c>
       <c r="L689" s="5" t="n">
-        <v>19962</v>
+        <v>23764</v>
       </c>
       <c r="M689" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N689" s="3" t="inlineStr">
@@ -43652,18 +43652,18 @@
       </c>
       <c r="J690" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K690" s="5" t="n">
-        <v>6037920</v>
+        <v>7188000</v>
       </c>
       <c r="L690" s="5" t="n">
-        <v>19732</v>
+        <v>23490</v>
       </c>
       <c r="M690" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N690" s="3" t="inlineStr">
@@ -43784,18 +43784,18 @@
       </c>
       <c r="J692" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K692" s="5" t="n">
-        <v>6466320</v>
+        <v>7698000</v>
       </c>
       <c r="L692" s="5" t="n">
-        <v>20593</v>
+        <v>24516</v>
       </c>
       <c r="M692" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N692" s="3" t="inlineStr">
@@ -43846,18 +43846,18 @@
       </c>
       <c r="J693" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K693" s="5" t="n">
-        <v>6575310</v>
+        <v>7827750</v>
       </c>
       <c r="L693" s="5" t="n">
-        <v>21418</v>
+        <v>25498</v>
       </c>
       <c r="M693" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N693" s="3" t="inlineStr">
@@ -44180,18 +44180,18 @@
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K698" s="5" t="n">
-        <v>7919100</v>
+        <v>9427500</v>
       </c>
       <c r="L698" s="5" t="n">
-        <v>18417</v>
+        <v>21924</v>
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N698" s="3" t="inlineStr">
@@ -44242,18 +44242,18 @@
       </c>
       <c r="J699" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K699" s="5" t="n">
-        <v>5894910</v>
+        <v>7017750</v>
       </c>
       <c r="L699" s="5" t="n">
-        <v>19328</v>
+        <v>23009</v>
       </c>
       <c r="M699" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N699" s="3" t="inlineStr">
@@ -44304,18 +44304,18 @@
       </c>
       <c r="J700" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K700" s="5" t="n">
-        <v>5514390</v>
+        <v>6564750</v>
       </c>
       <c r="L700" s="5" t="n">
-        <v>17904</v>
+        <v>21314</v>
       </c>
       <c r="M700" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N700" s="3" t="inlineStr">
@@ -44366,18 +44366,18 @@
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K701" s="5" t="n">
-        <v>5454540</v>
+        <v>6493500</v>
       </c>
       <c r="L701" s="5" t="n">
-        <v>17884</v>
+        <v>21290</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N701" s="3" t="inlineStr">
@@ -44490,18 +44490,18 @@
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K703" s="5" t="n">
-        <v>7389900</v>
+        <v>8797500</v>
       </c>
       <c r="L703" s="5" t="n">
-        <v>16833</v>
+        <v>20040</v>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N703" s="3" t="inlineStr">
@@ -44552,18 +44552,18 @@
       </c>
       <c r="J704" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K704" s="5" t="n">
-        <v>6196680</v>
+        <v>7377000</v>
       </c>
       <c r="L704" s="5" t="n">
-        <v>19672</v>
+        <v>23419</v>
       </c>
       <c r="M704" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N704" s="3" t="inlineStr">
@@ -44614,18 +44614,18 @@
       </c>
       <c r="J705" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K705" s="5" t="n">
-        <v>6162030</v>
+        <v>7335750</v>
       </c>
       <c r="L705" s="5" t="n">
-        <v>20072</v>
+        <v>23895</v>
       </c>
       <c r="M705" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N705" s="3" t="inlineStr">
@@ -45002,18 +45002,18 @@
       </c>
       <c r="J711" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K711" s="5" t="n">
-        <v>5824980</v>
+        <v>6934500</v>
       </c>
       <c r="L711" s="5" t="n">
-        <v>19098</v>
+        <v>22736</v>
       </c>
       <c r="M711" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N711" s="3" t="inlineStr">
@@ -45064,18 +45064,18 @@
       </c>
       <c r="J712" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K712" s="5" t="n">
-        <v>5875380</v>
+        <v>6994500</v>
       </c>
       <c r="L712" s="5" t="n">
-        <v>19076</v>
+        <v>22709</v>
       </c>
       <c r="M712" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N712" s="3" t="inlineStr">
@@ -45126,18 +45126,18 @@
       </c>
       <c r="J713" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K713" s="5" t="n">
-        <v>5812380</v>
+        <v>6919500</v>
       </c>
       <c r="L713" s="5" t="n">
-        <v>19057</v>
+        <v>22687</v>
       </c>
       <c r="M713" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N713" s="3" t="inlineStr">
@@ -45320,18 +45320,18 @@
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K716" s="5" t="n">
-        <v>6589800</v>
+        <v>7845000</v>
       </c>
       <c r="L716" s="5" t="n">
-        <v>20920</v>
+        <v>24905</v>
       </c>
       <c r="M716" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N716" s="3" t="inlineStr">
@@ -45382,18 +45382,18 @@
       </c>
       <c r="J717" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K717" s="5" t="n">
-        <v>6454980</v>
+        <v>7684500</v>
       </c>
       <c r="L717" s="5" t="n">
-        <v>21026</v>
+        <v>25031</v>
       </c>
       <c r="M717" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N717" s="3" t="inlineStr">
@@ -45692,18 +45692,18 @@
       </c>
       <c r="J722" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K722" s="5" t="n">
-        <v>7759710</v>
+        <v>9237750</v>
       </c>
       <c r="L722" s="5" t="n">
-        <v>18046</v>
+        <v>21483</v>
       </c>
       <c r="M722" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N722" s="3" t="inlineStr">
@@ -45754,18 +45754,18 @@
       </c>
       <c r="J723" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K723" s="5" t="n">
-        <v>5767020</v>
+        <v>6865500</v>
       </c>
       <c r="L723" s="5" t="n">
-        <v>18908</v>
+        <v>22510</v>
       </c>
       <c r="M723" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N723" s="3" t="inlineStr">
@@ -45816,18 +45816,18 @@
       </c>
       <c r="J724" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K724" s="5" t="n">
-        <v>5403510</v>
+        <v>6432750</v>
       </c>
       <c r="L724" s="5" t="n">
-        <v>17544</v>
+        <v>20886</v>
       </c>
       <c r="M724" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N724" s="3" t="inlineStr">
@@ -45878,18 +45878,18 @@
       </c>
       <c r="J725" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K725" s="5" t="n">
-        <v>5352480</v>
+        <v>6372000</v>
       </c>
       <c r="L725" s="5" t="n">
-        <v>17549</v>
+        <v>20892</v>
       </c>
       <c r="M725" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N725" s="3" t="inlineStr">
@@ -46002,18 +46002,18 @@
       </c>
       <c r="J727" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K727" s="5" t="n">
-        <v>7091280</v>
+        <v>8442000</v>
       </c>
       <c r="L727" s="5" t="n">
-        <v>16153</v>
+        <v>19230</v>
       </c>
       <c r="M727" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N727" s="3" t="inlineStr">
@@ -46064,18 +46064,18 @@
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K728" s="5" t="n">
-        <v>6051150</v>
+        <v>7203750</v>
       </c>
       <c r="L728" s="5" t="n">
-        <v>19210</v>
+        <v>22869</v>
       </c>
       <c r="M728" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N728" s="3" t="inlineStr">
@@ -46126,18 +46126,18 @@
       </c>
       <c r="J729" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K729" s="5" t="n">
-        <v>6025950</v>
+        <v>7173750</v>
       </c>
       <c r="L729" s="5" t="n">
-        <v>19629</v>
+        <v>23367</v>
       </c>
       <c r="M729" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N729" s="3" t="inlineStr">
@@ -46522,18 +46522,18 @@
       </c>
       <c r="J735" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K735" s="5" t="n">
-        <v>5718510</v>
+        <v>6807750</v>
       </c>
       <c r="L735" s="5" t="n">
-        <v>18749</v>
+        <v>22320</v>
       </c>
       <c r="M735" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N735" s="3" t="inlineStr">
@@ -46584,18 +46584,18 @@
       </c>
       <c r="J736" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K736" s="5" t="n">
-        <v>5758830</v>
+        <v>6855750</v>
       </c>
       <c r="L736" s="5" t="n">
-        <v>18698</v>
+        <v>22259</v>
       </c>
       <c r="M736" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N736" s="3" t="inlineStr">
@@ -46646,18 +46646,18 @@
       </c>
       <c r="J737" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K737" s="5" t="n">
-        <v>5701500</v>
+        <v>6787500</v>
       </c>
       <c r="L737" s="5" t="n">
-        <v>18632</v>
+        <v>22181</v>
       </c>
       <c r="M737" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N737" s="3" t="inlineStr">
@@ -46832,18 +46832,18 @@
       </c>
       <c r="J740" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K740" s="5" t="n">
-        <v>6396390</v>
+        <v>7614750</v>
       </c>
       <c r="L740" s="5" t="n">
-        <v>20306</v>
+        <v>24174</v>
       </c>
       <c r="M740" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N740" s="3" t="inlineStr">
@@ -46894,18 +46894,18 @@
       </c>
       <c r="J741" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K741" s="5" t="n">
-        <v>6262200</v>
+        <v>7455000</v>
       </c>
       <c r="L741" s="5" t="n">
-        <v>20398</v>
+        <v>24283</v>
       </c>
       <c r="M741" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N741" s="3" t="inlineStr">
@@ -47212,18 +47212,18 @@
       </c>
       <c r="J746" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K746" s="5" t="n">
-        <v>7591500</v>
+        <v>9037500</v>
       </c>
       <c r="L746" s="5" t="n">
-        <v>17655</v>
+        <v>21017</v>
       </c>
       <c r="M746" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N746" s="3" t="inlineStr">
@@ -47274,18 +47274,18 @@
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K747" s="5" t="n">
-        <v>5651100</v>
+        <v>6727500</v>
       </c>
       <c r="L747" s="5" t="n">
-        <v>18528</v>
+        <v>22057</v>
       </c>
       <c r="M747" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N747" s="3" t="inlineStr">
@@ -47336,18 +47336,18 @@
       </c>
       <c r="J748" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K748" s="5" t="n">
-        <v>5300820</v>
+        <v>6310500</v>
       </c>
       <c r="L748" s="5" t="n">
-        <v>17210</v>
+        <v>20489</v>
       </c>
       <c r="M748" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N748" s="3" t="inlineStr">
@@ -47398,18 +47398,18 @@
       </c>
       <c r="J749" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K749" s="5" t="n">
-        <v>5241600</v>
+        <v>6240000</v>
       </c>
       <c r="L749" s="5" t="n">
-        <v>17186</v>
+        <v>20459</v>
       </c>
       <c r="M749" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N749" s="3" t="inlineStr">
@@ -47584,18 +47584,18 @@
       </c>
       <c r="J752" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K752" s="5" t="n">
-        <v>5923260</v>
+        <v>7051500</v>
       </c>
       <c r="L752" s="5" t="n">
-        <v>18804</v>
+        <v>22386</v>
       </c>
       <c r="M752" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N752" s="3" t="inlineStr">
@@ -47646,18 +47646,18 @@
       </c>
       <c r="J753" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K753" s="5" t="n">
-        <v>5889870</v>
+        <v>7011750</v>
       </c>
       <c r="L753" s="5" t="n">
-        <v>19185</v>
+        <v>22840</v>
       </c>
       <c r="M753" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N753" s="3" t="inlineStr">
@@ -48088,18 +48088,18 @@
       </c>
       <c r="J760" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K760" s="5" t="n">
-        <v>5642910</v>
+        <v>6717750</v>
       </c>
       <c r="L760" s="5" t="n">
-        <v>18321</v>
+        <v>21811</v>
       </c>
       <c r="M760" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N760" s="3" t="inlineStr">
@@ -48840,18 +48840,18 @@
       </c>
       <c r="J772" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K772" s="5" t="n">
-        <v>5189940</v>
+        <v>6178500</v>
       </c>
       <c r="L772" s="5" t="n">
-        <v>16850</v>
+        <v>20060</v>
       </c>
       <c r="M772" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>置佳時機120天即供付款計劃</t>
         </is>
       </c>
       <c r="N772" s="3" t="inlineStr">

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -51436,38 +51436,30 @@
       </c>
       <c r="F814" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G814" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H814" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I814" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H814" s="5" t="n">
+        <v>13080000</v>
+      </c>
+      <c r="I814" s="5" t="n">
+        <v>23739</v>
       </c>
       <c r="J814" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K814" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L814" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K814" s="5" t="n">
+        <v>13080000</v>
+      </c>
+      <c r="L814" s="5" t="n">
+        <v>23739</v>
       </c>
       <c r="M814" s="3" t="inlineStr">
         <is>
@@ -51476,7 +51468,7 @@
       </c>
       <c r="N814" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -62290,7 +62282,7 @@
         </is>
       </c>
       <c r="E989" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F989" s="3" t="inlineStr">
         <is>
@@ -62306,7 +62298,7 @@
         <v>5250000</v>
       </c>
       <c r="I989" s="5" t="n">
-        <v>17213</v>
+        <v>17157</v>
       </c>
       <c r="J989" s="3" t="inlineStr">
         <is>
@@ -62317,7 +62309,7 @@
         <v>5250000</v>
       </c>
       <c r="L989" s="5" t="n">
-        <v>17213</v>
+        <v>17157</v>
       </c>
       <c r="M989" s="3" t="inlineStr">
         <is>
@@ -70302,17 +70294,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -71651,12 +71643,12 @@
 (26年-01月-01日)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 551呎 (2房)
-招标单位
--
-(在售)</t>
+$1308万
+$23,739/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -73238,9 +73230,9 @@
       </c>
       <c r="I32" s="21" t="inlineStr">
         <is>
-          <t>H | 305呎 (1房)
+          <t>H | 306呎 (1房)
 $525万
-$17,213/呎
+$17,157/呎
 (25年-12月-02日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>4834000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>16785</v>
+        <v>16961</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>4834000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>16785</v>
+        <v>16961</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="K423" s="5" t="n">
@@ -44735,7 +44735,7 @@
       </c>
       <c r="G707" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H707" s="5" t="n">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="G708" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H708" s="5" t="n">
@@ -48072,34 +48072,34 @@
       </c>
       <c r="F760" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G760" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H760" s="5" t="n">
-        <v>8957000</v>
+        <v>6718000</v>
       </c>
       <c r="I760" s="5" t="n">
-        <v>29081</v>
+        <v>21812</v>
       </c>
       <c r="J760" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K760" s="5" t="n">
-        <v>6717750</v>
+        <v>6718000</v>
       </c>
       <c r="L760" s="5" t="n">
-        <v>21811</v>
+        <v>21812</v>
       </c>
       <c r="M760" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N760" s="3" t="inlineStr">
@@ -49510,7 +49510,7 @@
         </is>
       </c>
       <c r="E783" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F783" s="3" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>6288000</v>
       </c>
       <c r="I783" s="5" t="n">
-        <v>20616</v>
+        <v>20549</v>
       </c>
       <c r="J783" s="3" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>6288000</v>
       </c>
       <c r="L783" s="5" t="n">
-        <v>20616</v>
+        <v>20549</v>
       </c>
       <c r="M783" s="3" t="inlineStr">
         <is>
@@ -66366,9 +66366,9 @@
       </c>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t>N | 288呎 (1房)
+          <t>N | 285呎 (1房)
 $483万
-$16,785/呎
+$16,961/呎
 (24年-10月-02日)</t>
         </is>
       </c>
@@ -70294,7 +70294,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -70304,7 +70304,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -70705,7 +70705,7 @@
           <t>A | 508呎 (2房)
 $1321万
 $26,000/呎
-(26年-06月-25日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -70713,7 +70713,7 @@
           <t>B | 482呎 (2房)
 $1254万
 $26,008/呎
-(26年-06月-25日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -71279,12 +71279,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
-$896万
-$29,081/呎
-(在售)</t>
+$672万
+$21,812/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -71495,9 +71495,9 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>K | 305呎 (1房)
+          <t>K | 306呎 (1房)
 $629万
-$20,616/呎
+$20,549/呎
 (26年-03月-18日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>6455000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>20958</v>
+        <v>20890</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>6455000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>20958</v>
+        <v>20890</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
           <t>C | 498呎 (2房)
 $1172万
 $23,526/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -64474,7 +64474,7 @@
           <t>M | 481呎 (2房)
 $970万
 $20,166/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N5" s="22" t="inlineStr">
@@ -64585,7 +64585,7 @@
           <t>M | 481呎 (2房)
 $1107万
 $23,010/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -64608,7 +64608,7 @@
           <t>A | 774呎 (3房)
 $2144万
 $27,698/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -64616,7 +64616,7 @@
           <t>B | 536呎 (2房)
 $1233万
 $23,000/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -64696,7 +64696,7 @@
           <t>M | 481呎 (2房)
 $1059万
 $22,012/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="N7" s="22" t="inlineStr">
@@ -64727,7 +64727,7 @@
           <t>B | 536呎 (2房)
 $1150万
 $21,455/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -64743,7 +64743,7 @@
           <t>D | 534呎 (2房)
 $1271万
 $23,800/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -64759,7 +64759,7 @@
           <t>F | 427呎 (2房)
 $856万
 $20,059/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -64775,7 +64775,7 @@
           <t>H | 305呎 (1房)
 $635万
 $20,813/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -64791,7 +64791,7 @@
           <t>K | 309呎 (1房)
 $653万
 $21,126/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -64799,7 +64799,7 @@
           <t>L | 430呎 (2房)
 $809万
 $18,814/呎
-(25年-05月-25日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -64807,7 +64807,7 @@
           <t>M | 481呎 (2房)
 $1010万
 $20,998/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -64830,7 +64830,7 @@
           <t>A | 774呎 (3房)
 $2007万
 $25,928/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -64838,7 +64838,7 @@
           <t>B | 536呎 (2房)
 $1138万
 $21,231/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -64854,7 +64854,7 @@
           <t>D | 534呎 (2房)
 $1188万
 $22,238/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -64862,7 +64862,7 @@
           <t>E | 437呎 (2房)
 $958万
 $21,918/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -64870,7 +64870,7 @@
           <t>F | 427呎 (2房)
 $846万
 $19,822/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -64878,7 +64878,7 @@
           <t>G | 306呎 (1房)
 $676万
 $22,092/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -64886,7 +64886,7 @@
           <t>H | 306呎 (1房)
 $632万
 $20,647/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -64899,10 +64899,10 @@
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
-          <t>K | 308呎 (1房)
+          <t>K | 309呎 (1房)
 $646万
-$20,958/呎
-(26年-04月-07日)</t>
+$20,890/呎
+(26年-04月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -64910,7 +64910,7 @@
           <t>L | 430呎 (2房)
 $891万
 $20,726/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -64918,7 +64918,7 @@
           <t>M | 481呎 (2房)
 $1008万
 $20,967/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -64949,7 +64949,7 @@
           <t>B | 536呎 (2房)
 $1126万
 $21,000/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -64965,7 +64965,7 @@
           <t>D | 534呎 (2房)
 $1239万
 $23,199/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -64973,7 +64973,7 @@
           <t>E | 437呎 (2房)
 $999万
 $22,856/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -64981,7 +64981,7 @@
           <t>F | 427呎 (2房)
 $851万
 $19,925/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -64989,7 +64989,7 @@
           <t>G | 306呎 (1房)
 $670万
 $21,889/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -65005,7 +65005,7 @@
           <t>J | 306呎 (1房)
 $696万
 $22,732/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -65013,7 +65013,7 @@
           <t>K | 309呎 (1房)
 $615万
 $19,916/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -65021,7 +65021,7 @@
           <t>L | 430呎 (2房)
 $860万
 $20,000/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -65029,7 +65029,7 @@
           <t>M | 481呎 (2房)
 $990万
 $20,582/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -65037,7 +65037,7 @@
           <t>N | 285呎 (1房)
 $672万
 $23,579/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -65052,7 +65052,7 @@
           <t>A | 774呎 (3房)
 $1889万
 $24,403/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -65060,7 +65060,7 @@
           <t>B | 536呎 (2房)
 $1099万
 $20,500/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -65076,7 +65076,7 @@
           <t>D | 534呎 (2房)
 $1162万
 $21,753/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -65084,7 +65084,7 @@
           <t>E | 437呎 (2房)
 $909万
 $20,798/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -65092,7 +65092,7 @@
           <t>F | 427呎 (2房)
 $836万
 $19,590/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -65100,7 +65100,7 @@
           <t>G | 306呎 (1房)
 $664万
 $21,693/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -65108,7 +65108,7 @@
           <t>H | 306呎 (1房)
 $627万
 $20,484/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -65116,7 +65116,7 @@
           <t>J | 306呎 (1房)
 $689万
 $22,516/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -65124,7 +65124,7 @@
           <t>K | 309呎 (1房)
 $613万
 $19,848/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -65132,7 +65132,7 @@
           <t>L | 430呎 (2房)
 $890万
 $20,695/呎
-(24年-06月-23日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -65140,7 +65140,7 @@
           <t>M | 481呎 (2房)
 $1007万
 $20,933/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -65148,7 +65148,7 @@
           <t>N | 285呎 (1房)
 $679万
 $23,818/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -65163,7 +65163,7 @@
           <t>A | 771呎 (3房)
 $1748万
 $22,672/呎
-(25年-05月-15日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -65171,7 +65171,7 @@
           <t>B | 536呎 (2房)
 $1085万
 $20,235/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -65187,7 +65187,7 @@
           <t>D | 534呎 (2房)
 $1078万
 $20,185/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -65195,7 +65195,7 @@
           <t>E | 437呎 (2房)
 $864万
 $19,767/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -65203,7 +65203,7 @@
           <t>F | 427呎 (2房)
 $839万
 $19,644/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -65211,7 +65211,7 @@
           <t>G | 306呎 (1房)
 $658万
 $21,487/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -65219,7 +65219,7 @@
           <t>H | 306呎 (1房)
 $620万
 $20,261/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -65227,7 +65227,7 @@
           <t>J | 305呎 (1房)
 $550万
 $18,030/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -65235,7 +65235,7 @@
           <t>K | 308呎 (1房)
 $608万
 $19,756/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -65243,7 +65243,7 @@
           <t>L | 430呎 (2房)
 $792万
 $18,409/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -65251,7 +65251,7 @@
           <t>M | 481呎 (2房)
 $998万
 $20,753/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -65259,7 +65259,7 @@
           <t>N | 285呎 (1房)
 $672万
 $23,579/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -65274,7 +65274,7 @@
           <t>A | 771呎 (3房)
 $1760万
 $22,827/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -65282,7 +65282,7 @@
           <t>B | 536呎 (2房)
 $1080万
 $20,142/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -65298,7 +65298,7 @@
           <t>D | 534呎 (2房)
 $1087万
 $20,358/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -65306,7 +65306,7 @@
           <t>E | 437呎 (2房)
 $857万
 $19,616/呎
-(25年-05月-22日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -65314,7 +65314,7 @@
           <t>F | 427呎 (2房)
 $789万
 $18,485/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -65322,7 +65322,7 @@
           <t>G | 306呎 (1房)
 $651万
 $21,275/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -65330,7 +65330,7 @@
           <t>H | 306呎 (1房)
 $596万
 $19,471/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -65338,7 +65338,7 @@
           <t>J | 305呎 (1房)
 $546万
 $17,892/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -65346,7 +65346,7 @@
           <t>K | 308呎 (1房)
 $605万
 $19,653/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -65354,7 +65354,7 @@
           <t>L | 430呎 (2房)
 $876万
 $20,377/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -65362,7 +65362,7 @@
           <t>M | 481呎 (2房)
 $994万
 $20,674/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -65370,7 +65370,7 @@
           <t>N | 285呎 (1房)
 $631万
 $22,133/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -65385,7 +65385,7 @@
           <t>A | 774呎 (3房)
 $1807万
 $23,344/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -65393,7 +65393,7 @@
           <t>B | 536呎 (2房)
 $1060万
 $19,778/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -65409,7 +65409,7 @@
           <t>D | 534呎 (2房)
 $1114万
 $20,861/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -65417,7 +65417,7 @@
           <t>E | 437呎 (2房)
 $857万
 $19,606/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -65425,7 +65425,7 @@
           <t>F | 427呎 (2房)
 $778万
 $18,220/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -65433,7 +65433,7 @@
           <t>G | 306呎 (1房)
 $542万
 $17,703/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -65441,7 +65441,7 @@
           <t>H | 306呎 (1房)
 $592万
 $19,350/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -65449,7 +65449,7 @@
           <t>J | 305呎 (1房)
 $539万
 $17,685/呎
-(25年-03月-06日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -65457,7 +65457,7 @@
           <t>K | 308呎 (1房)
 $602万
 $19,549/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -65465,7 +65465,7 @@
           <t>L | 430呎 (2房)
 $875万
 $20,344/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -65473,7 +65473,7 @@
           <t>M | 481呎 (2房)
 $992万
 $20,626/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -65481,7 +65481,7 @@
           <t>N | 288呎 (1房)
 $553万
 $19,215/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -65496,7 +65496,7 @@
           <t>A | 774呎 (3房)
 $1755万
 $22,679/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -65504,7 +65504,7 @@
           <t>B | 536呎 (2房)
 $1060万
 $19,767/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -65520,7 +65520,7 @@
           <t>D | 534呎 (2房)
 $1054万
 $19,745/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -65528,7 +65528,7 @@
           <t>E | 437呎 (2房)
 $849万
 $19,437/呎
-(25年-03月-09日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -65536,7 +65536,7 @@
           <t>F | 427呎 (2房)
 $786万
 $18,412/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -65544,7 +65544,7 @@
           <t>G | 306呎 (1房)
 $540万
 $17,663/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -65552,7 +65552,7 @@
           <t>H | 305呎 (1房)
 $589万
 $19,302/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -65560,7 +65560,7 @@
           <t>J | 305呎 (1房)
 $540万
 $17,695/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -65568,7 +65568,7 @@
           <t>K | 309呎 (1房)
 $599万
 $19,382/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -65576,7 +65576,7 @@
           <t>L | 430呎 (2房)
 $873万
 $20,312/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -65584,7 +65584,7 @@
           <t>M | 481呎 (2房)
 $991万
 $20,595/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -65592,7 +65592,7 @@
           <t>N | 288呎 (1房)
 $552万
 $19,153/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -65607,7 +65607,7 @@
           <t>A | 774呎 (3房)
 $1967万
 $25,411/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -65615,7 +65615,7 @@
           <t>B | 536呎 (2房)
 $1068万
 $19,925/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -65631,7 +65631,7 @@
           <t>D | 534呎 (2房)
 $1096万
 $20,530/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -65639,7 +65639,7 @@
           <t>E | 437呎 (2房)
 $922万
 $21,094/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -65647,7 +65647,7 @@
           <t>F | 427呎 (2房)
 $777万
 $18,187/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -65655,7 +65655,7 @@
           <t>G | 306呎 (1房)
 $537万
 $17,562/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -65663,7 +65663,7 @@
           <t>H | 305呎 (1房)
 $585万
 $19,184/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -65671,7 +65671,7 @@
           <t>J | 305呎 (1房)
 $538万
 $17,639/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -65679,7 +65679,7 @@
           <t>K | 308呎 (1房)
 $595万
 $19,318/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -65687,7 +65687,7 @@
           <t>L | 430呎 (2房)
 $777万
 $18,063/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -65695,7 +65695,7 @@
           <t>M | 481呎 (2房)
 $989万
 $20,557/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -65703,7 +65703,7 @@
           <t>N | 285呎 (1房)
 $598万
 $20,989/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -65718,7 +65718,7 @@
           <t>A | 774呎 (3房)
 $1774万
 $22,917/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -65726,7 +65726,7 @@
           <t>B | 536呎 (2房)
 $1062万
 $19,817/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -65734,7 +65734,7 @@
           <t>C | 498呎 (2房)
 $1100万
 $22,092/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -65742,7 +65742,7 @@
           <t>D | 534呎 (2房)
 $1034万
 $19,354/呎
-(25年-01月-01日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -65750,7 +65750,7 @@
           <t>E | 437呎 (2房)
 $927万
 $21,215/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -65758,7 +65758,7 @@
           <t>F | 427呎 (2房)
 $769万
 $18,009/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -65766,7 +65766,7 @@
           <t>G | 306呎 (1房)
 $536万
 $17,529/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -65774,7 +65774,7 @@
           <t>H | 305呎 (1房)
 $584万
 $19,134/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -65782,7 +65782,7 @@
           <t>J | 305呎 (1房)
 $536万
 $17,584/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -65790,7 +65790,7 @@
           <t>K | 309呎 (1房)
 $592万
 $19,162/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -65798,7 +65798,7 @@
           <t>L | 430呎 (2房)
 $871万
 $20,253/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -65806,7 +65806,7 @@
           <t>M | 481呎 (2房)
 $978万
 $20,333/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -65814,7 +65814,7 @@
           <t>N | 285呎 (1房)
 $594万
 $20,853/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -65829,7 +65829,7 @@
           <t>A | 771呎 (3房)
 $1718万
 $22,283/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -65837,7 +65837,7 @@
           <t>B | 536呎 (2房)
 $1047万
 $19,530/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -65853,7 +65853,7 @@
           <t>D | 534呎 (2房)
 $1038万
 $19,436/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -65861,7 +65861,7 @@
           <t>E | 437呎 (2房)
 $838万
 $19,183/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -65869,7 +65869,7 @@
           <t>F | 427呎 (2房)
 $773万
 $18,103/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -65877,7 +65877,7 @@
           <t>G | 306呎 (1房)
 $637万
 $20,807/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -65885,7 +65885,7 @@
           <t>H | 305呎 (1房)
 $581万
 $19,036/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -65893,7 +65893,7 @@
           <t>J | 305呎 (1房)
 $537万
 $17,597/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -65901,7 +65901,7 @@
           <t>K | 308呎 (1房)
 $546万
 $17,724/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -65909,7 +65909,7 @@
           <t>L | 430呎 (2房)
 $869万
 $20,216/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -65917,7 +65917,7 @@
           <t>M | 481呎 (2房)
 $986万
 $20,491/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -65925,7 +65925,7 @@
           <t>N | 285呎 (1房)
 $549万
 $19,249/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -65940,7 +65940,7 @@
           <t>A | 774呎 (3房)
 $1851万
 $23,912/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -65948,7 +65948,7 @@
           <t>B | 536呎 (2房)
 $1050万
 $19,590/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -65964,7 +65964,7 @@
           <t>D | 534呎 (2房)
 $1027万
 $19,238/呎
-(25年-06月-02日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -65972,7 +65972,7 @@
           <t>E | 437呎 (2房)
 $915万
 $20,934/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -65980,7 +65980,7 @@
           <t>F | 427呎 (2房)
 $855万
 $20,014/呎
-(23年-11月-19日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -65988,7 +65988,7 @@
           <t>G | 306呎 (1房)
 $530万
 $17,324/呎
-(25年-02月-24日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -65996,7 +65996,7 @@
           <t>H | 305呎 (1房)
 $580万
 $19,003/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -66004,7 +66004,7 @@
           <t>J | 305呎 (1房)
 $532万
 $17,459/呎
-(25年-03月-11日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -66012,7 +66012,7 @@
           <t>K | 308呎 (1房)
 $590万
 $19,159/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -66020,7 +66020,7 @@
           <t>L | 430呎 (2房)
 $781万
 $18,172/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -66028,7 +66028,7 @@
           <t>M | 481呎 (2房)
 $984万
 $20,457/呎
-(23年-11月-26日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -66036,7 +66036,7 @@
           <t>N | 288呎 (1房)
 $549万
 $19,059/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -66051,7 +66051,7 @@
           <t>A | 774呎 (3房)
 $1888万
 $24,393/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -66059,7 +66059,7 @@
           <t>B | 536呎 (2房)
 $1063万
 $19,826/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -66075,7 +66075,7 @@
           <t>D | 534呎 (2房)
 $1027万
 $19,238/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -66083,7 +66083,7 @@
           <t>E | 437呎 (1房)
 $875万
 $20,018/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -66091,7 +66091,7 @@
           <t>F | 427呎 (2房)
 $855万
 $20,014/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -66099,7 +66099,7 @@
           <t>G | 306呎 (1房)
 $530万
 $17,324/呎
-(25年-03月-05日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -66107,7 +66107,7 @@
           <t>H | 305呎 (1房)
 $536万
 $17,561/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -66115,7 +66115,7 @@
           <t>J | 305呎 (1房)
 $534万
 $17,505/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -66123,7 +66123,7 @@
           <t>K | 308呎 (1房)
 $541万
 $17,562/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -66131,7 +66131,7 @@
           <t>L | 430呎 (2房)
 $779万
 $18,109/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -66139,7 +66139,7 @@
           <t>M | 481呎 (2房)
 $984万
 $20,457/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -66147,7 +66147,7 @@
           <t>N | 288呎 (1房)
 $589万
 $20,441/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -66162,7 +66162,7 @@
           <t>A | 771呎 (3房)
 $1650万
 $21,401/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -66170,7 +66170,7 @@
           <t>B | 536呎 (2房)
 $1025万
 $19,123/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -66178,7 +66178,7 @@
           <t>C | 497呎 (2房)
 $1143万
 $22,994/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -66186,7 +66186,7 @@
           <t>D | 534呎 (2房)
 $983万
 $18,416/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -66194,7 +66194,7 @@
           <t>E | 437呎 (2房)
 $829万
 $18,966/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -66202,7 +66202,7 @@
           <t>F | 427呎 (2房)
 $847万
 $19,845/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -66210,7 +66210,7 @@
           <t>G | 306呎 (1房)
 $506万
 $16,539/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -66218,7 +66218,7 @@
           <t>H | 305呎 (1房)
 $504万
 $16,511/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -66226,7 +66226,7 @@
           <t>J | 305呎 (1房)
 $528万
 $17,321/呎
-(25年-03月-16日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -66234,7 +66234,7 @@
           <t>K | 308呎 (1房)
 $520万
 $16,873/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -66242,7 +66242,7 @@
           <t>L | 430呎 (2房)
 $859万
 $19,984/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -66250,7 +66250,7 @@
           <t>M | 481呎 (2房)
 $977万
 $20,316/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -66258,7 +66258,7 @@
           <t>N | 288呎 (1房)
 $485万
 $16,847/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -66273,7 +66273,7 @@
           <t>A | 771呎 (3房)
 $1660万
 $21,530/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -66281,7 +66281,7 @@
           <t>B | 536呎 (2房)
 $1007万
 $18,795/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -66289,7 +66289,7 @@
           <t>C | 498呎 (2房)
 $1079万
 $21,663/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -66297,7 +66297,7 @@
           <t>D | 534呎 (2房)
 $978万
 $18,324/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -66305,7 +66305,7 @@
           <t>E | 437呎 (2房)
 $818万
 $18,709/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -66313,7 +66313,7 @@
           <t>F | 427呎 (2房)
 $846万
 $19,806/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -66321,7 +66321,7 @@
           <t>G | 306呎 (1房)
 $627万
 $20,497/呎
-(24年-07月-10日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -66329,7 +66329,7 @@
           <t>H | 305呎 (1房)
 $501万
 $16,430/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -66337,7 +66337,7 @@
           <t>J | 305呎 (1房)
 $525万
 $17,203/呎
-(25年-03月-03日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -66345,7 +66345,7 @@
           <t>K | 308呎 (1房)
 $517万
 $16,779/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -66353,7 +66353,7 @@
           <t>L | 430呎 (2房)
 $857万
 $19,928/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -66361,7 +66361,7 @@
           <t>M | 481呎 (2房)
 $973万
 $20,237/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -66369,7 +66369,7 @@
           <t>N | 285呎 (1房)
 $483万
 $16,961/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -66384,7 +66384,7 @@
           <t>A | 771呎 (3房)
 $1683万
 $21,829/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -66392,7 +66392,7 @@
           <t>B | 536呎 (2房)
 $1021万
 $19,050/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -66400,7 +66400,7 @@
           <t>C | 497呎 (2房)
 $1081万
 $21,746/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -66408,7 +66408,7 @@
           <t>D | 534呎 (2房)
 $976万
 $18,270/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -66416,7 +66416,7 @@
           <t>E | 437呎 (2房)
 $818万
 $18,725/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -66424,7 +66424,7 @@
           <t>F | 427呎 (2房)
 $844万
 $19,770/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -66432,7 +66432,7 @@
           <t>G | 306呎 (1房)
 $503万
 $16,428/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -66440,7 +66440,7 @@
           <t>H | 305呎 (1房)
 $504万
 $16,531/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -66448,7 +66448,7 @@
           <t>J | 305呎 (1房)
 $525万
 $17,223/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -66456,7 +66456,7 @@
           <t>K | 308呎 (1房)
 $516万
 $16,747/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -66464,7 +66464,7 @@
           <t>L | 430呎 (2房)
 $855万
 $19,888/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -66472,7 +66472,7 @@
           <t>M | 481呎 (2房)
 $971万
 $20,191/呎
-(23年-11月-20日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -66480,7 +66480,7 @@
           <t>N | 288呎 (1房)
 $492万
 $17,066/呎
-(24年-10月-16日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -66495,7 +66495,7 @@
           <t>A | 771呎 (3房)
 $1626万
 $21,089/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -66503,7 +66503,7 @@
           <t>B | 536呎 (2房)
 $997万
 $18,601/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -66519,7 +66519,7 @@
           <t>D | 534呎 (2房)
 $980万
 $18,350/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -66527,7 +66527,7 @@
           <t>E | 437呎 (2房)
 $806万
 $18,449/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -66535,7 +66535,7 @@
           <t>F | 427呎 (2房)
 $842万
 $19,721/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -66543,7 +66543,7 @@
           <t>G | 306呎 (1房)
 $502万
 $16,399/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -66551,7 +66551,7 @@
           <t>H | 305呎 (1房)
 $499万
 $16,367/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -66559,7 +66559,7 @@
           <t>J | 305呎 (1房)
 $522万
 $17,108/呎
-(25年-03月-05日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -66567,7 +66567,7 @@
           <t>K | 308呎 (1房)
 $515万
 $16,708/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -66575,7 +66575,7 @@
           <t>L | 430呎 (2房)
 $853万
 $19,847/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -66583,7 +66583,7 @@
           <t>M | 481呎 (2房)
 $969万
 $20,150/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -66591,7 +66591,7 @@
           <t>N | 288呎 (1房)
 $490万
 $17,017/呎
-(24年-10月-16日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
           <t>A | 774呎 (3房)
 $1759万
 $22,724/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -66614,7 +66614,7 @@
           <t>B | 536呎 (2房)
 $1001万
 $18,679/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -66622,7 +66622,7 @@
           <t>C | 497呎 (2房)
 $1071万
 $21,545/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -66630,7 +66630,7 @@
           <t>D | 534呎 (2房)
 $970万
 $18,161/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -66638,7 +66638,7 @@
           <t>E | 437呎 (2房)
 $799万
 $18,293/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -66646,7 +66646,7 @@
           <t>F | 427呎 (2房)
 $840万
 $19,660/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -66654,7 +66654,7 @@
           <t>G | 306呎 (1房)
 $501万
 $16,366/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -66662,7 +66662,7 @@
           <t>H | 305呎 (1房)
 $498万
 $16,331/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -66670,7 +66670,7 @@
           <t>J | 306呎 (1房)
 $524万
 $17,131/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -66678,7 +66678,7 @@
           <t>K | 308呎 (1房)
 $514万
 $16,675/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -66686,7 +66686,7 @@
           <t>L | 430呎 (2房)
 $852万
 $19,805/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -66694,7 +66694,7 @@
           <t>M | 481呎 (2房)
 $967万
 $20,108/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -66702,7 +66702,7 @@
           <t>N | 288呎 (1房)
 $479万
 $16,628/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -66717,7 +66717,7 @@
           <t>A | 771呎 (3房)
 $1650万
 $21,401/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -66725,7 +66725,7 @@
           <t>B | 536呎 (2房)
 $991万
 $18,494/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -66733,7 +66733,7 @@
           <t>C | 498呎 (2房)
 $996万
 $20,000/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -66741,7 +66741,7 @@
           <t>D | 534呎 (2房)
 $967万
 $18,110/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -66749,7 +66749,7 @@
           <t>E | 437呎 (2房)
 $800万
 $18,311/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -66757,7 +66757,7 @@
           <t>F | 427呎 (2房)
 $837万
 $19,597/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -66765,7 +66765,7 @@
           <t>G | 306呎 (1房)
 $500万
 $16,330/呎
-(24年-10月-09日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -66773,7 +66773,7 @@
           <t>H | 305呎 (1房)
 $497万
 $16,298/呎
-(24年-10月-21日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -66781,7 +66781,7 @@
           <t>J | 305呎 (1房)
 $519万
 $17,010/呎
-(25年-03月-04日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -66789,7 +66789,7 @@
           <t>K | 308呎 (1房)
 $641万
 $20,805/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -66797,7 +66797,7 @@
           <t>L | 430呎 (2房)
 $850万
 $19,767/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -66805,7 +66805,7 @@
           <t>M | 481呎 (2房)
 $965万
 $20,067/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -66813,7 +66813,7 @@
           <t>N | 288呎 (1房)
 $477万
 $16,576/呎
-(24年-09月-23日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -66828,7 +66828,7 @@
           <t>A | 774呎 (3房)
 $1697万
 $21,922/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -66836,7 +66836,7 @@
           <t>B | 536呎 (2房)
 $1002万
 $18,700/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -66844,7 +66844,7 @@
           <t>C | 498呎 (2房)
 $997万
 $20,016/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -66852,7 +66852,7 @@
           <t>D | 534呎 (2房)
 $964万
 $18,058/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -66860,7 +66860,7 @@
           <t>E | 437呎 (2房)
 $796万
 $18,217/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -66868,7 +66868,7 @@
           <t>F | 427呎 (2房)
 $835万
 $19,560/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -66876,7 +66876,7 @@
           <t>G | 306呎 (1房)
 $499万
 $16,310/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -66884,7 +66884,7 @@
           <t>H | 305呎 (1房)
 $500万
 $16,393/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -66892,7 +66892,7 @@
           <t>J | 305呎 (1房)
 $519万
 $17,026/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -66900,7 +66900,7 @@
           <t>K | 308呎 (1房)
 $512万
 $16,607/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -66908,7 +66908,7 @@
           <t>L | 429呎 (2房)
 $861万
 $20,065/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -66916,7 +66916,7 @@
           <t>M | 481呎 (2房)
 $963万
 $20,025/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -66924,7 +66924,7 @@
           <t>N | 285呎 (1房)
 $476万
 $16,702/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -66939,7 +66939,7 @@
           <t>A | 771呎 (3房)
 $1666万
 $21,606/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -66947,7 +66947,7 @@
           <t>B | 536呎 (2房)
 $988万
 $18,437/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -66955,7 +66955,7 @@
           <t>C | 497呎 (2房)
 $1001万
 $20,137/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -66963,7 +66963,7 @@
           <t>D | 534呎 (2房)
 $964万
 $18,058/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -66971,7 +66971,7 @@
           <t>E | 437呎 (2房)
 $819万
 $18,746/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -66979,7 +66979,7 @@
           <t>F | 427呎 (2房)
 $835万
 $19,560/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -66987,7 +66987,7 @@
           <t>G | 306呎 (1房)
 $621万
 $20,307/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -66995,7 +66995,7 @@
           <t>H | 305呎 (1房)
 $500万
 $16,393/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -67003,7 +67003,7 @@
           <t>J | 306呎 (1房)
 $592万
 $19,337/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -67011,7 +67011,7 @@
           <t>K | 308呎 (1房)
 $512万
 $16,607/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -67019,7 +67019,7 @@
           <t>L | 430呎 (2房)
 $848万
 $19,721/呎
-(23年-11月-19日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -67027,7 +67027,7 @@
           <t>M | 481呎 (2房)
 $963万
 $20,025/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -67035,7 +67035,7 @@
           <t>N | 288呎 (1房)
 $486万
 $16,865/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -67050,7 +67050,7 @@
           <t>A | 771呎 (3房)
 $1681万
 $21,800/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -67058,7 +67058,7 @@
           <t>B | 536呎 (2房)
 $993万
 $18,522/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -67066,7 +67066,7 @@
           <t>C | 498呎 (2房)
 $981万
 $19,701/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -67074,7 +67074,7 @@
           <t>D | 534呎 (2房)
 $954万
 $17,875/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -67082,7 +67082,7 @@
           <t>E | 437呎 (2房)
 $797万
 $18,231/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -67090,7 +67090,7 @@
           <t>F | 427呎 (2房)
 $829万
 $19,412/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -67098,7 +67098,7 @@
           <t>G | 306呎 (1房)
 $496万
 $16,199/呎
-(24年-10月-08日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -67106,7 +67106,7 @@
           <t>H | 305呎 (1房)
 $493万
 $16,161/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -67114,7 +67114,7 @@
           <t>J | 305呎 (1房)
 $514万
 $16,846/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -67122,7 +67122,7 @@
           <t>K | 308呎 (1房)
 $508万
 $16,484/呎
-(25年-01月-09日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -67130,7 +67130,7 @@
           <t>L | 430呎 (2房)
 $844万
 $19,619/呎
-(23年-11月-22日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -67138,7 +67138,7 @@
           <t>M | 481呎 (2房)
 $868万
 $18,037/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -67146,7 +67146,7 @@
           <t>N | 288呎 (1房)
 $472万
 $16,392/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -67161,7 +67161,7 @@
           <t>A | 774呎 (3房)
 $1661万
 $21,460/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -67169,7 +67169,7 @@
           <t>B | 536呎 (2房)
 $980万
 $18,282/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -67177,7 +67177,7 @@
           <t>C | 498呎 (2房)
 $976万
 $19,606/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -67185,7 +67185,7 @@
           <t>D | 534呎 (2房)
 $948万
 $17,760/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -67193,7 +67193,7 @@
           <t>E | 437呎 (2房)
 $792万
 $18,114/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -67201,7 +67201,7 @@
           <t>F | 427呎 (2房)
 $790万
 $18,501/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -67209,7 +67209,7 @@
           <t>G | 306呎 (1房)
 $494万
 $16,134/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -67217,7 +67217,7 @@
           <t>H | 305呎 (1房)
 $491万
 $16,089/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -67225,7 +67225,7 @@
           <t>J | 305呎 (1房)
 $516万
 $16,925/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -67233,7 +67233,7 @@
           <t>K | 308呎 (1房)
 $506万
 $16,425/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -67241,7 +67241,7 @@
           <t>L | 430呎 (2房)
 $842万
 $19,572/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -67249,7 +67249,7 @@
           <t>M | 481呎 (2房)
 $956万
 $19,865/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -67257,7 +67257,7 @@
           <t>N | 288呎 (1房)
 $471万
 $16,365/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -67272,7 +67272,7 @@
           <t>A | 771呎 (3房)
 $1608万
 $20,856/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -67280,7 +67280,7 @@
           <t>B | 536呎 (2房)
 $992万
 $18,498/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -67288,7 +67288,7 @@
           <t>C | 497呎 (2房)
 $999万
 $20,097/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -67296,7 +67296,7 @@
           <t>D | 534呎 (2房)
 $954万
 $17,873/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -67304,7 +67304,7 @@
           <t>E | 437呎 (2房)
 $797万
 $18,243/呎
-(25年-05月-28日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -67312,7 +67312,7 @@
           <t>F | 427呎 (2房)
 $726万
 $16,998/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -67320,7 +67320,7 @@
           <t>G | 306呎 (1房)
 $498万
 $16,258/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -67328,7 +67328,7 @@
           <t>H | 305呎 (1房)
 $493万
 $16,167/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -67336,7 +67336,7 @@
           <t>J | 305呎 (1房)
 $520万
 $17,049/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -67344,7 +67344,7 @@
           <t>K | 308呎 (1房)
 $505万
 $16,390/呎
-(25年-01月-02日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -67352,7 +67352,7 @@
           <t>L | 430呎 (2房)
 $746万
 $17,351/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -67360,7 +67360,7 @@
           <t>M | 481呎 (2房)
 $846万
 $17,593/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -67368,7 +67368,7 @@
           <t>N | 288呎 (1房)
 $479万
 $16,628/呎
-(24年-10月-21日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -67383,7 +67383,7 @@
           <t>A | 774呎 (3房)
 $1660万
 $21,444/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -67391,7 +67391,7 @@
           <t>B | 536呎 (2房)
 $978万
 $18,241/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -67399,7 +67399,7 @@
           <t>C | 497呎 (2房)
 $974万
 $19,594/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -67407,7 +67407,7 @@
           <t>D | 534呎 (2房)
 $939万
 $17,590/呎
-(25年-02月-25日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -67415,7 +67415,7 @@
           <t>E | 437呎 (2房)
 $787万
 $18,011/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -67423,7 +67423,7 @@
           <t>F | 427呎 (2房)
 $822万
 $19,251/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -67431,7 +67431,7 @@
           <t>G | 306呎 (1房)
 $490万
 $16,007/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -67439,7 +67439,7 @@
           <t>H | 305呎 (1房)
 $488万
 $16,003/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -67447,7 +67447,7 @@
           <t>J | 305呎 (1房)
 $509万
 $16,682/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -67455,7 +67455,7 @@
           <t>K | 308呎 (1房)
 $502万
 $16,299/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -67463,7 +67463,7 @@
           <t>L | 430呎 (2房)
 $839万
 $19,507/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -67471,7 +67471,7 @@
           <t>M | 481呎 (2房)
 $836万
 $17,380/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -67479,7 +67479,7 @@
           <t>N | 285呎 (1房)
 $467万
 $16,400/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -67494,7 +67494,7 @@
           <t>A | 774呎 (3房)
 $1681万
 $21,716/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -67502,7 +67502,7 @@
           <t>B | 536呎 (2房)
 $983万
 $18,343/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -67510,7 +67510,7 @@
           <t>C | 497呎 (2房)
 $985万
 $19,815/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -67518,7 +67518,7 @@
           <t>D | 534呎 (2房)
 $983万
 $18,404/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -67526,7 +67526,7 @@
           <t>E | 437呎 (2房)
 $788万
 $18,043/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -67534,7 +67534,7 @@
           <t>F | 427呎 (2房)
 $714万
 $16,733/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -67542,7 +67542,7 @@
           <t>G | 306呎 (1房)
 $488万
 $15,941/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -67550,7 +67550,7 @@
           <t>H | 305呎 (1房)
 $523万
 $17,148/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -67558,7 +67558,7 @@
           <t>J | 305呎 (1房)
 $510万
 $16,738/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -67566,7 +67566,7 @@
           <t>K | 308呎 (1房)
 $499万
 $16,205/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -67574,7 +67574,7 @@
           <t>L | 430呎 (2房)
 $837万
 $19,458/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -67582,7 +67582,7 @@
           <t>M | 481呎 (2房)
 $835万
 $17,356/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N33" s="21" t="inlineStr">
@@ -67590,7 +67590,7 @@
           <t>N | 288呎 (1房)
 $465万
 $16,153/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -67605,7 +67605,7 @@
           <t>A | 771呎 (3房)
 $1681万
 $21,800/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -67613,7 +67613,7 @@
           <t>B | 536呎 (2房)
 $978万
 $18,239/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -67621,7 +67621,7 @@
           <t>C | 497呎 (2房)
 $978万
 $19,674/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -67629,7 +67629,7 @@
           <t>D | 534呎 (2房)
 $994万
 $18,609/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -67637,7 +67637,7 @@
           <t>E | 437呎 (2房)
 $787万
 $18,014/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -67645,7 +67645,7 @@
           <t>F | 427呎 (2房)
 $711万
 $16,656/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -67653,7 +67653,7 @@
           <t>G | 306呎 (1房)
 $487万
 $15,928/呎
-(25年-01月-05日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -67661,7 +67661,7 @@
           <t>H | 305呎 (1房)
 $520万
 $17,059/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
@@ -67669,7 +67669,7 @@
           <t>J | 305呎 (1房)
 $534万
 $17,492/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -67677,7 +67677,7 @@
           <t>K | 308呎 (1房)
 $503万
 $16,328/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -67685,7 +67685,7 @@
           <t>L | 430呎 (2房)
 $729万
 $16,949/呎
-(25年-04月-13日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -67693,7 +67693,7 @@
           <t>M | 481呎 (2房)
 $831万
 $17,285/呎
-(25年-01月-22日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="N34" s="21" t="inlineStr">
@@ -67701,7 +67701,7 @@
           <t>N | 288呎 (1房)
 $461万
 $15,997/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -67893,7 +67893,7 @@
           <t>D | 477呎 (2房)
 $1289万
 $27,019/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -67901,7 +67901,7 @@
           <t>E | 553呎 (2房)
 $1289万
 $23,315/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -67948,7 +67948,7 @@
           <t>A | 586呎 (3房)
 $1429万
 $24,389/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -68012,7 +68012,7 @@
           <t>J | 537呎 (2房)
 $1454万
 $27,073/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -68027,7 +68027,7 @@
           <t>A | 586呎 (3房)
 $1465万
 $25,000/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -68059,7 +68059,7 @@
           <t>E | 553呎 (2房)
 $1278万
 $23,105/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -68091,7 +68091,7 @@
           <t>J | 538呎 (2房)
 $1250万
 $23,234/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -68106,7 +68106,7 @@
           <t>A | 586呎 (3房)
 $1432万
 $24,437/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -68114,7 +68114,7 @@
           <t>B | 474呎 (2房)
 $1064万
 $22,443/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -68122,7 +68122,7 @@
           <t>C | 450呎 (2房)
 $999万
 $22,196/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -68138,7 +68138,7 @@
           <t>E | 553呎 (2房)
 $1208万
 $21,852/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -68154,7 +68154,7 @@
           <t>G | 432呎 (2房)
 $823万
 $19,051/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -68162,7 +68162,7 @@
           <t>H | 432呎 (2房)
 $812万
 $18,789/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -68170,7 +68170,7 @@
           <t>J | 538呎 (2房)
 $1148万
 $21,338/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -68185,7 +68185,7 @@
           <t>A | 586呎 (3房)
 $1407万
 $24,007/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -68193,7 +68193,7 @@
           <t>B | 474呎 (2房)
 $993万
 $20,947/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -68201,7 +68201,7 @@
           <t>C | 450呎 (2房)
 $993万
 $22,062/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -68217,7 +68217,7 @@
           <t>E | 553呎 (2房)
 $1229万
 $22,221/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -68225,7 +68225,7 @@
           <t>F | 307呎 (1房)
 $634万
 $20,645/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -68233,7 +68233,7 @@
           <t>G | 432呎 (2房)
 $788万
 $18,243/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -68241,7 +68241,7 @@
           <t>H | 432呎 (2房)
 $807万
 $18,688/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -68249,7 +68249,7 @@
           <t>J | 538呎 (2房)
 $1130万
 $21,000/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -68264,7 +68264,7 @@
           <t>A | 586呎 (3房)
 $1408万
 $24,027/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -68272,7 +68272,7 @@
           <t>B | 474呎 (2房)
 $988万
 $20,842/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -68296,7 +68296,7 @@
           <t>E | 553呎 (2房)
 $1201万
 $21,723/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -68304,7 +68304,7 @@
           <t>F | 307呎 (1房)
 $631万
 $20,547/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -68312,7 +68312,7 @@
           <t>G | 432呎 (2房)
 $811万
 $18,778/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -68320,7 +68320,7 @@
           <t>H | 432呎 (2房)
 $806万
 $18,653/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -68328,7 +68328,7 @@
           <t>J | 538呎 (2房)
 $1128万
 $20,967/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -68343,7 +68343,7 @@
           <t>A | 586呎 (3房)
 $1348万
 $23,003/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -68351,7 +68351,7 @@
           <t>B | 474呎 (2房)
 $960万
 $20,245/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -68359,7 +68359,7 @@
           <t>C | 450呎 (2房)
 $987万
 $21,929/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -68375,7 +68375,7 @@
           <t>E | 553呎 (2房)
 $1244万
 $22,503/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -68383,7 +68383,7 @@
           <t>F | 307呎 (1房)
 $626万
 $20,375/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -68391,7 +68391,7 @@
           <t>G | 432呎 (2房)
 $770万
 $17,824/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -68399,7 +68399,7 @@
           <t>H | 432呎 (2房)
 $803万
 $18,590/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -68407,7 +68407,7 @@
           <t>J | 538呎 (2房)
 $1087万
 $20,201/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68422,7 +68422,7 @@
           <t>A | 586呎 (3房)
 $1298万
 $22,150/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -68430,7 +68430,7 @@
           <t>B | 474呎 (2房)
 $955万
 $20,141/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -68438,7 +68438,7 @@
           <t>C | 450呎 (2房)
 $977万
 $21,707/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -68454,7 +68454,7 @@
           <t>E | 553呎 (2房)
 $1234万
 $22,311/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -68462,7 +68462,7 @@
           <t>F | 307呎 (1房)
 $646万
 $21,026/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -68470,7 +68470,7 @@
           <t>G | 432呎 (2房)
 $760万
 $17,583/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -68478,7 +68478,7 @@
           <t>H | 431呎 (2房)
 $757万
 $17,568/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -68486,7 +68486,7 @@
           <t>J | 537呎 (2房)
 $1060万
 $19,739/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -68501,7 +68501,7 @@
           <t>A | 586呎 (3房)
 $1293万
 $22,070/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -68509,7 +68509,7 @@
           <t>B | 474呎 (2房)
 $978万
 $20,627/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -68517,7 +68517,7 @@
           <t>C | 450呎 (2房)
 $917万
 $20,373/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -68533,7 +68533,7 @@
           <t>E | 553呎 (2房)
 $1221万
 $22,083/呎
-(24年-08月-12日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -68541,7 +68541,7 @@
           <t>F | 307呎 (1房)
 $618万
 $20,124/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -68549,7 +68549,7 @@
           <t>G | 432呎 (2房)
 $778万
 $18,007/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -68557,7 +68557,7 @@
           <t>H | 431呎 (2房)
 $759万
 $17,615/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -68565,7 +68565,7 @@
           <t>J | 538呎 (2房)
 $1052万
 $19,548/呎
-(25年-03月-09日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68580,7 +68580,7 @@
           <t>A | 586呎 (3房)
 $1293万
 $22,058/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -68588,7 +68588,7 @@
           <t>B | 474呎 (2房)
 $938万
 $19,781/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -68596,7 +68596,7 @@
           <t>C | 450呎 (2房)
 $914万
 $20,318/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -68612,7 +68612,7 @@
           <t>E | 553呎 (2房)
 $1175万
 $21,248/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -68620,7 +68620,7 @@
           <t>F | 307呎 (1房)
 $602万
 $19,603/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -68628,7 +68628,7 @@
           <t>G | 432呎 (2房)
 $755万
 $17,468/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -68636,7 +68636,7 @@
           <t>H | 431呎 (2房)
 $760万
 $17,643/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -68644,7 +68644,7 @@
           <t>J | 538呎 (2房)
 $1067万
 $19,840/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68659,7 +68659,7 @@
           <t>A | 586呎 (3房)
 $1299万
 $22,162/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -68667,7 +68667,7 @@
           <t>B | 474呎 (2房)
 $956万
 $20,169/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -68675,7 +68675,7 @@
           <t>C | 450呎 (2房)
 $912万
 $20,256/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -68683,7 +68683,7 @@
           <t>D | 477呎 (2房)
 $1054万
 $22,092/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -68691,7 +68691,7 @@
           <t>E | 553呎 (2房)
 $1176万
 $21,266/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -68699,7 +68699,7 @@
           <t>F | 307呎 (1房)
 $588万
 $19,150/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -68707,7 +68707,7 @@
           <t>G | 432呎 (2房)
 $753万
 $17,431/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -68715,7 +68715,7 @@
           <t>H | 431呎 (2房)
 $786万
 $18,230/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -68723,7 +68723,7 @@
           <t>J | 538呎 (2房)
 $1049万
 $19,498/呎
-(25年-03月-16日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68738,7 +68738,7 @@
           <t>A | 586呎 (3房)
 $1276万
 $21,776/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -68746,7 +68746,7 @@
           <t>B | 474呎 (2房)
 $952万
 $20,093/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -68754,7 +68754,7 @@
           <t>C | 450呎 (2房)
 $909万
 $20,200/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -68762,7 +68762,7 @@
           <t>D | 477呎 (2房)
 $1048万
 $21,966/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -68770,7 +68770,7 @@
           <t>E | 553呎 (2房)
 $1210万
 $21,888/呎
-(23年-11月-19日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -68778,7 +68778,7 @@
           <t>F | 307呎 (1房)
 $585万
 $19,046/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -68786,7 +68786,7 @@
           <t>G | 432呎 (2房)
 $752万
 $17,396/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -68794,7 +68794,7 @@
           <t>H | 431呎 (2房)
 $749万
 $17,387/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -68802,7 +68802,7 @@
           <t>J | 538呎 (2房)
 $1061万
 $19,723/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68817,7 +68817,7 @@
           <t>A | 586呎 (3房)
 $1508万
 $25,741/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -68825,7 +68825,7 @@
           <t>B | 474呎 (2房)
 $926万
 $19,540/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -68833,7 +68833,7 @@
           <t>C | 450呎 (2房)
 $906万
 $20,144/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -68849,7 +68849,7 @@
           <t>E | 553呎 (2房)
 $1207万
 $21,823/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -68857,7 +68857,7 @@
           <t>F | 307呎 (1房)
 $605万
 $19,710/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -68865,7 +68865,7 @@
           <t>G | 432呎 (2房)
 $750万
 $17,361/呎
-(25年-05月-25日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -68873,7 +68873,7 @@
           <t>H | 431呎 (2房)
 $785万
 $18,216/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -68881,7 +68881,7 @@
           <t>J | 538呎 (2房)
 $1036万
 $19,247/呎
-(25年-03月-06日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68896,7 +68896,7 @@
           <t>A | 586呎 (3房)
 $1279万
 $21,821/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -68904,7 +68904,7 @@
           <t>B | 474呎 (2房)
 $927万
 $19,553/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -68912,7 +68912,7 @@
           <t>C | 450呎 (2房)
 $904万
 $20,087/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -68928,7 +68928,7 @@
           <t>E | 553呎 (2房)
 $1203万
 $21,758/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -68936,7 +68936,7 @@
           <t>F | 307呎 (1房)
 $602万
 $19,612/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -68944,7 +68944,7 @@
           <t>G | 432呎 (2房)
 $746万
 $17,269/呎
-(25年-01月-16日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -68952,7 +68952,7 @@
           <t>H | 432呎 (2房)
 $781万
 $18,076/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -68960,7 +68960,7 @@
           <t>J | 538呎 (2房)
 $1055万
 $19,602/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -68975,7 +68975,7 @@
           <t>A | 586呎 (3房)
 $1280万
 $21,838/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -68983,7 +68983,7 @@
           <t>B | 474呎 (2房)
 $914万
 $19,287/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -68991,7 +68991,7 @@
           <t>C | 450呎 (2房)
 $901万
 $20,027/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -69007,7 +69007,7 @@
           <t>E | 553呎 (2房)
 $1151万
 $20,812/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -69015,7 +69015,7 @@
           <t>F | 307呎 (1房)
 $599万
 $19,508/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -69023,7 +69023,7 @@
           <t>G | 432呎 (2房)
 $747万
 $17,292/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -69031,7 +69031,7 @@
           <t>H | 431呎 (2房)
 $750万
 $17,408/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -69039,7 +69039,7 @@
           <t>J | 538呎 (2房)
 $1026万
 $19,061/呎
-(25年-03月-06日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -69054,7 +69054,7 @@
           <t>A | 586呎 (3房)
 $1290万
 $22,014/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -69062,7 +69062,7 @@
           <t>B | 474呎 (2房)
 $918万
 $19,357/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -69070,7 +69070,7 @@
           <t>C | 450呎 (2房)
 $898万
 $19,958/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -69086,7 +69086,7 @@
           <t>E | 553呎 (2房)
 $1162万
 $21,016/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -69094,7 +69094,7 @@
           <t>F | 307呎 (1房)
 $597万
 $19,446/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -69102,7 +69102,7 @@
           <t>G | 432呎 (2房)
 $739万
 $17,106/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -69110,7 +69110,7 @@
           <t>H | 432呎 (2房)
 $777万
 $17,981/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -69118,7 +69118,7 @@
           <t>J | 538呎 (2房)
 $1026万
 $19,061/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -69133,7 +69133,7 @@
           <t>A | 586呎 (3房)
 $1359万
 $23,188/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -69141,7 +69141,7 @@
           <t>B | 474呎 (2房)
 $880万
 $18,557/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -69149,7 +69149,7 @@
           <t>C | 450呎 (2房)
 $862万
 $19,164/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -69157,7 +69157,7 @@
           <t>D | 477呎 (2房)
 $1019万
 $21,358/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -69165,7 +69165,7 @@
           <t>E | 553呎 (2房)
 $1187万
 $21,463/呎
-(23年-11月-26日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -69173,7 +69173,7 @@
           <t>F | 307呎 (1房)
 $512万
 $16,681/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -69181,7 +69181,7 @@
           <t>G | 432呎 (2房)
 $707万
 $16,370/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -69189,7 +69189,7 @@
           <t>H | 431呎 (2房)
 $730万
 $16,926/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -69197,7 +69197,7 @@
           <t>J | 538呎 (2房)
 $982万
 $18,249/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -69212,7 +69212,7 @@
           <t>A | 586呎 (3房)
 $1478万
 $25,217/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -69220,7 +69220,7 @@
           <t>B | 474呎 (2房)
 $875万
 $18,466/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -69228,7 +69228,7 @@
           <t>C | 450呎 (2房)
 $974万
 $21,651/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -69236,7 +69236,7 @@
           <t>D | 477呎 (2房)
 $961万
 $20,143/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -69244,7 +69244,7 @@
           <t>E | 553呎 (2房)
 $1181万
 $21,353/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -69252,7 +69252,7 @@
           <t>F | 307呎 (1房)
 $616万
 $20,072/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -69260,7 +69260,7 @@
           <t>G | 432呎 (2房)
 $706万
 $16,338/呎
-(24年-10月-07日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -69268,7 +69268,7 @@
           <t>H | 431呎 (2房)
 $728万
 $16,891/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -69276,7 +69276,7 @@
           <t>J | 538呎 (2房)
 $976万
 $18,147/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69291,7 +69291,7 @@
           <t>A | 586呎 (3房)
 $1216万
 $20,746/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -69299,7 +69299,7 @@
           <t>B | 474呎 (2房)
 $879万
 $18,553/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -69307,7 +69307,7 @@
           <t>C | 450呎 (2房)
 $884万
 $19,633/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -69323,7 +69323,7 @@
           <t>E | 553呎 (2房)
 $1177万
 $21,289/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -69331,7 +69331,7 @@
           <t>F | 307呎 (1房)
 $503万
 $16,397/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -69339,7 +69339,7 @@
           <t>G | 432呎 (2房)
 $704万
 $16,306/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -69347,7 +69347,7 @@
           <t>H | 431呎 (2房)
 $839万
 $19,462/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -69355,7 +69355,7 @@
           <t>J | 538呎 (2房)
 $973万
 $18,093/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -69370,7 +69370,7 @@
           <t>A | 586呎 (3房)
 $1222万
 $20,846/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -69378,7 +69378,7 @@
           <t>B | 474呎 (2房)
 $870万
 $18,361/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -69386,7 +69386,7 @@
           <t>C | 450呎 (2房)
 $848万
 $18,833/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -69402,7 +69402,7 @@
           <t>E | 553呎 (2房)
 $1174万
 $21,226/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -69410,7 +69410,7 @@
           <t>F | 307呎 (1房)
 $502万
 $16,365/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -69418,7 +69418,7 @@
           <t>G | 432呎 (2房)
 $703万
 $16,269/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -69426,7 +69426,7 @@
           <t>H | 432呎 (2房)
 $714万
 $16,528/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -69434,7 +69434,7 @@
           <t>J | 538呎 (2房)
 $989万
 $18,375/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69449,7 +69449,7 @@
           <t>A | 586呎 (3房)
 $1200万
 $20,478/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -69457,7 +69457,7 @@
           <t>B | 474呎 (2房)
 $964万
 $20,333/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -69465,7 +69465,7 @@
           <t>C | 450呎 (2房)
 $878万
 $19,520/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -69473,7 +69473,7 @@
           <t>D | 477呎 (2房)
 $999万
 $20,939/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -69481,7 +69481,7 @@
           <t>E | 553呎 (2房)
 $1170万
 $21,161/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -69489,7 +69489,7 @@
           <t>F | 307呎 (1房)
 $612万
 $19,948/呎
-(24年-08月-07日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -69497,7 +69497,7 @@
           <t>G | 432呎 (2房)
 $701万
 $16,234/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -69505,7 +69505,7 @@
           <t>H | 431呎 (2房)
 $719万
 $16,691/呎
-(25年-01月-20日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -69513,7 +69513,7 @@
           <t>J | 538呎 (2房)
 $986万
 $18,320/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69528,7 +69528,7 @@
           <t>A | 586呎 (3房)
 $1206万
 $20,577/呎
-(25年-05月-18日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -69536,7 +69536,7 @@
           <t>B | 474呎 (2房)
 $872万
 $18,392/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -69544,7 +69544,7 @@
           <t>C | 450呎 (2房)
 $860万
 $19,111/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -69552,7 +69552,7 @@
           <t>D | 477呎 (2房)
 $937万
 $19,639/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -69560,7 +69560,7 @@
           <t>E | 553呎 (2房)
 $1167万
 $21,098/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -69568,7 +69568,7 @@
           <t>F | 307呎 (1房)
 $500万
 $16,303/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -69576,7 +69576,7 @@
           <t>G | 432呎 (2房)
 $700万
 $16,201/呎
-(24年-09月-23日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -69584,7 +69584,7 @@
           <t>H | 431呎 (2房)
 $709万
 $16,441/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -69592,7 +69592,7 @@
           <t>J | 538呎 (2房)
 $965万
 $17,929/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -69607,7 +69607,7 @@
           <t>A | 586呎 (3房)
 $1193万
 $20,363/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -69615,7 +69615,7 @@
           <t>B | 474呎 (2房)
 $879万
 $18,546/呎
-(25年-01月-21日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -69623,7 +69623,7 @@
           <t>C | 450呎 (2房)
 $960万
 $21,340/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -69631,7 +69631,7 @@
           <t>D | 477呎 (2房)
 $931万
 $19,514/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -69639,7 +69639,7 @@
           <t>E | 553呎 (2房)
 $1134万
 $20,510/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -69647,7 +69647,7 @@
           <t>F | 307呎 (1房)
 $499万
 $16,267/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -69655,7 +69655,7 @@
           <t>G | 432呎 (2房)
 $698万
 $16,167/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -69663,7 +69663,7 @@
           <t>H | 431呎 (2房)
 $710万
 $16,471/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -69671,7 +69671,7 @@
           <t>J | 538呎 (2房)
 $962万
 $17,875/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69686,7 +69686,7 @@
           <t>A | 586呎 (3房)
 $1227万
 $20,935/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -69694,7 +69694,7 @@
           <t>B | 474呎 (2房)
 $863万
 $18,205/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -69702,7 +69702,7 @@
           <t>C | 450呎 (2房)
 $867万
 $19,273/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -69710,7 +69710,7 @@
           <t>D | 477呎 (2房)
 $984万
 $20,625/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -69718,7 +69718,7 @@
           <t>E | 553呎 (2房)
 $1134万
 $20,510/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -69726,7 +69726,7 @@
           <t>F | 307呎 (1房)
 $499万
 $16,267/呎
-(24年-09月-22日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -69734,7 +69734,7 @@
           <t>G | 432呎 (2房)
 $790万
 $18,287/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -69742,7 +69742,7 @@
           <t>H | 431呎 (2房)
 $707万
 $16,411/呎
-(24年-10月-21日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -69750,7 +69750,7 @@
           <t>J | 537呎 (2房)
 $962万
 $17,909/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69765,7 +69765,7 @@
           <t>A | 586呎 (3房)
 $1265万
 $21,587/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -69773,7 +69773,7 @@
           <t>B | 474呎 (2房)
 $894万
 $18,861/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -69781,7 +69781,7 @@
           <t>C | 450呎 (2房)
 $865万
 $19,227/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -69797,7 +69797,7 @@
           <t>E | 553呎 (2房)
 $1150万
 $20,803/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -69805,7 +69805,7 @@
           <t>F | 307呎 (1房)
 $496万
 $16,150/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -69813,7 +69813,7 @@
           <t>G | 432呎 (2房)
 $695万
 $16,095/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -69821,7 +69821,7 @@
           <t>H | 432呎 (2房)
 $701万
 $16,222/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -69829,7 +69829,7 @@
           <t>J | 538呎 (2房)
 $949万
 $17,643/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -69844,7 +69844,7 @@
           <t>A | 586呎 (3房)
 $1188万
 $20,275/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -69852,7 +69852,7 @@
           <t>B | 474呎 (2房)
 $851万
 $17,956/呎
-(25年-01月-07日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -69860,7 +69860,7 @@
           <t>C | 450呎 (2房)
 $828万
 $18,407/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -69868,7 +69868,7 @@
           <t>D | 477呎 (2房)
 $992万
 $20,801/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -69876,7 +69876,7 @@
           <t>E | 553呎 (2房)
 $1144万
 $20,685/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -69884,7 +69884,7 @@
           <t>F | 307呎 (1房)
 $579万
 $18,853/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -69892,7 +69892,7 @@
           <t>G | 432呎 (2房)
 $693万
 $16,042/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -69900,7 +69900,7 @@
           <t>H | 431呎 (2房)
 $699万
 $16,225/呎
-(24年-10月-13日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -69908,7 +69908,7 @@
           <t>J | 538呎 (2房)
 $945万
 $17,572/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -69923,7 +69923,7 @@
           <t>A | 586呎 (3房)
 $1179万
 $20,123/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -69931,7 +69931,7 @@
           <t>B | 474呎 (2房)
 $866万
 $18,264/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -69939,7 +69939,7 @@
           <t>C | 450呎 (2房)
 $824万
 $18,316/呎
-(25年-02月-26日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -69947,7 +69947,7 @@
           <t>D | 477呎 (2房)
 $914万
 $19,157/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -69955,7 +69955,7 @@
           <t>E | 553呎 (2房)
 $1085万
 $19,617/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -69963,7 +69963,7 @@
           <t>F | 307呎 (1房)
 $498万
 $16,225/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -69971,7 +69971,7 @@
           <t>G | 432呎 (2房)
 $700万
 $16,199/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -69979,7 +69979,7 @@
           <t>H | 431呎 (2房)
 $700万
 $16,248/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -69987,7 +69987,7 @@
           <t>J | 538呎 (2房)
 $949万
 $17,647/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -70002,7 +70002,7 @@
           <t>A | 586呎 (3房)
 $1173万
 $20,014/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -70010,7 +70010,7 @@
           <t>B | 474呎 (2房)
 $843万
 $17,778/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -70018,7 +70018,7 @@
           <t>C | 450呎 (2房)
 $938万
 $20,833/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -70026,7 +70026,7 @@
           <t>D | 477呎 (2房)
 $907万
 $19,010/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -70034,7 +70034,7 @@
           <t>E | 553呎 (2房)
 $1051万
 $19,013/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -70042,7 +70042,7 @@
           <t>F | 307呎 (1房)
 $491万
 $16,003/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -70050,7 +70050,7 @@
           <t>G | 432呎 (2房)
 $721万
 $16,694/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -70058,7 +70058,7 @@
           <t>H | 431呎 (2房)
 $689万
 $15,986/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -70066,7 +70066,7 @@
           <t>J | 538呎 (2房)
 $930万
 $17,279/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -70081,7 +70081,7 @@
           <t>A | 586呎 (3房)
 $1172万
 $20,000/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -70089,7 +70089,7 @@
           <t>B | 474呎 (2房)
 $863万
 $18,211/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -70097,7 +70097,7 @@
           <t>C | 450呎 (2房)
 $848万
 $18,836/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -70105,7 +70105,7 @@
           <t>D | 477呎 (2房)
 $947万
 $19,849/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -70113,7 +70113,7 @@
           <t>E | 553呎 (2房)
 $1038万
 $18,772/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -70121,7 +70121,7 @@
           <t>F | 307呎 (1房)
 $490万
 $15,958/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -70129,7 +70129,7 @@
           <t>G | 432呎 (2房)
 $688万
 $15,928/呎
-(24年-10月-03日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -70137,7 +70137,7 @@
           <t>H | 432呎 (2房)
 $754万
 $17,461/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -70145,7 +70145,7 @@
           <t>J | 538呎 (2房)
 $969万
 $18,011/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -70161,7 +70161,7 @@
           <t>B | 467呎 (2房)
 $856万
 $18,334/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -70169,7 +70169,7 @@
           <t>C | 450呎 (2房)
 $836万
 $18,584/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -70177,7 +70177,7 @@
           <t>D | 477呎 (2房)
 $938万
 $19,660/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -70185,7 +70185,7 @@
           <t>E | 553呎 (2房)
 $1027万
 $18,579/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -70193,7 +70193,7 @@
           <t>F | 307呎 (1房)
 $489万
 $15,928/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -70201,7 +70201,7 @@
           <t>G | 432呎 (2房)
 $688万
 $15,928/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -70209,7 +70209,7 @@
           <t>H | 390呎 (2房)
 $803万
 $20,585/呎
-(25年-02月-12日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="J34" s="24" t="inlineStr"/>
@@ -70705,7 +70705,7 @@
           <t>A | 508呎 (2房)
 $1321万
 $26,000/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -70713,7 +70713,7 @@
           <t>B | 482呎 (2房)
 $1254万
 $26,008/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -70753,7 +70753,7 @@
           <t>G | 306呎 (1房)
 $678万
 $22,144/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -70793,7 +70793,7 @@
           <t>M | 307呎 (1房)
 $637万
 $20,743/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -70808,7 +70808,7 @@
           <t>A | 508呎 (2房)
 $1193万
 $23,480/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -70816,7 +70816,7 @@
           <t>B | 482呎 (2房)
 $1161万
 $24,083/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -70824,7 +70824,7 @@
           <t>C | 551呎 (2房)
 $1350万
 $24,501/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -70856,7 +70856,7 @@
           <t>G | 306呎 (1房)
 $672万
 $21,948/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -70896,7 +70896,7 @@
           <t>M | 307呎 (1房)
 $631万
 $20,547/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -70911,7 +70911,7 @@
           <t>A | 508呎 (2房)
 $1257万
 $24,748/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -70959,7 +70959,7 @@
           <t>G | 306呎 (1房)
 $666万
 $21,752/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -70999,7 +70999,7 @@
           <t>M | 307呎 (1房)
 $625万
 $20,352/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -71014,7 +71014,7 @@
           <t>A | 508呎 (2房)
 $1187万
 $23,362/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -71022,7 +71022,7 @@
           <t>B | 482呎 (2房)
 $1150万
 $23,855/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -71054,7 +71054,7 @@
           <t>F | 439呎 (2房)
 $901万
 $20,519/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -71062,7 +71062,7 @@
           <t>G | 306呎 (1房)
 $639万
 $20,876/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -71102,7 +71102,7 @@
           <t>M | 307呎 (1房)
 $596万
 $19,397/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -71117,7 +71117,7 @@
           <t>A | 508呎 (2房)
 $1167万
 $22,969/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -71125,7 +71125,7 @@
           <t>B | 482呎 (2房)
 $1114万
 $23,108/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -71157,7 +71157,7 @@
           <t>F | 439呎 (2房)
 $892万
 $20,314/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -71165,7 +71165,7 @@
           <t>G | 306呎 (1房)
 $633万
 $20,680/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -71205,7 +71205,7 @@
           <t>M | 307呎 (1房)
 $589万
 $19,179/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -71220,7 +71220,7 @@
           <t>A | 508呎 (2房)
 $1119万
 $22,024/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -71228,7 +71228,7 @@
           <t>B | 482呎 (2房)
 $1089万
 $22,589/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -71244,7 +71244,7 @@
           <t>D | 307呎 (1房)
 $716万
 $23,329/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -71252,7 +71252,7 @@
           <t>E | 315呎 (1房)
 $739万
 $23,467/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -71260,7 +71260,7 @@
           <t>F | 439呎 (2房)
 $849万
 $19,335/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -71268,7 +71268,7 @@
           <t>G | 306呎 (1房)
 $627万
 $20,484/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -71276,7 +71276,7 @@
           <t>H | 306呎 (1房)
 $646万
 $21,098/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -71284,7 +71284,7 @@
           <t>J | 308呎 (1房)
 $672万
 $21,812/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -71292,7 +71292,7 @@
           <t>K | 306呎 (1房)
 $647万
 $21,137/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -71300,7 +71300,7 @@
           <t>L | 429呎 (2房)
 $936万
 $21,807/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -71308,7 +71308,7 @@
           <t>M | 307呎 (1房)
 $582万
 $18,971/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -71323,7 +71323,7 @@
           <t>A | 508呎 (2房)
 $1107万
 $21,787/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -71331,7 +71331,7 @@
           <t>B | 482呎 (2房)
 $1077万
 $22,340/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -71347,7 +71347,7 @@
           <t>D | 307呎 (1房)
 $701万
 $22,827/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -71355,7 +71355,7 @@
           <t>E | 315呎 (1房)
 $704万
 $22,343/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -71363,7 +71363,7 @@
           <t>F | 439呎 (2房)
 $844万
 $19,221/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -71371,7 +71371,7 @@
           <t>G | 306呎 (1房)
 $560万
 $18,301/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -71379,7 +71379,7 @@
           <t>H | 306呎 (1房)
 $568万
 $18,562/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -71395,7 +71395,7 @@
           <t>K | 306呎 (1房)
 $639万
 $20,876/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -71403,7 +71403,7 @@
           <t>L | 430呎 (2房)
 $925万
 $21,507/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -71411,7 +71411,7 @@
           <t>M | 307呎 (1房)
 $565万
 $18,401/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71426,7 +71426,7 @@
           <t>A | 508呎 (2房)
 $1091万
 $21,472/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -71434,7 +71434,7 @@
           <t>B | 482呎 (2房)
 $1061万
 $22,008/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -71442,7 +71442,7 @@
           <t>C | 551呎 (2房)
 $1262万
 $22,900/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -71450,7 +71450,7 @@
           <t>D | 307呎 (1房)
 $692万
 $22,534/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -71458,7 +71458,7 @@
           <t>E | 315呎 (1房)
 $672万
 $21,340/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -71466,7 +71466,7 @@
           <t>F | 439呎 (2房)
 $831万
 $18,925/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -71474,7 +71474,7 @@
           <t>G | 306呎 (1房)
 $559万
 $18,258/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -71482,7 +71482,7 @@
           <t>H | 306呎 (1房)
 $567万
 $18,520/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -71490,7 +71490,7 @@
           <t>J | 308呎 (1房)
 $588万
 $19,091/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -71498,7 +71498,7 @@
           <t>K | 306呎 (1房)
 $629万
 $20,549/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -71506,7 +71506,7 @@
           <t>L | 430呎 (2房)
 $909万
 $21,135/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -71514,7 +71514,7 @@
           <t>M | 307呎 (1房)
 $559万
 $18,202/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71529,7 +71529,7 @@
           <t>A | 508呎 (2房)
 $1080万
 $21,256/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -71537,7 +71537,7 @@
           <t>B | 482呎 (2房)
 $1051万
 $21,801/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -71545,7 +71545,7 @@
           <t>C | 551呎 (2房)
 $1213万
 $22,011/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -71553,7 +71553,7 @@
           <t>D | 307呎 (1房)
 $687万
 $22,371/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -71561,7 +71561,7 @@
           <t>E | 315呎 (1房)
 $690万
 $21,898/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -71569,7 +71569,7 @@
           <t>F | 439呎 (2房)
 $827万
 $18,834/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -71577,7 +71577,7 @@
           <t>G | 306呎 (1房)
 $557万
 $18,203/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -71585,7 +71585,7 @@
           <t>H | 306呎 (1房)
 $566万
 $18,480/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -71593,7 +71593,7 @@
           <t>J | 308呎 (1房)
 $607万
 $19,701/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -71601,7 +71601,7 @@
           <t>K | 306呎 (1房)
 $602万
 $19,690/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -71609,7 +71609,7 @@
           <t>L | 429呎 (2房)
 $882万
 $20,555/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -71617,7 +71617,7 @@
           <t>M | 307呎 (1房)
 $553万
 $18,000/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71632,7 +71632,7 @@
           <t>A | 508呎 (2房)
 $1109万
 $21,827/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -71640,7 +71640,7 @@
           <t>B | 482呎 (2房)
 $1041万
 $21,593/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -71648,7 +71648,7 @@
           <t>C | 551呎 (2房)
 $1308万
 $23,739/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -71656,7 +71656,7 @@
           <t>D | 307呎 (1房)
 $655万
 $21,336/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -71664,7 +71664,7 @@
           <t>E | 315呎 (1房)
 $683万
 $21,676/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -71672,7 +71672,7 @@
           <t>F | 439呎 (2房)
 $823万
 $18,743/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -71680,7 +71680,7 @@
           <t>G | 306呎 (1房)
 $556万
 $18,167/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -71688,7 +71688,7 @@
           <t>H | 305呎 (1房)
 $564万
 $18,489/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -71696,7 +71696,7 @@
           <t>J | 308呎 (1房)
 $618万
 $20,058/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -71704,7 +71704,7 @@
           <t>K | 306呎 (1房)
 $611万
 $19,961/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -71712,7 +71712,7 @@
           <t>L | 429呎 (2房)
 $863万
 $20,112/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -71720,7 +71720,7 @@
           <t>M | 307呎 (1房)
 $547万
 $17,805/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71735,7 +71735,7 @@
           <t>A | 508呎 (2房)
 $1083万
 $21,315/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -71743,7 +71743,7 @@
           <t>B | 482呎 (2房)
 $1009万
 $20,932/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -71751,7 +71751,7 @@
           <t>C | 551呎 (2房)
 $1210万
 $21,956/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -71759,7 +71759,7 @@
           <t>D | 307呎 (1房)
 $649万
 $21,134/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -71767,7 +71767,7 @@
           <t>E | 315呎 (1房)
 $640万
 $20,305/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -71775,7 +71775,7 @@
           <t>F | 439呎 (2房)
 $818万
 $18,633/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -71783,7 +71783,7 @@
           <t>G | 306呎 (1房)
 $555万
 $18,124/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -71791,7 +71791,7 @@
           <t>H | 305呎 (1房)
 $562万
 $18,443/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -71799,7 +71799,7 @@
           <t>J | 308呎 (1房)
 $616万
 $19,984/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -71807,7 +71807,7 @@
           <t>K | 306呎 (1房)
 $598万
 $19,542/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -71815,7 +71815,7 @@
           <t>L | 429呎 (2房)
 $837万
 $19,510/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -71823,7 +71823,7 @@
           <t>M | 307呎 (1房)
 $540万
 $17,590/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71838,7 +71838,7 @@
           <t>A | 508呎 (2房)
 $1037万
 $20,409/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -71846,7 +71846,7 @@
           <t>B | 482呎 (2房)
 $1008万
 $20,913/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -71854,7 +71854,7 @@
           <t>C | 551呎 (2房)
 $1199万
 $21,757/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -71862,7 +71862,7 @@
           <t>D | 307呎 (1房)
 $642万
 $20,906/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -71870,7 +71870,7 @@
           <t>E | 315呎 (1房)
 $633万
 $20,105/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -71878,7 +71878,7 @@
           <t>F | 439呎 (2房)
 $791万
 $18,009/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -71886,7 +71886,7 @@
           <t>G | 306呎 (1房)
 $553万
 $18,078/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -71894,7 +71894,7 @@
           <t>H | 305呎 (1房)
 $561万
 $18,393/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -71902,7 +71902,7 @@
           <t>J | 308呎 (1房)
 $590万
 $19,169/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -71910,7 +71910,7 @@
           <t>K | 306呎 (1房)
 $607万
 $19,830/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -71918,7 +71918,7 @@
           <t>L | 429呎 (2房)
 $847万
 $19,739/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -71926,7 +71926,7 @@
           <t>M | 307呎 (1房)
 $534万
 $17,404/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -71941,7 +71941,7 @@
           <t>A | 508呎 (2房)
 $1061万
 $20,882/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -71949,7 +71949,7 @@
           <t>B | 482呎 (2房)
 $1029万
 $21,344/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -71957,7 +71957,7 @@
           <t>C | 551呎 (2房)
 $1169万
 $21,212/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -71965,7 +71965,7 @@
           <t>D | 307呎 (1房)
 $660万
 $21,511/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -71973,7 +71973,7 @@
           <t>E | 315呎 (1房)
 $627万
 $19,905/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -71981,7 +71981,7 @@
           <t>F | 439呎 (2房)
 $786万
 $17,911/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -71989,7 +71989,7 @@
           <t>G | 306呎 (1房)
 $550万
 $17,974/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -71997,7 +71997,7 @@
           <t>H | 305呎 (1房)
 $558万
 $18,305/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -72005,7 +72005,7 @@
           <t>J | 308呎 (1房)
 $577万
 $18,727/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -72013,7 +72013,7 @@
           <t>K | 306呎 (1房)
 $572万
 $18,686/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -72021,7 +72021,7 @@
           <t>L | 430呎 (2房)
 $821万
 $19,091/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -72029,7 +72029,7 @@
           <t>M | 307呎 (1房)
 $528万
 $17,199/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72044,7 +72044,7 @@
           <t>A | 508呎 (2房)
 $1051万
 $20,685/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -72052,7 +72052,7 @@
           <t>B | 482呎 (2房)
 $1021万
 $21,178/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -72060,7 +72060,7 @@
           <t>C | 551呎 (2房)
 $1158万
 $21,013/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -72068,7 +72068,7 @@
           <t>D | 307呎 (1房)
 $629万
 $20,482/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -72076,7 +72076,7 @@
           <t>E | 315呎 (1房)
 $621万
 $19,711/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -72084,7 +72084,7 @@
           <t>F | 439呎 (2房)
 $782万
 $17,809/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -72092,7 +72092,7 @@
           <t>G | 306呎 (1房)
 $549万
 $17,941/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -72100,7 +72100,7 @@
           <t>H | 305呎 (1房)
 $557万
 $18,259/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -72108,7 +72108,7 @@
           <t>J | 308呎 (1房)
 $575万
 $18,662/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -72116,7 +72116,7 @@
           <t>K | 306呎 (1房)
 $570万
 $18,621/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -72124,7 +72124,7 @@
           <t>L | 429呎 (2房)
 $814万
 $18,979/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -72132,7 +72132,7 @@
           <t>M | 307呎 (1房)
 $521万
 $16,971/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72147,7 +72147,7 @@
           <t>A | 508呎 (2房)
 $1025万
 $20,173/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -72155,7 +72155,7 @@
           <t>B | 482呎 (2房)
 $997万
 $20,680/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -72163,7 +72163,7 @@
           <t>C | 551呎 (2房)
 $1147万
 $20,813/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -72171,7 +72171,7 @@
           <t>D | 307呎 (1房)
 $623万
 $20,287/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -72179,7 +72179,7 @@
           <t>E | 315呎 (1房)
 $615万
 $19,517/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -72187,7 +72187,7 @@
           <t>F | 439呎 (2房)
 $778万
 $17,711/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -72195,7 +72195,7 @@
           <t>G | 306呎 (1房)
 $548万
 $17,899/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -72203,7 +72203,7 @@
           <t>H | 305呎 (1房)
 $556万
 $18,216/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -72211,7 +72211,7 @@
           <t>J | 308呎 (1房)
 $573万
 $18,597/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -72219,7 +72219,7 @@
           <t>K | 305呎 (1房)
 $568万
 $18,616/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -72227,7 +72227,7 @@
           <t>L | 430呎 (2房)
 $812万
 $18,881/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -72235,7 +72235,7 @@
           <t>M | 307呎 (1房)
 $520万
 $16,954/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72250,7 +72250,7 @@
           <t>A | 508呎 (2房)
 $1053万
 $20,724/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -72258,7 +72258,7 @@
           <t>B | 482呎 (2房)
 $994万
 $20,627/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -72266,7 +72266,7 @@
           <t>C | 551呎 (2房)
 $1102万
 $19,998/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -72274,7 +72274,7 @@
           <t>D | 307呎 (1房)
 $618万
 $20,130/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -72282,7 +72282,7 @@
           <t>E | 315呎 (1房)
 $609万
 $19,340/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -72290,7 +72290,7 @@
           <t>F | 439呎 (2房)
 $773万
 $17,608/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -72298,7 +72298,7 @@
           <t>G | 306呎 (1房)
 $546万
 $17,853/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -72306,7 +72306,7 @@
           <t>H | 305呎 (1房)
 $554万
 $18,174/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -72314,7 +72314,7 @@
           <t>J | 308呎 (1房)
 $571万
 $18,532/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -72322,7 +72322,7 @@
           <t>K | 306呎 (1房)
 $566万
 $18,490/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -72330,7 +72330,7 @@
           <t>L | 429呎 (2房)
 $809万
 $18,865/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -72338,7 +72338,7 @@
           <t>M | 307呎 (1房)
 $520万
 $16,938/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72353,7 +72353,7 @@
           <t>A | 508呎 (2房)
 $1020万
 $20,085/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -72361,7 +72361,7 @@
           <t>B | 482呎 (2房)
 $992万
 $20,585/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -72369,7 +72369,7 @@
           <t>C | 551呎 (2房)
 $1091万
 $19,800/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -72377,7 +72377,7 @@
           <t>D | 307呎 (1房)
 $653万
 $21,264/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -72385,7 +72385,7 @@
           <t>E | 315呎 (1房)
 $604万
 $19,168/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -72393,7 +72393,7 @@
           <t>F | 439呎 (2房)
 $769万
 $17,510/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -72401,7 +72401,7 @@
           <t>G | 306呎 (1房)
 $545万
 $17,810/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -72409,7 +72409,7 @@
           <t>H | 306呎 (1房)
 $553万
 $18,065/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -72417,7 +72417,7 @@
           <t>J | 308呎 (1房)
 $569万
 $18,468/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -72425,7 +72425,7 @@
           <t>K | 306呎 (1房)
 $564万
 $18,425/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -72433,7 +72433,7 @@
           <t>L | 430呎 (2房)
 $807万
 $18,763/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -72441,7 +72441,7 @@
           <t>M | 307呎 (1房)
 $519万
 $16,915/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72456,7 +72456,7 @@
           <t>A | 508呎 (2房)
 $1091万
 $21,472/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -72464,7 +72464,7 @@
           <t>B | 482呎 (2房)
 $990万
 $20,539/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -72472,7 +72472,7 @@
           <t>C | 551呎 (2房)
 $1159万
 $21,031/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -72480,7 +72480,7 @@
           <t>D | 307呎 (1房)
 $611万
 $19,896/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -72488,7 +72488,7 @@
           <t>E | 315呎 (1房)
 $603万
 $19,137/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -72496,7 +72496,7 @@
           <t>F | 439呎 (2房)
 $787万
 $17,923/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -72504,7 +72504,7 @@
           <t>G | 306呎 (1房)
 $544万
 $17,765/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -72512,7 +72512,7 @@
           <t>H | 305呎 (1房)
 $552万
 $18,092/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -72520,7 +72520,7 @@
           <t>J | 308呎 (1房)
 $567万
 $18,403/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -72528,7 +72528,7 @@
           <t>K | 306呎 (1房)
 $562万
 $18,359/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -72536,7 +72536,7 @@
           <t>L | 429呎 (2房)
 $804万
 $18,748/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -72544,7 +72544,7 @@
           <t>M | 307呎 (1房)
 $519万
 $16,899/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72559,7 +72559,7 @@
           <t>A | 508呎 (2房)
 $1044万
 $20,547/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -72567,7 +72567,7 @@
           <t>B | 482呎 (2房)
 $1009万
 $20,929/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -72575,7 +72575,7 @@
           <t>C | 551呎 (2房)
 $1151万
 $20,886/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -72583,7 +72583,7 @@
           <t>D | 307呎 (1房)
 $649万
 $21,134/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -72591,7 +72591,7 @@
           <t>E | 315呎 (1房)
 $602万
 $19,105/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -72599,7 +72599,7 @@
           <t>F | 439呎 (2房)
 $782万
 $17,809/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -72607,7 +72607,7 @@
           <t>G | 306呎 (1房)
 $542万
 $17,722/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -72615,7 +72615,7 @@
           <t>H | 305呎 (1房)
 $550万
 $18,033/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -72623,7 +72623,7 @@
           <t>J | 308呎 (1房)
 $566万
 $18,370/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -72631,7 +72631,7 @@
           <t>K | 306呎 (1房)
 $560万
 $18,301/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -72639,7 +72639,7 @@
           <t>L | 430呎 (2房)
 $790万
 $18,367/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -72647,7 +72647,7 @@
           <t>M | 307呎 (1房)
 $518万
 $16,883/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72662,7 +72662,7 @@
           <t>A | 508呎 (2房)
 $1068万
 $21,020/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -72670,7 +72670,7 @@
           <t>B | 482呎 (2房)
 $986万
 $20,456/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -72678,7 +72678,7 @@
           <t>C | 551呎 (2房)
 $1213万
 $22,011/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -72686,7 +72686,7 @@
           <t>D | 307呎 (1房)
 $607万
 $19,765/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -72694,7 +72694,7 @@
           <t>E | 315呎 (1房)
 $600万
 $19,048/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -72702,7 +72702,7 @@
           <t>F | 439呎 (2房)
 $778万
 $17,718/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -72710,7 +72710,7 @@
           <t>G | 306呎 (1房)
 $541万
 $17,676/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -72718,7 +72718,7 @@
           <t>H | 305呎 (1房)
 $549万
 $17,990/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -72726,7 +72726,7 @@
           <t>J | 308呎 (1房)
 $565万
 $18,331/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -72734,7 +72734,7 @@
           <t>K | 306呎 (1房)
 $559万
 $18,268/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -72742,7 +72742,7 @@
           <t>L | 430呎 (2房)
 $782万
 $18,179/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -72750,7 +72750,7 @@
           <t>M | 307呎 (1房)
 $518万
 $16,866/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72765,7 +72765,7 @@
           <t>A | 508呎 (2房)
 $1093万
 $21,512/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -72773,7 +72773,7 @@
           <t>B | 482呎 (2房)
 $1027万
 $21,303/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -72781,7 +72781,7 @@
           <t>C | 551呎 (2房)
 $1181万
 $21,432/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -72789,7 +72789,7 @@
           <t>D | 307呎 (1房)
 $604万
 $19,668/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -72797,7 +72797,7 @@
           <t>E | 315呎 (1房)
 $589万
 $18,698/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -72805,7 +72805,7 @@
           <t>F | 439呎 (2房)
 $774万
 $17,626/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -72813,7 +72813,7 @@
           <t>G | 306呎 (1房)
 $536万
 $17,500/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -72821,7 +72821,7 @@
           <t>H | 305呎 (1房)
 $543万
 $17,810/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -72829,7 +72829,7 @@
           <t>J | 308呎 (1房)
 $572万
 $18,578/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -72837,7 +72837,7 @@
           <t>K | 306呎 (1房)
 $549万
 $17,935/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -72845,7 +72845,7 @@
           <t>L | 430呎 (2房)
 $774万
 $17,998/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -72853,7 +72853,7 @@
           <t>M | 307呎 (1房)
 $510万
 $16,612/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72868,7 +72868,7 @@
           <t>A | 508呎 (2房)
 $1033万
 $20,331/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -72876,7 +72876,7 @@
           <t>B | 482呎 (2房)
 $1004万
 $20,826/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -72884,7 +72884,7 @@
           <t>C | 551呎 (2房)
 $1114万
 $20,214/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -72892,7 +72892,7 @@
           <t>D | 307呎 (1房)
 $639万
 $20,808/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -72900,7 +72900,7 @@
           <t>E | 315呎 (1房)
 $586万
 $18,610/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -72908,7 +72908,7 @@
           <t>F | 439呎 (2房)
 $747万
 $17,009/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -72916,7 +72916,7 @@
           <t>G | 306呎 (1房)
 $534万
 $17,461/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -72924,7 +72924,7 @@
           <t>H | 306呎 (1房)
 $542万
 $17,709/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -72932,7 +72932,7 @@
           <t>J | 308呎 (1房)
 $569万
 $18,487/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -72940,7 +72940,7 @@
           <t>K | 306呎 (1房)
 $546万
 $17,830/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -72948,7 +72948,7 @@
           <t>L | 430呎 (2房)
 $762万
 $17,719/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -72956,7 +72956,7 @@
           <t>M | 307呎 (1房)
 $501万
 $16,313/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -72971,7 +72971,7 @@
           <t>A | 508呎 (2房)
 $1028万
 $20,236/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -72979,7 +72979,7 @@
           <t>B | 482呎 (2房)
 $999万
 $20,722/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -72987,7 +72987,7 @@
           <t>C | 551呎 (2房)
 $1103万
 $20,015/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -72995,7 +72995,7 @@
           <t>D | 307呎 (1房)
 $647万
 $21,068/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -73003,7 +73003,7 @@
           <t>E | 315呎 (1房)
 $603万
 $19,152/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -73011,7 +73011,7 @@
           <t>F | 439呎 (2房)
 $741万
 $16,884/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -73019,7 +73019,7 @@
           <t>G | 306呎 (1房)
 $533万
 $17,415/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -73027,7 +73027,7 @@
           <t>H | 306呎 (1房)
 $540万
 $17,663/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -73035,7 +73035,7 @@
           <t>J | 308呎 (1房)
 $548万
 $17,792/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -73043,7 +73043,7 @@
           <t>K | 305呎 (1房)
 $564万
 $18,502/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -73051,7 +73051,7 @@
           <t>L | 430呎 (2房)
 $748万
 $17,393/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -73059,7 +73059,7 @@
           <t>M | 307呎 (1房)
 $498万
 $16,221/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -73074,7 +73074,7 @@
           <t>A | 508呎 (2房)
 $919万
 $18,087/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -73082,7 +73082,7 @@
           <t>B | 482呎 (2房)
 $893万
 $18,527/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -73090,7 +73090,7 @@
           <t>C | 551呎 (2房)
 $1099万
 $19,942/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -73098,7 +73098,7 @@
           <t>D | 307呎 (1房)
 $637万
 $20,743/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -73106,7 +73106,7 @@
           <t>E | 315呎 (1房)
 $598万
 $18,978/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -73114,7 +73114,7 @@
           <t>F | 439呎 (2房)
 $732万
 $16,670/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -73122,7 +73122,7 @@
           <t>G | 306呎 (1房)
 $526万
 $17,196/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -73130,7 +73130,7 @@
           <t>H | 305呎 (1房)
 $534万
 $17,498/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -73138,7 +73138,7 @@
           <t>J | 308呎 (1房)
 $540万
 $17,526/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -73146,7 +73146,7 @@
           <t>K | 306呎 (1房)
 $534万
 $17,444/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -73154,7 +73154,7 @@
           <t>L | 430呎 (2房)
 $735万
 $17,088/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -73162,7 +73162,7 @@
           <t>M | 307呎 (1房)
 $495万
 $16,117/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -73177,7 +73177,7 @@
           <t>A | 508呎 (2房)
 $889万
 $17,500/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -73185,7 +73185,7 @@
           <t>B | 482呎 (2房)
 $844万
 $17,502/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -73193,7 +73193,7 @@
           <t>C | 551呎 (2房)
 $1122万
 $20,363/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -73201,7 +73201,7 @@
           <t>D | 307呎 (1房)
 $570万
 $18,560/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -73209,7 +73209,7 @@
           <t>E | 315呎 (1房)
 $552万
 $17,517/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -73217,7 +73217,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -73225,7 +73225,7 @@
           <t>G | 306呎 (1房)
 $518万
 $16,915/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -73233,7 +73233,7 @@
           <t>H | 306呎 (1房)
 $525万
 $17,157/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -73241,7 +73241,7 @@
           <t>J | 308呎 (1房)
 $531万
 $17,240/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -73249,7 +73249,7 @@
           <t>K | 306呎 (1房)
 $526万
 $17,190/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -73257,7 +73257,7 @@
           <t>L | 430呎 (2房)
 $738万
 $17,160/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -73265,7 +73265,7 @@
           <t>M | 307呎 (1房)
 $491万
 $16,003/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -73280,7 +73280,7 @@
           <t>A | 508呎 (2房)
 $864万
 $17,002/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -73288,7 +73288,7 @@
           <t>B | 482呎 (2房)
 $820万
 $17,002/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -73296,7 +73296,7 @@
           <t>C | 551呎 (2房)
 $1060万
 $19,234/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -73304,7 +73304,7 @@
           <t>D | 307呎 (1房)
 $553万
 $18,007/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -73312,7 +73312,7 @@
           <t>E | 315呎 (1房)
 $536万
 $17,000/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -73320,7 +73320,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -73328,7 +73328,7 @@
           <t>G | 306呎 (1房)
 $505万
 $16,503/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -73336,7 +73336,7 @@
           <t>H | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -73344,7 +73344,7 @@
           <t>J | 308呎 (1房)
 $524万
 $17,006/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -73352,7 +73352,7 @@
           <t>K | 305呎 (1房)
 $519万
 $17,010/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -73360,7 +73360,7 @@
           <t>L | 430呎 (2房)
 $710万
 $16,512/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -73368,7 +73368,7 @@
           <t>M | 307呎 (1房)
 $492万
 $16,020/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -73391,7 +73391,7 @@
           <t>B | 445呎 (2房)
 $1066万
 $23,946/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -73399,7 +73399,7 @@
           <t>C | 513呎 (2房)
 $1313万
 $25,591/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -73416,7 +73416,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -73424,7 +73424,7 @@
           <t>G | 306呎 (1房)
 $505万
 $16,503/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -73432,7 +73432,7 @@
           <t>H | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
@@ -73440,7 +73440,7 @@
           <t>J | 308呎 (1房)
 $524万
 $17,006/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -73448,7 +73448,7 @@
           <t>K | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -73456,7 +73456,7 @@
           <t>L | 429呎 (2房)
 $710万
 $16,550/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -73464,7 +73464,7 @@
           <t>M | 269呎 (1房)
 $600万
 $22,305/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -64402,7 +64402,7 @@
           <t>C | 498呎 (2房)
 $1172万
 $23,526/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -64474,7 +64474,7 @@
           <t>M | 481呎 (2房)
 $970万
 $20,166/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N5" s="22" t="inlineStr">
@@ -64585,7 +64585,7 @@
           <t>M | 481呎 (2房)
 $1107万
 $23,010/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -64608,7 +64608,7 @@
           <t>A | 774呎 (3房)
 $2144万
 $27,698/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -64616,7 +64616,7 @@
           <t>B | 536呎 (2房)
 $1233万
 $23,000/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -64696,7 +64696,7 @@
           <t>M | 481呎 (2房)
 $1059万
 $22,012/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="N7" s="22" t="inlineStr">
@@ -64727,7 +64727,7 @@
           <t>B | 536呎 (2房)
 $1150万
 $21,455/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -64743,7 +64743,7 @@
           <t>D | 534呎 (2房)
 $1271万
 $23,800/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -64759,7 +64759,7 @@
           <t>F | 427呎 (2房)
 $856万
 $20,059/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -64775,7 +64775,7 @@
           <t>H | 305呎 (1房)
 $635万
 $20,813/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -64791,7 +64791,7 @@
           <t>K | 309呎 (1房)
 $653万
 $21,126/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -64799,7 +64799,7 @@
           <t>L | 430呎 (2房)
 $809万
 $18,814/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -64807,7 +64807,7 @@
           <t>M | 481呎 (2房)
 $1010万
 $20,998/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -64830,7 +64830,7 @@
           <t>A | 774呎 (3房)
 $2007万
 $25,928/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -64838,7 +64838,7 @@
           <t>B | 536呎 (2房)
 $1138万
 $21,231/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -64854,7 +64854,7 @@
           <t>D | 534呎 (2房)
 $1188万
 $22,238/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -64862,7 +64862,7 @@
           <t>E | 437呎 (2房)
 $958万
 $21,918/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -64870,7 +64870,7 @@
           <t>F | 427呎 (2房)
 $846万
 $19,822/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -64878,7 +64878,7 @@
           <t>G | 306呎 (1房)
 $676万
 $22,092/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -64886,7 +64886,7 @@
           <t>H | 306呎 (1房)
 $632万
 $20,647/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -64902,7 +64902,7 @@
           <t>K | 309呎 (1房)
 $646万
 $20,890/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -64910,7 +64910,7 @@
           <t>L | 430呎 (2房)
 $891万
 $20,726/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -64918,7 +64918,7 @@
           <t>M | 481呎 (2房)
 $1008万
 $20,967/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -64949,7 +64949,7 @@
           <t>B | 536呎 (2房)
 $1126万
 $21,000/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -64965,7 +64965,7 @@
           <t>D | 534呎 (2房)
 $1239万
 $23,199/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -64973,7 +64973,7 @@
           <t>E | 437呎 (2房)
 $999万
 $22,856/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -64981,7 +64981,7 @@
           <t>F | 427呎 (2房)
 $851万
 $19,925/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -64989,7 +64989,7 @@
           <t>G | 306呎 (1房)
 $670万
 $21,889/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -65005,7 +65005,7 @@
           <t>J | 306呎 (1房)
 $696万
 $22,732/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -65013,7 +65013,7 @@
           <t>K | 309呎 (1房)
 $615万
 $19,916/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -65021,7 +65021,7 @@
           <t>L | 430呎 (2房)
 $860万
 $20,000/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -65029,7 +65029,7 @@
           <t>M | 481呎 (2房)
 $990万
 $20,582/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -65037,7 +65037,7 @@
           <t>N | 285呎 (1房)
 $672万
 $23,579/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -65052,7 +65052,7 @@
           <t>A | 774呎 (3房)
 $1889万
 $24,403/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -65060,7 +65060,7 @@
           <t>B | 536呎 (2房)
 $1099万
 $20,500/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -65076,7 +65076,7 @@
           <t>D | 534呎 (2房)
 $1162万
 $21,753/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -65084,7 +65084,7 @@
           <t>E | 437呎 (2房)
 $909万
 $20,798/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -65092,7 +65092,7 @@
           <t>F | 427呎 (2房)
 $836万
 $19,590/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -65100,7 +65100,7 @@
           <t>G | 306呎 (1房)
 $664万
 $21,693/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -65108,7 +65108,7 @@
           <t>H | 306呎 (1房)
 $627万
 $20,484/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -65116,7 +65116,7 @@
           <t>J | 306呎 (1房)
 $689万
 $22,516/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -65124,7 +65124,7 @@
           <t>K | 309呎 (1房)
 $613万
 $19,848/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -65132,7 +65132,7 @@
           <t>L | 430呎 (2房)
 $890万
 $20,695/呎
-(24年-06月)</t>
+(24年-06月-23日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -65140,7 +65140,7 @@
           <t>M | 481呎 (2房)
 $1007万
 $20,933/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -65148,7 +65148,7 @@
           <t>N | 285呎 (1房)
 $679万
 $23,818/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -65163,7 +65163,7 @@
           <t>A | 771呎 (3房)
 $1748万
 $22,672/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -65171,7 +65171,7 @@
           <t>B | 536呎 (2房)
 $1085万
 $20,235/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -65187,7 +65187,7 @@
           <t>D | 534呎 (2房)
 $1078万
 $20,185/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -65195,7 +65195,7 @@
           <t>E | 437呎 (2房)
 $864万
 $19,767/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -65203,7 +65203,7 @@
           <t>F | 427呎 (2房)
 $839万
 $19,644/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -65211,7 +65211,7 @@
           <t>G | 306呎 (1房)
 $658万
 $21,487/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -65219,7 +65219,7 @@
           <t>H | 306呎 (1房)
 $620万
 $20,261/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -65227,7 +65227,7 @@
           <t>J | 305呎 (1房)
 $550万
 $18,030/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -65235,7 +65235,7 @@
           <t>K | 308呎 (1房)
 $608万
 $19,756/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -65243,7 +65243,7 @@
           <t>L | 430呎 (2房)
 $792万
 $18,409/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -65251,7 +65251,7 @@
           <t>M | 481呎 (2房)
 $998万
 $20,753/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -65259,7 +65259,7 @@
           <t>N | 285呎 (1房)
 $672万
 $23,579/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -65274,7 +65274,7 @@
           <t>A | 771呎 (3房)
 $1760万
 $22,827/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -65282,7 +65282,7 @@
           <t>B | 536呎 (2房)
 $1080万
 $20,142/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -65298,7 +65298,7 @@
           <t>D | 534呎 (2房)
 $1087万
 $20,358/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -65306,7 +65306,7 @@
           <t>E | 437呎 (2房)
 $857万
 $19,616/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -65314,7 +65314,7 @@
           <t>F | 427呎 (2房)
 $789万
 $18,485/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -65322,7 +65322,7 @@
           <t>G | 306呎 (1房)
 $651万
 $21,275/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -65330,7 +65330,7 @@
           <t>H | 306呎 (1房)
 $596万
 $19,471/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -65338,7 +65338,7 @@
           <t>J | 305呎 (1房)
 $546万
 $17,892/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -65346,7 +65346,7 @@
           <t>K | 308呎 (1房)
 $605万
 $19,653/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -65354,7 +65354,7 @@
           <t>L | 430呎 (2房)
 $876万
 $20,377/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -65362,7 +65362,7 @@
           <t>M | 481呎 (2房)
 $994万
 $20,674/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -65370,7 +65370,7 @@
           <t>N | 285呎 (1房)
 $631万
 $22,133/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -65385,7 +65385,7 @@
           <t>A | 774呎 (3房)
 $1807万
 $23,344/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -65393,7 +65393,7 @@
           <t>B | 536呎 (2房)
 $1060万
 $19,778/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -65409,7 +65409,7 @@
           <t>D | 534呎 (2房)
 $1114万
 $20,861/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -65417,7 +65417,7 @@
           <t>E | 437呎 (2房)
 $857万
 $19,606/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -65425,7 +65425,7 @@
           <t>F | 427呎 (2房)
 $778万
 $18,220/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -65433,7 +65433,7 @@
           <t>G | 306呎 (1房)
 $542万
 $17,703/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -65441,7 +65441,7 @@
           <t>H | 306呎 (1房)
 $592万
 $19,350/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -65449,7 +65449,7 @@
           <t>J | 305呎 (1房)
 $539万
 $17,685/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -65457,7 +65457,7 @@
           <t>K | 308呎 (1房)
 $602万
 $19,549/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -65465,7 +65465,7 @@
           <t>L | 430呎 (2房)
 $875万
 $20,344/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -65473,7 +65473,7 @@
           <t>M | 481呎 (2房)
 $992万
 $20,626/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -65481,7 +65481,7 @@
           <t>N | 288呎 (1房)
 $553万
 $19,215/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -65496,7 +65496,7 @@
           <t>A | 774呎 (3房)
 $1755万
 $22,679/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -65504,7 +65504,7 @@
           <t>B | 536呎 (2房)
 $1060万
 $19,767/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -65520,7 +65520,7 @@
           <t>D | 534呎 (2房)
 $1054万
 $19,745/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -65528,7 +65528,7 @@
           <t>E | 437呎 (2房)
 $849万
 $19,437/呎
-(25年-03月)</t>
+(25年-03月-09日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -65536,7 +65536,7 @@
           <t>F | 427呎 (2房)
 $786万
 $18,412/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -65544,7 +65544,7 @@
           <t>G | 306呎 (1房)
 $540万
 $17,663/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -65552,7 +65552,7 @@
           <t>H | 305呎 (1房)
 $589万
 $19,302/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -65560,7 +65560,7 @@
           <t>J | 305呎 (1房)
 $540万
 $17,695/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -65568,7 +65568,7 @@
           <t>K | 309呎 (1房)
 $599万
 $19,382/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -65576,7 +65576,7 @@
           <t>L | 430呎 (2房)
 $873万
 $20,312/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -65584,7 +65584,7 @@
           <t>M | 481呎 (2房)
 $991万
 $20,595/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -65592,7 +65592,7 @@
           <t>N | 288呎 (1房)
 $552万
 $19,153/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -65607,7 +65607,7 @@
           <t>A | 774呎 (3房)
 $1967万
 $25,411/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -65615,7 +65615,7 @@
           <t>B | 536呎 (2房)
 $1068万
 $19,925/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -65631,7 +65631,7 @@
           <t>D | 534呎 (2房)
 $1096万
 $20,530/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -65639,7 +65639,7 @@
           <t>E | 437呎 (2房)
 $922万
 $21,094/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -65647,7 +65647,7 @@
           <t>F | 427呎 (2房)
 $777万
 $18,187/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -65655,7 +65655,7 @@
           <t>G | 306呎 (1房)
 $537万
 $17,562/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -65663,7 +65663,7 @@
           <t>H | 305呎 (1房)
 $585万
 $19,184/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -65671,7 +65671,7 @@
           <t>J | 305呎 (1房)
 $538万
 $17,639/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -65679,7 +65679,7 @@
           <t>K | 308呎 (1房)
 $595万
 $19,318/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -65687,7 +65687,7 @@
           <t>L | 430呎 (2房)
 $777万
 $18,063/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -65695,7 +65695,7 @@
           <t>M | 481呎 (2房)
 $989万
 $20,557/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -65703,7 +65703,7 @@
           <t>N | 285呎 (1房)
 $598万
 $20,989/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -65718,7 +65718,7 @@
           <t>A | 774呎 (3房)
 $1774万
 $22,917/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -65726,7 +65726,7 @@
           <t>B | 536呎 (2房)
 $1062万
 $19,817/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -65734,7 +65734,7 @@
           <t>C | 498呎 (2房)
 $1100万
 $22,092/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -65742,7 +65742,7 @@
           <t>D | 534呎 (2房)
 $1034万
 $19,354/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -65750,7 +65750,7 @@
           <t>E | 437呎 (2房)
 $927万
 $21,215/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -65758,7 +65758,7 @@
           <t>F | 427呎 (2房)
 $769万
 $18,009/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -65766,7 +65766,7 @@
           <t>G | 306呎 (1房)
 $536万
 $17,529/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -65774,7 +65774,7 @@
           <t>H | 305呎 (1房)
 $584万
 $19,134/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -65782,7 +65782,7 @@
           <t>J | 305呎 (1房)
 $536万
 $17,584/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -65790,7 +65790,7 @@
           <t>K | 309呎 (1房)
 $592万
 $19,162/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -65798,7 +65798,7 @@
           <t>L | 430呎 (2房)
 $871万
 $20,253/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -65806,7 +65806,7 @@
           <t>M | 481呎 (2房)
 $978万
 $20,333/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -65814,7 +65814,7 @@
           <t>N | 285呎 (1房)
 $594万
 $20,853/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -65829,7 +65829,7 @@
           <t>A | 771呎 (3房)
 $1718万
 $22,283/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -65837,7 +65837,7 @@
           <t>B | 536呎 (2房)
 $1047万
 $19,530/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -65853,7 +65853,7 @@
           <t>D | 534呎 (2房)
 $1038万
 $19,436/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -65861,7 +65861,7 @@
           <t>E | 437呎 (2房)
 $838万
 $19,183/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -65869,7 +65869,7 @@
           <t>F | 427呎 (2房)
 $773万
 $18,103/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -65877,7 +65877,7 @@
           <t>G | 306呎 (1房)
 $637万
 $20,807/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -65885,7 +65885,7 @@
           <t>H | 305呎 (1房)
 $581万
 $19,036/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -65893,7 +65893,7 @@
           <t>J | 305呎 (1房)
 $537万
 $17,597/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -65901,7 +65901,7 @@
           <t>K | 308呎 (1房)
 $546万
 $17,724/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -65909,7 +65909,7 @@
           <t>L | 430呎 (2房)
 $869万
 $20,216/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -65917,7 +65917,7 @@
           <t>M | 481呎 (2房)
 $986万
 $20,491/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -65925,7 +65925,7 @@
           <t>N | 285呎 (1房)
 $549万
 $19,249/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -65940,7 +65940,7 @@
           <t>A | 774呎 (3房)
 $1851万
 $23,912/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -65948,7 +65948,7 @@
           <t>B | 536呎 (2房)
 $1050万
 $19,590/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -65964,7 +65964,7 @@
           <t>D | 534呎 (2房)
 $1027万
 $19,238/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -65972,7 +65972,7 @@
           <t>E | 437呎 (2房)
 $915万
 $20,934/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -65980,7 +65980,7 @@
           <t>F | 427呎 (2房)
 $855万
 $20,014/呎
-(23年-11月)</t>
+(23年-11月-19日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -65988,7 +65988,7 @@
           <t>G | 306呎 (1房)
 $530万
 $17,324/呎
-(25年-02月)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -65996,7 +65996,7 @@
           <t>H | 305呎 (1房)
 $580万
 $19,003/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -66004,7 +66004,7 @@
           <t>J | 305呎 (1房)
 $532万
 $17,459/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -66012,7 +66012,7 @@
           <t>K | 308呎 (1房)
 $590万
 $19,159/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -66020,7 +66020,7 @@
           <t>L | 430呎 (2房)
 $781万
 $18,172/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -66028,7 +66028,7 @@
           <t>M | 481呎 (2房)
 $984万
 $20,457/呎
-(23年-11月)</t>
+(23年-11月-26日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -66036,7 +66036,7 @@
           <t>N | 288呎 (1房)
 $549万
 $19,059/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -66051,7 +66051,7 @@
           <t>A | 774呎 (3房)
 $1888万
 $24,393/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -66059,7 +66059,7 @@
           <t>B | 536呎 (2房)
 $1063万
 $19,826/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -66075,7 +66075,7 @@
           <t>D | 534呎 (2房)
 $1027万
 $19,238/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -66083,7 +66083,7 @@
           <t>E | 437呎 (1房)
 $875万
 $20,018/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -66091,7 +66091,7 @@
           <t>F | 427呎 (2房)
 $855万
 $20,014/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -66099,7 +66099,7 @@
           <t>G | 306呎 (1房)
 $530万
 $17,324/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -66107,7 +66107,7 @@
           <t>H | 305呎 (1房)
 $536万
 $17,561/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -66115,7 +66115,7 @@
           <t>J | 305呎 (1房)
 $534万
 $17,505/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -66123,7 +66123,7 @@
           <t>K | 308呎 (1房)
 $541万
 $17,562/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -66131,7 +66131,7 @@
           <t>L | 430呎 (2房)
 $779万
 $18,109/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -66139,7 +66139,7 @@
           <t>M | 481呎 (2房)
 $984万
 $20,457/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -66147,7 +66147,7 @@
           <t>N | 288呎 (1房)
 $589万
 $20,441/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -66162,7 +66162,7 @@
           <t>A | 771呎 (3房)
 $1650万
 $21,401/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -66170,7 +66170,7 @@
           <t>B | 536呎 (2房)
 $1025万
 $19,123/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -66178,7 +66178,7 @@
           <t>C | 497呎 (2房)
 $1143万
 $22,994/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -66186,7 +66186,7 @@
           <t>D | 534呎 (2房)
 $983万
 $18,416/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -66194,7 +66194,7 @@
           <t>E | 437呎 (2房)
 $829万
 $18,966/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -66202,7 +66202,7 @@
           <t>F | 427呎 (2房)
 $847万
 $19,845/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -66210,7 +66210,7 @@
           <t>G | 306呎 (1房)
 $506万
 $16,539/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -66218,7 +66218,7 @@
           <t>H | 305呎 (1房)
 $504万
 $16,511/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -66226,7 +66226,7 @@
           <t>J | 305呎 (1房)
 $528万
 $17,321/呎
-(25年-03月)</t>
+(25年-03月-16日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -66234,7 +66234,7 @@
           <t>K | 308呎 (1房)
 $520万
 $16,873/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -66242,7 +66242,7 @@
           <t>L | 430呎 (2房)
 $859万
 $19,984/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -66250,7 +66250,7 @@
           <t>M | 481呎 (2房)
 $977万
 $20,316/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -66258,7 +66258,7 @@
           <t>N | 288呎 (1房)
 $485万
 $16,847/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -66273,7 +66273,7 @@
           <t>A | 771呎 (3房)
 $1660万
 $21,530/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -66281,7 +66281,7 @@
           <t>B | 536呎 (2房)
 $1007万
 $18,795/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -66289,7 +66289,7 @@
           <t>C | 498呎 (2房)
 $1079万
 $21,663/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -66297,7 +66297,7 @@
           <t>D | 534呎 (2房)
 $978万
 $18,324/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -66305,7 +66305,7 @@
           <t>E | 437呎 (2房)
 $818万
 $18,709/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -66313,7 +66313,7 @@
           <t>F | 427呎 (2房)
 $846万
 $19,806/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -66321,7 +66321,7 @@
           <t>G | 306呎 (1房)
 $627万
 $20,497/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -66329,7 +66329,7 @@
           <t>H | 305呎 (1房)
 $501万
 $16,430/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -66337,7 +66337,7 @@
           <t>J | 305呎 (1房)
 $525万
 $17,203/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -66345,7 +66345,7 @@
           <t>K | 308呎 (1房)
 $517万
 $16,779/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -66353,7 +66353,7 @@
           <t>L | 430呎 (2房)
 $857万
 $19,928/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -66361,7 +66361,7 @@
           <t>M | 481呎 (2房)
 $973万
 $20,237/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -66369,7 +66369,7 @@
           <t>N | 285呎 (1房)
 $483万
 $16,961/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -66384,7 +66384,7 @@
           <t>A | 771呎 (3房)
 $1683万
 $21,829/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -66392,7 +66392,7 @@
           <t>B | 536呎 (2房)
 $1021万
 $19,050/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -66400,7 +66400,7 @@
           <t>C | 497呎 (2房)
 $1081万
 $21,746/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -66408,7 +66408,7 @@
           <t>D | 534呎 (2房)
 $976万
 $18,270/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -66416,7 +66416,7 @@
           <t>E | 437呎 (2房)
 $818万
 $18,725/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -66424,7 +66424,7 @@
           <t>F | 427呎 (2房)
 $844万
 $19,770/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -66432,7 +66432,7 @@
           <t>G | 306呎 (1房)
 $503万
 $16,428/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -66440,7 +66440,7 @@
           <t>H | 305呎 (1房)
 $504万
 $16,531/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -66448,7 +66448,7 @@
           <t>J | 305呎 (1房)
 $525万
 $17,223/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -66456,7 +66456,7 @@
           <t>K | 308呎 (1房)
 $516万
 $16,747/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -66464,7 +66464,7 @@
           <t>L | 430呎 (2房)
 $855万
 $19,888/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -66472,7 +66472,7 @@
           <t>M | 481呎 (2房)
 $971万
 $20,191/呎
-(23年-11月)</t>
+(23年-11月-20日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -66480,7 +66480,7 @@
           <t>N | 288呎 (1房)
 $492万
 $17,066/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -66495,7 +66495,7 @@
           <t>A | 771呎 (3房)
 $1626万
 $21,089/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -66503,7 +66503,7 @@
           <t>B | 536呎 (2房)
 $997万
 $18,601/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -66519,7 +66519,7 @@
           <t>D | 534呎 (2房)
 $980万
 $18,350/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -66527,7 +66527,7 @@
           <t>E | 437呎 (2房)
 $806万
 $18,449/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -66535,7 +66535,7 @@
           <t>F | 427呎 (2房)
 $842万
 $19,721/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -66543,7 +66543,7 @@
           <t>G | 306呎 (1房)
 $502万
 $16,399/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -66551,7 +66551,7 @@
           <t>H | 305呎 (1房)
 $499万
 $16,367/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -66559,7 +66559,7 @@
           <t>J | 305呎 (1房)
 $522万
 $17,108/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -66567,7 +66567,7 @@
           <t>K | 308呎 (1房)
 $515万
 $16,708/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -66575,7 +66575,7 @@
           <t>L | 430呎 (2房)
 $853万
 $19,847/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -66583,7 +66583,7 @@
           <t>M | 481呎 (2房)
 $969万
 $20,150/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -66591,7 +66591,7 @@
           <t>N | 288呎 (1房)
 $490万
 $17,017/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
           <t>A | 774呎 (3房)
 $1759万
 $22,724/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -66614,7 +66614,7 @@
           <t>B | 536呎 (2房)
 $1001万
 $18,679/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -66622,7 +66622,7 @@
           <t>C | 497呎 (2房)
 $1071万
 $21,545/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -66630,7 +66630,7 @@
           <t>D | 534呎 (2房)
 $970万
 $18,161/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -66638,7 +66638,7 @@
           <t>E | 437呎 (2房)
 $799万
 $18,293/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -66646,7 +66646,7 @@
           <t>F | 427呎 (2房)
 $840万
 $19,660/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -66654,7 +66654,7 @@
           <t>G | 306呎 (1房)
 $501万
 $16,366/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -66662,7 +66662,7 @@
           <t>H | 305呎 (1房)
 $498万
 $16,331/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -66670,7 +66670,7 @@
           <t>J | 306呎 (1房)
 $524万
 $17,131/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -66678,7 +66678,7 @@
           <t>K | 308呎 (1房)
 $514万
 $16,675/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -66686,7 +66686,7 @@
           <t>L | 430呎 (2房)
 $852万
 $19,805/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -66694,7 +66694,7 @@
           <t>M | 481呎 (2房)
 $967万
 $20,108/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -66702,7 +66702,7 @@
           <t>N | 288呎 (1房)
 $479万
 $16,628/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -66717,7 +66717,7 @@
           <t>A | 771呎 (3房)
 $1650万
 $21,401/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -66725,7 +66725,7 @@
           <t>B | 536呎 (2房)
 $991万
 $18,494/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -66733,7 +66733,7 @@
           <t>C | 498呎 (2房)
 $996万
 $20,000/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -66741,7 +66741,7 @@
           <t>D | 534呎 (2房)
 $967万
 $18,110/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -66749,7 +66749,7 @@
           <t>E | 437呎 (2房)
 $800万
 $18,311/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -66757,7 +66757,7 @@
           <t>F | 427呎 (2房)
 $837万
 $19,597/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -66765,7 +66765,7 @@
           <t>G | 306呎 (1房)
 $500万
 $16,330/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -66773,7 +66773,7 @@
           <t>H | 305呎 (1房)
 $497万
 $16,298/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -66781,7 +66781,7 @@
           <t>J | 305呎 (1房)
 $519万
 $17,010/呎
-(25年-03月)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -66789,7 +66789,7 @@
           <t>K | 308呎 (1房)
 $641万
 $20,805/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -66797,7 +66797,7 @@
           <t>L | 430呎 (2房)
 $850万
 $19,767/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -66805,7 +66805,7 @@
           <t>M | 481呎 (2房)
 $965万
 $20,067/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -66813,7 +66813,7 @@
           <t>N | 288呎 (1房)
 $477万
 $16,576/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -66828,7 +66828,7 @@
           <t>A | 774呎 (3房)
 $1697万
 $21,922/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -66836,7 +66836,7 @@
           <t>B | 536呎 (2房)
 $1002万
 $18,700/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -66844,7 +66844,7 @@
           <t>C | 498呎 (2房)
 $997万
 $20,016/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -66852,7 +66852,7 @@
           <t>D | 534呎 (2房)
 $964万
 $18,058/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -66860,7 +66860,7 @@
           <t>E | 437呎 (2房)
 $796万
 $18,217/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -66868,7 +66868,7 @@
           <t>F | 427呎 (2房)
 $835万
 $19,560/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -66876,7 +66876,7 @@
           <t>G | 306呎 (1房)
 $499万
 $16,310/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -66884,7 +66884,7 @@
           <t>H | 305呎 (1房)
 $500万
 $16,393/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -66892,7 +66892,7 @@
           <t>J | 305呎 (1房)
 $519万
 $17,026/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -66900,7 +66900,7 @@
           <t>K | 308呎 (1房)
 $512万
 $16,607/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -66908,7 +66908,7 @@
           <t>L | 429呎 (2房)
 $861万
 $20,065/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -66916,7 +66916,7 @@
           <t>M | 481呎 (2房)
 $963万
 $20,025/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -66924,7 +66924,7 @@
           <t>N | 285呎 (1房)
 $476万
 $16,702/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -66939,7 +66939,7 @@
           <t>A | 771呎 (3房)
 $1666万
 $21,606/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -66947,7 +66947,7 @@
           <t>B | 536呎 (2房)
 $988万
 $18,437/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -66955,7 +66955,7 @@
           <t>C | 497呎 (2房)
 $1001万
 $20,137/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -66963,7 +66963,7 @@
           <t>D | 534呎 (2房)
 $964万
 $18,058/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -66971,7 +66971,7 @@
           <t>E | 437呎 (2房)
 $819万
 $18,746/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -66979,7 +66979,7 @@
           <t>F | 427呎 (2房)
 $835万
 $19,560/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -66987,7 +66987,7 @@
           <t>G | 306呎 (1房)
 $621万
 $20,307/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -66995,7 +66995,7 @@
           <t>H | 305呎 (1房)
 $500万
 $16,393/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -67003,7 +67003,7 @@
           <t>J | 306呎 (1房)
 $592万
 $19,337/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -67011,7 +67011,7 @@
           <t>K | 308呎 (1房)
 $512万
 $16,607/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -67019,7 +67019,7 @@
           <t>L | 430呎 (2房)
 $848万
 $19,721/呎
-(23年-11月)</t>
+(23年-11月-19日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -67027,7 +67027,7 @@
           <t>M | 481呎 (2房)
 $963万
 $20,025/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -67035,7 +67035,7 @@
           <t>N | 288呎 (1房)
 $486万
 $16,865/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -67050,7 +67050,7 @@
           <t>A | 771呎 (3房)
 $1681万
 $21,800/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -67058,7 +67058,7 @@
           <t>B | 536呎 (2房)
 $993万
 $18,522/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -67066,7 +67066,7 @@
           <t>C | 498呎 (2房)
 $981万
 $19,701/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -67074,7 +67074,7 @@
           <t>D | 534呎 (2房)
 $954万
 $17,875/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -67082,7 +67082,7 @@
           <t>E | 437呎 (2房)
 $797万
 $18,231/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -67090,7 +67090,7 @@
           <t>F | 427呎 (2房)
 $829万
 $19,412/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -67098,7 +67098,7 @@
           <t>G | 306呎 (1房)
 $496万
 $16,199/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -67106,7 +67106,7 @@
           <t>H | 305呎 (1房)
 $493万
 $16,161/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -67114,7 +67114,7 @@
           <t>J | 305呎 (1房)
 $514万
 $16,846/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -67122,7 +67122,7 @@
           <t>K | 308呎 (1房)
 $508万
 $16,484/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -67130,7 +67130,7 @@
           <t>L | 430呎 (2房)
 $844万
 $19,619/呎
-(23年-11月)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -67138,7 +67138,7 @@
           <t>M | 481呎 (2房)
 $868万
 $18,037/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -67146,7 +67146,7 @@
           <t>N | 288呎 (1房)
 $472万
 $16,392/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -67161,7 +67161,7 @@
           <t>A | 774呎 (3房)
 $1661万
 $21,460/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -67169,7 +67169,7 @@
           <t>B | 536呎 (2房)
 $980万
 $18,282/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -67177,7 +67177,7 @@
           <t>C | 498呎 (2房)
 $976万
 $19,606/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -67185,7 +67185,7 @@
           <t>D | 534呎 (2房)
 $948万
 $17,760/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -67193,7 +67193,7 @@
           <t>E | 437呎 (2房)
 $792万
 $18,114/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -67201,7 +67201,7 @@
           <t>F | 427呎 (2房)
 $790万
 $18,501/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -67209,7 +67209,7 @@
           <t>G | 306呎 (1房)
 $494万
 $16,134/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -67217,7 +67217,7 @@
           <t>H | 305呎 (1房)
 $491万
 $16,089/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -67225,7 +67225,7 @@
           <t>J | 305呎 (1房)
 $516万
 $16,925/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -67233,7 +67233,7 @@
           <t>K | 308呎 (1房)
 $506万
 $16,425/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -67241,7 +67241,7 @@
           <t>L | 430呎 (2房)
 $842万
 $19,572/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -67249,7 +67249,7 @@
           <t>M | 481呎 (2房)
 $956万
 $19,865/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -67257,7 +67257,7 @@
           <t>N | 288呎 (1房)
 $471万
 $16,365/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
     </row>
@@ -67272,7 +67272,7 @@
           <t>A | 771呎 (3房)
 $1608万
 $20,856/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -67280,7 +67280,7 @@
           <t>B | 536呎 (2房)
 $992万
 $18,498/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -67288,7 +67288,7 @@
           <t>C | 497呎 (2房)
 $999万
 $20,097/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -67296,7 +67296,7 @@
           <t>D | 534呎 (2房)
 $954万
 $17,873/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -67304,7 +67304,7 @@
           <t>E | 437呎 (2房)
 $797万
 $18,243/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -67312,7 +67312,7 @@
           <t>F | 427呎 (2房)
 $726万
 $16,998/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -67320,7 +67320,7 @@
           <t>G | 306呎 (1房)
 $498万
 $16,258/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -67328,7 +67328,7 @@
           <t>H | 305呎 (1房)
 $493万
 $16,167/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -67336,7 +67336,7 @@
           <t>J | 305呎 (1房)
 $520万
 $17,049/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -67344,7 +67344,7 @@
           <t>K | 308呎 (1房)
 $505万
 $16,390/呎
-(25年-01月)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -67352,7 +67352,7 @@
           <t>L | 430呎 (2房)
 $746万
 $17,351/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -67360,7 +67360,7 @@
           <t>M | 481呎 (2房)
 $846万
 $17,593/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -67368,7 +67368,7 @@
           <t>N | 288呎 (1房)
 $479万
 $16,628/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -67383,7 +67383,7 @@
           <t>A | 774呎 (3房)
 $1660万
 $21,444/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -67391,7 +67391,7 @@
           <t>B | 536呎 (2房)
 $978万
 $18,241/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -67399,7 +67399,7 @@
           <t>C | 497呎 (2房)
 $974万
 $19,594/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -67407,7 +67407,7 @@
           <t>D | 534呎 (2房)
 $939万
 $17,590/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -67415,7 +67415,7 @@
           <t>E | 437呎 (2房)
 $787万
 $18,011/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -67423,7 +67423,7 @@
           <t>F | 427呎 (2房)
 $822万
 $19,251/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -67431,7 +67431,7 @@
           <t>G | 306呎 (1房)
 $490万
 $16,007/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -67439,7 +67439,7 @@
           <t>H | 305呎 (1房)
 $488万
 $16,003/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -67447,7 +67447,7 @@
           <t>J | 305呎 (1房)
 $509万
 $16,682/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -67455,7 +67455,7 @@
           <t>K | 308呎 (1房)
 $502万
 $16,299/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -67463,7 +67463,7 @@
           <t>L | 430呎 (2房)
 $839万
 $19,507/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -67471,7 +67471,7 @@
           <t>M | 481呎 (2房)
 $836万
 $17,380/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -67479,7 +67479,7 @@
           <t>N | 285呎 (1房)
 $467万
 $16,400/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -67494,7 +67494,7 @@
           <t>A | 774呎 (3房)
 $1681万
 $21,716/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -67502,7 +67502,7 @@
           <t>B | 536呎 (2房)
 $983万
 $18,343/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -67510,7 +67510,7 @@
           <t>C | 497呎 (2房)
 $985万
 $19,815/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -67518,7 +67518,7 @@
           <t>D | 534呎 (2房)
 $983万
 $18,404/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -67526,7 +67526,7 @@
           <t>E | 437呎 (2房)
 $788万
 $18,043/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -67534,7 +67534,7 @@
           <t>F | 427呎 (2房)
 $714万
 $16,733/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -67542,7 +67542,7 @@
           <t>G | 306呎 (1房)
 $488万
 $15,941/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -67550,7 +67550,7 @@
           <t>H | 305呎 (1房)
 $523万
 $17,148/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -67558,7 +67558,7 @@
           <t>J | 305呎 (1房)
 $510万
 $16,738/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -67566,7 +67566,7 @@
           <t>K | 308呎 (1房)
 $499万
 $16,205/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -67574,7 +67574,7 @@
           <t>L | 430呎 (2房)
 $837万
 $19,458/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -67582,7 +67582,7 @@
           <t>M | 481呎 (2房)
 $835万
 $17,356/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="N33" s="21" t="inlineStr">
@@ -67590,7 +67590,7 @@
           <t>N | 288呎 (1房)
 $465万
 $16,153/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -67605,7 +67605,7 @@
           <t>A | 771呎 (3房)
 $1681万
 $21,800/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -67613,7 +67613,7 @@
           <t>B | 536呎 (2房)
 $978万
 $18,239/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -67621,7 +67621,7 @@
           <t>C | 497呎 (2房)
 $978万
 $19,674/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -67629,7 +67629,7 @@
           <t>D | 534呎 (2房)
 $994万
 $18,609/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -67637,7 +67637,7 @@
           <t>E | 437呎 (2房)
 $787万
 $18,014/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -67645,7 +67645,7 @@
           <t>F | 427呎 (2房)
 $711万
 $16,656/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -67653,7 +67653,7 @@
           <t>G | 306呎 (1房)
 $487万
 $15,928/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -67661,7 +67661,7 @@
           <t>H | 305呎 (1房)
 $520万
 $17,059/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
@@ -67669,7 +67669,7 @@
           <t>J | 305呎 (1房)
 $534万
 $17,492/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -67677,7 +67677,7 @@
           <t>K | 308呎 (1房)
 $503万
 $16,328/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -67685,7 +67685,7 @@
           <t>L | 430呎 (2房)
 $729万
 $16,949/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -67693,7 +67693,7 @@
           <t>M | 481呎 (2房)
 $831万
 $17,285/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="N34" s="21" t="inlineStr">
@@ -67701,7 +67701,7 @@
           <t>N | 288呎 (1房)
 $461万
 $15,997/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -67893,7 +67893,7 @@
           <t>D | 477呎 (2房)
 $1289万
 $27,019/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -67901,7 +67901,7 @@
           <t>E | 553呎 (2房)
 $1289万
 $23,315/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -67948,7 +67948,7 @@
           <t>A | 586呎 (3房)
 $1429万
 $24,389/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -68012,7 +68012,7 @@
           <t>J | 537呎 (2房)
 $1454万
 $27,073/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -68027,7 +68027,7 @@
           <t>A | 586呎 (3房)
 $1465万
 $25,000/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -68059,7 +68059,7 @@
           <t>E | 553呎 (2房)
 $1278万
 $23,105/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -68091,7 +68091,7 @@
           <t>J | 538呎 (2房)
 $1250万
 $23,234/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -68106,7 +68106,7 @@
           <t>A | 586呎 (3房)
 $1432万
 $24,437/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -68114,7 +68114,7 @@
           <t>B | 474呎 (2房)
 $1064万
 $22,443/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -68122,7 +68122,7 @@
           <t>C | 450呎 (2房)
 $999万
 $22,196/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -68138,7 +68138,7 @@
           <t>E | 553呎 (2房)
 $1208万
 $21,852/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -68154,7 +68154,7 @@
           <t>G | 432呎 (2房)
 $823万
 $19,051/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -68162,7 +68162,7 @@
           <t>H | 432呎 (2房)
 $812万
 $18,789/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -68170,7 +68170,7 @@
           <t>J | 538呎 (2房)
 $1148万
 $21,338/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
     </row>
@@ -68185,7 +68185,7 @@
           <t>A | 586呎 (3房)
 $1407万
 $24,007/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -68193,7 +68193,7 @@
           <t>B | 474呎 (2房)
 $993万
 $20,947/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -68201,7 +68201,7 @@
           <t>C | 450呎 (2房)
 $993万
 $22,062/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -68217,7 +68217,7 @@
           <t>E | 553呎 (2房)
 $1229万
 $22,221/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -68225,7 +68225,7 @@
           <t>F | 307呎 (1房)
 $634万
 $20,645/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -68233,7 +68233,7 @@
           <t>G | 432呎 (2房)
 $788万
 $18,243/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -68241,7 +68241,7 @@
           <t>H | 432呎 (2房)
 $807万
 $18,688/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -68249,7 +68249,7 @@
           <t>J | 538呎 (2房)
 $1130万
 $21,000/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -68264,7 +68264,7 @@
           <t>A | 586呎 (3房)
 $1408万
 $24,027/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -68272,7 +68272,7 @@
           <t>B | 474呎 (2房)
 $988万
 $20,842/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -68296,7 +68296,7 @@
           <t>E | 553呎 (2房)
 $1201万
 $21,723/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -68304,7 +68304,7 @@
           <t>F | 307呎 (1房)
 $631万
 $20,547/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -68312,7 +68312,7 @@
           <t>G | 432呎 (2房)
 $811万
 $18,778/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -68320,7 +68320,7 @@
           <t>H | 432呎 (2房)
 $806万
 $18,653/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -68328,7 +68328,7 @@
           <t>J | 538呎 (2房)
 $1128万
 $20,967/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -68343,7 +68343,7 @@
           <t>A | 586呎 (3房)
 $1348万
 $23,003/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -68351,7 +68351,7 @@
           <t>B | 474呎 (2房)
 $960万
 $20,245/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -68359,7 +68359,7 @@
           <t>C | 450呎 (2房)
 $987万
 $21,929/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -68375,7 +68375,7 @@
           <t>E | 553呎 (2房)
 $1244万
 $22,503/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -68383,7 +68383,7 @@
           <t>F | 307呎 (1房)
 $626万
 $20,375/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -68391,7 +68391,7 @@
           <t>G | 432呎 (2房)
 $770万
 $17,824/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -68399,7 +68399,7 @@
           <t>H | 432呎 (2房)
 $803万
 $18,590/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -68407,7 +68407,7 @@
           <t>J | 538呎 (2房)
 $1087万
 $20,201/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -68422,7 +68422,7 @@
           <t>A | 586呎 (3房)
 $1298万
 $22,150/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -68430,7 +68430,7 @@
           <t>B | 474呎 (2房)
 $955万
 $20,141/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -68438,7 +68438,7 @@
           <t>C | 450呎 (2房)
 $977万
 $21,707/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -68454,7 +68454,7 @@
           <t>E | 553呎 (2房)
 $1234万
 $22,311/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -68462,7 +68462,7 @@
           <t>F | 307呎 (1房)
 $646万
 $21,026/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -68470,7 +68470,7 @@
           <t>G | 432呎 (2房)
 $760万
 $17,583/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -68478,7 +68478,7 @@
           <t>H | 431呎 (2房)
 $757万
 $17,568/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -68486,7 +68486,7 @@
           <t>J | 537呎 (2房)
 $1060万
 $19,739/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -68501,7 +68501,7 @@
           <t>A | 586呎 (3房)
 $1293万
 $22,070/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -68509,7 +68509,7 @@
           <t>B | 474呎 (2房)
 $978万
 $20,627/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -68517,7 +68517,7 @@
           <t>C | 450呎 (2房)
 $917万
 $20,373/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -68533,7 +68533,7 @@
           <t>E | 553呎 (2房)
 $1221万
 $22,083/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -68541,7 +68541,7 @@
           <t>F | 307呎 (1房)
 $618万
 $20,124/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -68549,7 +68549,7 @@
           <t>G | 432呎 (2房)
 $778万
 $18,007/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -68557,7 +68557,7 @@
           <t>H | 431呎 (2房)
 $759万
 $17,615/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -68565,7 +68565,7 @@
           <t>J | 538呎 (2房)
 $1052万
 $19,548/呎
-(25年-03月)</t>
+(25年-03月-09日)</t>
         </is>
       </c>
     </row>
@@ -68580,7 +68580,7 @@
           <t>A | 586呎 (3房)
 $1293万
 $22,058/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -68588,7 +68588,7 @@
           <t>B | 474呎 (2房)
 $938万
 $19,781/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -68596,7 +68596,7 @@
           <t>C | 450呎 (2房)
 $914万
 $20,318/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -68612,7 +68612,7 @@
           <t>E | 553呎 (2房)
 $1175万
 $21,248/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -68620,7 +68620,7 @@
           <t>F | 307呎 (1房)
 $602万
 $19,603/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -68628,7 +68628,7 @@
           <t>G | 432呎 (2房)
 $755万
 $17,468/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -68636,7 +68636,7 @@
           <t>H | 431呎 (2房)
 $760万
 $17,643/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -68644,7 +68644,7 @@
           <t>J | 538呎 (2房)
 $1067万
 $19,840/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -68659,7 +68659,7 @@
           <t>A | 586呎 (3房)
 $1299万
 $22,162/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -68667,7 +68667,7 @@
           <t>B | 474呎 (2房)
 $956万
 $20,169/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -68675,7 +68675,7 @@
           <t>C | 450呎 (2房)
 $912万
 $20,256/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -68683,7 +68683,7 @@
           <t>D | 477呎 (2房)
 $1054万
 $22,092/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -68691,7 +68691,7 @@
           <t>E | 553呎 (2房)
 $1176万
 $21,266/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -68699,7 +68699,7 @@
           <t>F | 307呎 (1房)
 $588万
 $19,150/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -68707,7 +68707,7 @@
           <t>G | 432呎 (2房)
 $753万
 $17,431/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -68715,7 +68715,7 @@
           <t>H | 431呎 (2房)
 $786万
 $18,230/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -68723,7 +68723,7 @@
           <t>J | 538呎 (2房)
 $1049万
 $19,498/呎
-(25年-03月)</t>
+(25年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -68738,7 +68738,7 @@
           <t>A | 586呎 (3房)
 $1276万
 $21,776/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -68746,7 +68746,7 @@
           <t>B | 474呎 (2房)
 $952万
 $20,093/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -68754,7 +68754,7 @@
           <t>C | 450呎 (2房)
 $909万
 $20,200/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -68762,7 +68762,7 @@
           <t>D | 477呎 (2房)
 $1048万
 $21,966/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -68770,7 +68770,7 @@
           <t>E | 553呎 (2房)
 $1210万
 $21,888/呎
-(23年-11月)</t>
+(23年-11月-19日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -68778,7 +68778,7 @@
           <t>F | 307呎 (1房)
 $585万
 $19,046/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -68786,7 +68786,7 @@
           <t>G | 432呎 (2房)
 $752万
 $17,396/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -68794,7 +68794,7 @@
           <t>H | 431呎 (2房)
 $749万
 $17,387/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -68802,7 +68802,7 @@
           <t>J | 538呎 (2房)
 $1061万
 $19,723/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -68817,7 +68817,7 @@
           <t>A | 586呎 (3房)
 $1508万
 $25,741/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -68825,7 +68825,7 @@
           <t>B | 474呎 (2房)
 $926万
 $19,540/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -68833,7 +68833,7 @@
           <t>C | 450呎 (2房)
 $906万
 $20,144/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -68849,7 +68849,7 @@
           <t>E | 553呎 (2房)
 $1207万
 $21,823/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -68857,7 +68857,7 @@
           <t>F | 307呎 (1房)
 $605万
 $19,710/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -68865,7 +68865,7 @@
           <t>G | 432呎 (2房)
 $750万
 $17,361/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -68873,7 +68873,7 @@
           <t>H | 431呎 (2房)
 $785万
 $18,216/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -68881,7 +68881,7 @@
           <t>J | 538呎 (2房)
 $1036万
 $19,247/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -68896,7 +68896,7 @@
           <t>A | 586呎 (3房)
 $1279万
 $21,821/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -68904,7 +68904,7 @@
           <t>B | 474呎 (2房)
 $927万
 $19,553/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -68912,7 +68912,7 @@
           <t>C | 450呎 (2房)
 $904万
 $20,087/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -68928,7 +68928,7 @@
           <t>E | 553呎 (2房)
 $1203万
 $21,758/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -68936,7 +68936,7 @@
           <t>F | 307呎 (1房)
 $602万
 $19,612/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -68944,7 +68944,7 @@
           <t>G | 432呎 (2房)
 $746万
 $17,269/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -68952,7 +68952,7 @@
           <t>H | 432呎 (2房)
 $781万
 $18,076/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -68960,7 +68960,7 @@
           <t>J | 538呎 (2房)
 $1055万
 $19,602/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -68975,7 +68975,7 @@
           <t>A | 586呎 (3房)
 $1280万
 $21,838/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -68983,7 +68983,7 @@
           <t>B | 474呎 (2房)
 $914万
 $19,287/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -68991,7 +68991,7 @@
           <t>C | 450呎 (2房)
 $901万
 $20,027/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -69007,7 +69007,7 @@
           <t>E | 553呎 (2房)
 $1151万
 $20,812/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -69015,7 +69015,7 @@
           <t>F | 307呎 (1房)
 $599万
 $19,508/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -69023,7 +69023,7 @@
           <t>G | 432呎 (2房)
 $747万
 $17,292/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -69031,7 +69031,7 @@
           <t>H | 431呎 (2房)
 $750万
 $17,408/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -69039,7 +69039,7 @@
           <t>J | 538呎 (2房)
 $1026万
 $19,061/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -69054,7 +69054,7 @@
           <t>A | 586呎 (3房)
 $1290万
 $22,014/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -69062,7 +69062,7 @@
           <t>B | 474呎 (2房)
 $918万
 $19,357/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -69070,7 +69070,7 @@
           <t>C | 450呎 (2房)
 $898万
 $19,958/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -69086,7 +69086,7 @@
           <t>E | 553呎 (2房)
 $1162万
 $21,016/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -69094,7 +69094,7 @@
           <t>F | 307呎 (1房)
 $597万
 $19,446/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -69102,7 +69102,7 @@
           <t>G | 432呎 (2房)
 $739万
 $17,106/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -69110,7 +69110,7 @@
           <t>H | 432呎 (2房)
 $777万
 $17,981/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -69118,7 +69118,7 @@
           <t>J | 538呎 (2房)
 $1026万
 $19,061/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -69133,7 +69133,7 @@
           <t>A | 586呎 (3房)
 $1359万
 $23,188/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -69141,7 +69141,7 @@
           <t>B | 474呎 (2房)
 $880万
 $18,557/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -69149,7 +69149,7 @@
           <t>C | 450呎 (2房)
 $862万
 $19,164/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -69157,7 +69157,7 @@
           <t>D | 477呎 (2房)
 $1019万
 $21,358/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -69165,7 +69165,7 @@
           <t>E | 553呎 (2房)
 $1187万
 $21,463/呎
-(23年-11月)</t>
+(23年-11月-26日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -69173,7 +69173,7 @@
           <t>F | 307呎 (1房)
 $512万
 $16,681/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -69181,7 +69181,7 @@
           <t>G | 432呎 (2房)
 $707万
 $16,370/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -69189,7 +69189,7 @@
           <t>H | 431呎 (2房)
 $730万
 $16,926/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -69197,7 +69197,7 @@
           <t>J | 538呎 (2房)
 $982万
 $18,249/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -69212,7 +69212,7 @@
           <t>A | 586呎 (3房)
 $1478万
 $25,217/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -69220,7 +69220,7 @@
           <t>B | 474呎 (2房)
 $875万
 $18,466/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -69228,7 +69228,7 @@
           <t>C | 450呎 (2房)
 $974万
 $21,651/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -69236,7 +69236,7 @@
           <t>D | 477呎 (2房)
 $961万
 $20,143/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -69244,7 +69244,7 @@
           <t>E | 553呎 (2房)
 $1181万
 $21,353/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -69252,7 +69252,7 @@
           <t>F | 307呎 (1房)
 $616万
 $20,072/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -69260,7 +69260,7 @@
           <t>G | 432呎 (2房)
 $706万
 $16,338/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -69268,7 +69268,7 @@
           <t>H | 431呎 (2房)
 $728万
 $16,891/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -69276,7 +69276,7 @@
           <t>J | 538呎 (2房)
 $976万
 $18,147/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -69291,7 +69291,7 @@
           <t>A | 586呎 (3房)
 $1216万
 $20,746/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -69299,7 +69299,7 @@
           <t>B | 474呎 (2房)
 $879万
 $18,553/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -69307,7 +69307,7 @@
           <t>C | 450呎 (2房)
 $884万
 $19,633/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -69323,7 +69323,7 @@
           <t>E | 553呎 (2房)
 $1177万
 $21,289/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -69331,7 +69331,7 @@
           <t>F | 307呎 (1房)
 $503万
 $16,397/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -69339,7 +69339,7 @@
           <t>G | 432呎 (2房)
 $704万
 $16,306/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -69347,7 +69347,7 @@
           <t>H | 431呎 (2房)
 $839万
 $19,462/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -69355,7 +69355,7 @@
           <t>J | 538呎 (2房)
 $973万
 $18,093/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -69370,7 +69370,7 @@
           <t>A | 586呎 (3房)
 $1222万
 $20,846/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -69378,7 +69378,7 @@
           <t>B | 474呎 (2房)
 $870万
 $18,361/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -69386,7 +69386,7 @@
           <t>C | 450呎 (2房)
 $848万
 $18,833/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -69402,7 +69402,7 @@
           <t>E | 553呎 (2房)
 $1174万
 $21,226/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -69410,7 +69410,7 @@
           <t>F | 307呎 (1房)
 $502万
 $16,365/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -69418,7 +69418,7 @@
           <t>G | 432呎 (2房)
 $703万
 $16,269/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -69426,7 +69426,7 @@
           <t>H | 432呎 (2房)
 $714万
 $16,528/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -69434,7 +69434,7 @@
           <t>J | 538呎 (2房)
 $989万
 $18,375/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -69449,7 +69449,7 @@
           <t>A | 586呎 (3房)
 $1200万
 $20,478/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -69457,7 +69457,7 @@
           <t>B | 474呎 (2房)
 $964万
 $20,333/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -69465,7 +69465,7 @@
           <t>C | 450呎 (2房)
 $878万
 $19,520/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -69473,7 +69473,7 @@
           <t>D | 477呎 (2房)
 $999万
 $20,939/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -69481,7 +69481,7 @@
           <t>E | 553呎 (2房)
 $1170万
 $21,161/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -69489,7 +69489,7 @@
           <t>F | 307呎 (1房)
 $612万
 $19,948/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -69497,7 +69497,7 @@
           <t>G | 432呎 (2房)
 $701万
 $16,234/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -69505,7 +69505,7 @@
           <t>H | 431呎 (2房)
 $719万
 $16,691/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -69513,7 +69513,7 @@
           <t>J | 538呎 (2房)
 $986万
 $18,320/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -69528,7 +69528,7 @@
           <t>A | 586呎 (3房)
 $1206万
 $20,577/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -69536,7 +69536,7 @@
           <t>B | 474呎 (2房)
 $872万
 $18,392/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -69544,7 +69544,7 @@
           <t>C | 450呎 (2房)
 $860万
 $19,111/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -69552,7 +69552,7 @@
           <t>D | 477呎 (2房)
 $937万
 $19,639/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -69560,7 +69560,7 @@
           <t>E | 553呎 (2房)
 $1167万
 $21,098/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -69568,7 +69568,7 @@
           <t>F | 307呎 (1房)
 $500万
 $16,303/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -69576,7 +69576,7 @@
           <t>G | 432呎 (2房)
 $700万
 $16,201/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -69584,7 +69584,7 @@
           <t>H | 431呎 (2房)
 $709万
 $16,441/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -69592,7 +69592,7 @@
           <t>J | 538呎 (2房)
 $965万
 $17,929/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -69607,7 +69607,7 @@
           <t>A | 586呎 (3房)
 $1193万
 $20,363/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -69615,7 +69615,7 @@
           <t>B | 474呎 (2房)
 $879万
 $18,546/呎
-(25年-01月)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -69623,7 +69623,7 @@
           <t>C | 450呎 (2房)
 $960万
 $21,340/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -69631,7 +69631,7 @@
           <t>D | 477呎 (2房)
 $931万
 $19,514/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -69639,7 +69639,7 @@
           <t>E | 553呎 (2房)
 $1134万
 $20,510/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -69647,7 +69647,7 @@
           <t>F | 307呎 (1房)
 $499万
 $16,267/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -69655,7 +69655,7 @@
           <t>G | 432呎 (2房)
 $698万
 $16,167/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -69663,7 +69663,7 @@
           <t>H | 431呎 (2房)
 $710万
 $16,471/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -69671,7 +69671,7 @@
           <t>J | 538呎 (2房)
 $962万
 $17,875/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -69686,7 +69686,7 @@
           <t>A | 586呎 (3房)
 $1227万
 $20,935/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -69694,7 +69694,7 @@
           <t>B | 474呎 (2房)
 $863万
 $18,205/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -69702,7 +69702,7 @@
           <t>C | 450呎 (2房)
 $867万
 $19,273/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -69710,7 +69710,7 @@
           <t>D | 477呎 (2房)
 $984万
 $20,625/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -69718,7 +69718,7 @@
           <t>E | 553呎 (2房)
 $1134万
 $20,510/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -69726,7 +69726,7 @@
           <t>F | 307呎 (1房)
 $499万
 $16,267/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -69734,7 +69734,7 @@
           <t>G | 432呎 (2房)
 $790万
 $18,287/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -69742,7 +69742,7 @@
           <t>H | 431呎 (2房)
 $707万
 $16,411/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -69750,7 +69750,7 @@
           <t>J | 537呎 (2房)
 $962万
 $17,909/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -69765,7 +69765,7 @@
           <t>A | 586呎 (3房)
 $1265万
 $21,587/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -69773,7 +69773,7 @@
           <t>B | 474呎 (2房)
 $894万
 $18,861/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -69781,7 +69781,7 @@
           <t>C | 450呎 (2房)
 $865万
 $19,227/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -69797,7 +69797,7 @@
           <t>E | 553呎 (2房)
 $1150万
 $20,803/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -69805,7 +69805,7 @@
           <t>F | 307呎 (1房)
 $496万
 $16,150/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -69813,7 +69813,7 @@
           <t>G | 432呎 (2房)
 $695万
 $16,095/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -69821,7 +69821,7 @@
           <t>H | 432呎 (2房)
 $701万
 $16,222/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -69829,7 +69829,7 @@
           <t>J | 538呎 (2房)
 $949万
 $17,643/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -69844,7 +69844,7 @@
           <t>A | 586呎 (3房)
 $1188万
 $20,275/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -69852,7 +69852,7 @@
           <t>B | 474呎 (2房)
 $851万
 $17,956/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -69860,7 +69860,7 @@
           <t>C | 450呎 (2房)
 $828万
 $18,407/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -69868,7 +69868,7 @@
           <t>D | 477呎 (2房)
 $992万
 $20,801/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -69876,7 +69876,7 @@
           <t>E | 553呎 (2房)
 $1144万
 $20,685/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -69884,7 +69884,7 @@
           <t>F | 307呎 (1房)
 $579万
 $18,853/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -69892,7 +69892,7 @@
           <t>G | 432呎 (2房)
 $693万
 $16,042/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -69900,7 +69900,7 @@
           <t>H | 431呎 (2房)
 $699万
 $16,225/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -69908,7 +69908,7 @@
           <t>J | 538呎 (2房)
 $945万
 $17,572/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -69923,7 +69923,7 @@
           <t>A | 586呎 (3房)
 $1179万
 $20,123/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -69931,7 +69931,7 @@
           <t>B | 474呎 (2房)
 $866万
 $18,264/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -69939,7 +69939,7 @@
           <t>C | 450呎 (2房)
 $824万
 $18,316/呎
-(25年-02月)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -69947,7 +69947,7 @@
           <t>D | 477呎 (2房)
 $914万
 $19,157/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -69955,7 +69955,7 @@
           <t>E | 553呎 (2房)
 $1085万
 $19,617/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -69963,7 +69963,7 @@
           <t>F | 307呎 (1房)
 $498万
 $16,225/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -69971,7 +69971,7 @@
           <t>G | 432呎 (2房)
 $700万
 $16,199/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -69979,7 +69979,7 @@
           <t>H | 431呎 (2房)
 $700万
 $16,248/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -69987,7 +69987,7 @@
           <t>J | 538呎 (2房)
 $949万
 $17,647/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -70002,7 +70002,7 @@
           <t>A | 586呎 (3房)
 $1173万
 $20,014/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -70010,7 +70010,7 @@
           <t>B | 474呎 (2房)
 $843万
 $17,778/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -70018,7 +70018,7 @@
           <t>C | 450呎 (2房)
 $938万
 $20,833/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -70026,7 +70026,7 @@
           <t>D | 477呎 (2房)
 $907万
 $19,010/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -70034,7 +70034,7 @@
           <t>E | 553呎 (2房)
 $1051万
 $19,013/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -70042,7 +70042,7 @@
           <t>F | 307呎 (1房)
 $491万
 $16,003/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -70050,7 +70050,7 @@
           <t>G | 432呎 (2房)
 $721万
 $16,694/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -70058,7 +70058,7 @@
           <t>H | 431呎 (2房)
 $689万
 $15,986/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -70066,7 +70066,7 @@
           <t>J | 538呎 (2房)
 $930万
 $17,279/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -70081,7 +70081,7 @@
           <t>A | 586呎 (3房)
 $1172万
 $20,000/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -70089,7 +70089,7 @@
           <t>B | 474呎 (2房)
 $863万
 $18,211/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -70097,7 +70097,7 @@
           <t>C | 450呎 (2房)
 $848万
 $18,836/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -70105,7 +70105,7 @@
           <t>D | 477呎 (2房)
 $947万
 $19,849/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -70113,7 +70113,7 @@
           <t>E | 553呎 (2房)
 $1038万
 $18,772/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -70121,7 +70121,7 @@
           <t>F | 307呎 (1房)
 $490万
 $15,958/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -70129,7 +70129,7 @@
           <t>G | 432呎 (2房)
 $688万
 $15,928/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -70137,7 +70137,7 @@
           <t>H | 432呎 (2房)
 $754万
 $17,461/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -70145,7 +70145,7 @@
           <t>J | 538呎 (2房)
 $969万
 $18,011/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -70161,7 +70161,7 @@
           <t>B | 467呎 (2房)
 $856万
 $18,334/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -70169,7 +70169,7 @@
           <t>C | 450呎 (2房)
 $836万
 $18,584/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -70177,7 +70177,7 @@
           <t>D | 477呎 (2房)
 $938万
 $19,660/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -70185,7 +70185,7 @@
           <t>E | 553呎 (2房)
 $1027万
 $18,579/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -70193,7 +70193,7 @@
           <t>F | 307呎 (1房)
 $489万
 $15,928/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -70201,7 +70201,7 @@
           <t>G | 432呎 (2房)
 $688万
 $15,928/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -70209,7 +70209,7 @@
           <t>H | 390呎 (2房)
 $803万
 $20,585/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="J34" s="24" t="inlineStr"/>
@@ -70705,7 +70705,7 @@
           <t>A | 508呎 (2房)
 $1321万
 $26,000/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -70713,7 +70713,7 @@
           <t>B | 482呎 (2房)
 $1254万
 $26,008/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -70753,7 +70753,7 @@
           <t>G | 306呎 (1房)
 $678万
 $22,144/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -70793,7 +70793,7 @@
           <t>M | 307呎 (1房)
 $637万
 $20,743/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -70808,7 +70808,7 @@
           <t>A | 508呎 (2房)
 $1193万
 $23,480/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -70816,7 +70816,7 @@
           <t>B | 482呎 (2房)
 $1161万
 $24,083/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -70824,7 +70824,7 @@
           <t>C | 551呎 (2房)
 $1350万
 $24,501/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -70856,7 +70856,7 @@
           <t>G | 306呎 (1房)
 $672万
 $21,948/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -70896,7 +70896,7 @@
           <t>M | 307呎 (1房)
 $631万
 $20,547/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -70911,7 +70911,7 @@
           <t>A | 508呎 (2房)
 $1257万
 $24,748/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -70959,7 +70959,7 @@
           <t>G | 306呎 (1房)
 $666万
 $21,752/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -70999,7 +70999,7 @@
           <t>M | 307呎 (1房)
 $625万
 $20,352/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -71014,7 +71014,7 @@
           <t>A | 508呎 (2房)
 $1187万
 $23,362/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -71022,7 +71022,7 @@
           <t>B | 482呎 (2房)
 $1150万
 $23,855/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -71054,7 +71054,7 @@
           <t>F | 439呎 (2房)
 $901万
 $20,519/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -71062,7 +71062,7 @@
           <t>G | 306呎 (1房)
 $639万
 $20,876/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -71102,7 +71102,7 @@
           <t>M | 307呎 (1房)
 $596万
 $19,397/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -71117,7 +71117,7 @@
           <t>A | 508呎 (2房)
 $1167万
 $22,969/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -71125,7 +71125,7 @@
           <t>B | 482呎 (2房)
 $1114万
 $23,108/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -71157,7 +71157,7 @@
           <t>F | 439呎 (2房)
 $892万
 $20,314/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -71165,7 +71165,7 @@
           <t>G | 306呎 (1房)
 $633万
 $20,680/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -71205,7 +71205,7 @@
           <t>M | 307呎 (1房)
 $589万
 $19,179/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -71220,7 +71220,7 @@
           <t>A | 508呎 (2房)
 $1119万
 $22,024/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -71228,7 +71228,7 @@
           <t>B | 482呎 (2房)
 $1089万
 $22,589/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -71244,7 +71244,7 @@
           <t>D | 307呎 (1房)
 $716万
 $23,329/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -71252,7 +71252,7 @@
           <t>E | 315呎 (1房)
 $739万
 $23,467/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -71260,7 +71260,7 @@
           <t>F | 439呎 (2房)
 $849万
 $19,335/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -71268,7 +71268,7 @@
           <t>G | 306呎 (1房)
 $627万
 $20,484/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -71276,7 +71276,7 @@
           <t>H | 306呎 (1房)
 $646万
 $21,098/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -71284,7 +71284,7 @@
           <t>J | 308呎 (1房)
 $672万
 $21,812/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -71292,7 +71292,7 @@
           <t>K | 306呎 (1房)
 $647万
 $21,137/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -71300,7 +71300,7 @@
           <t>L | 429呎 (2房)
 $936万
 $21,807/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -71308,7 +71308,7 @@
           <t>M | 307呎 (1房)
 $582万
 $18,971/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -71323,7 +71323,7 @@
           <t>A | 508呎 (2房)
 $1107万
 $21,787/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -71331,7 +71331,7 @@
           <t>B | 482呎 (2房)
 $1077万
 $22,340/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -71347,7 +71347,7 @@
           <t>D | 307呎 (1房)
 $701万
 $22,827/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -71355,7 +71355,7 @@
           <t>E | 315呎 (1房)
 $704万
 $22,343/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -71363,7 +71363,7 @@
           <t>F | 439呎 (2房)
 $844万
 $19,221/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -71371,7 +71371,7 @@
           <t>G | 306呎 (1房)
 $560万
 $18,301/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -71379,7 +71379,7 @@
           <t>H | 306呎 (1房)
 $568万
 $18,562/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -71395,7 +71395,7 @@
           <t>K | 306呎 (1房)
 $639万
 $20,876/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -71403,7 +71403,7 @@
           <t>L | 430呎 (2房)
 $925万
 $21,507/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -71411,7 +71411,7 @@
           <t>M | 307呎 (1房)
 $565万
 $18,401/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -71426,7 +71426,7 @@
           <t>A | 508呎 (2房)
 $1091万
 $21,472/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -71434,7 +71434,7 @@
           <t>B | 482呎 (2房)
 $1061万
 $22,008/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -71442,7 +71442,7 @@
           <t>C | 551呎 (2房)
 $1262万
 $22,900/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -71450,7 +71450,7 @@
           <t>D | 307呎 (1房)
 $692万
 $22,534/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -71458,7 +71458,7 @@
           <t>E | 315呎 (1房)
 $672万
 $21,340/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -71466,7 +71466,7 @@
           <t>F | 439呎 (2房)
 $831万
 $18,925/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -71474,7 +71474,7 @@
           <t>G | 306呎 (1房)
 $559万
 $18,258/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -71482,7 +71482,7 @@
           <t>H | 306呎 (1房)
 $567万
 $18,520/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -71490,7 +71490,7 @@
           <t>J | 308呎 (1房)
 $588万
 $19,091/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -71498,7 +71498,7 @@
           <t>K | 306呎 (1房)
 $629万
 $20,549/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -71506,7 +71506,7 @@
           <t>L | 430呎 (2房)
 $909万
 $21,135/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -71514,7 +71514,7 @@
           <t>M | 307呎 (1房)
 $559万
 $18,202/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -71529,7 +71529,7 @@
           <t>A | 508呎 (2房)
 $1080万
 $21,256/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -71537,7 +71537,7 @@
           <t>B | 482呎 (2房)
 $1051万
 $21,801/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -71545,7 +71545,7 @@
           <t>C | 551呎 (2房)
 $1213万
 $22,011/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -71553,7 +71553,7 @@
           <t>D | 307呎 (1房)
 $687万
 $22,371/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -71561,7 +71561,7 @@
           <t>E | 315呎 (1房)
 $690万
 $21,898/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -71569,7 +71569,7 @@
           <t>F | 439呎 (2房)
 $827万
 $18,834/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -71577,7 +71577,7 @@
           <t>G | 306呎 (1房)
 $557万
 $18,203/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -71585,7 +71585,7 @@
           <t>H | 306呎 (1房)
 $566万
 $18,480/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -71593,7 +71593,7 @@
           <t>J | 308呎 (1房)
 $607万
 $19,701/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -71601,7 +71601,7 @@
           <t>K | 306呎 (1房)
 $602万
 $19,690/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -71609,7 +71609,7 @@
           <t>L | 429呎 (2房)
 $882万
 $20,555/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -71617,7 +71617,7 @@
           <t>M | 307呎 (1房)
 $553万
 $18,000/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -71632,7 +71632,7 @@
           <t>A | 508呎 (2房)
 $1109万
 $21,827/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -71640,7 +71640,7 @@
           <t>B | 482呎 (2房)
 $1041万
 $21,593/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -71648,7 +71648,7 @@
           <t>C | 551呎 (2房)
 $1308万
 $23,739/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -71656,7 +71656,7 @@
           <t>D | 307呎 (1房)
 $655万
 $21,336/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -71664,7 +71664,7 @@
           <t>E | 315呎 (1房)
 $683万
 $21,676/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -71672,7 +71672,7 @@
           <t>F | 439呎 (2房)
 $823万
 $18,743/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -71680,7 +71680,7 @@
           <t>G | 306呎 (1房)
 $556万
 $18,167/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -71688,7 +71688,7 @@
           <t>H | 305呎 (1房)
 $564万
 $18,489/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -71696,7 +71696,7 @@
           <t>J | 308呎 (1房)
 $618万
 $20,058/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -71704,7 +71704,7 @@
           <t>K | 306呎 (1房)
 $611万
 $19,961/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -71712,7 +71712,7 @@
           <t>L | 429呎 (2房)
 $863万
 $20,112/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -71720,7 +71720,7 @@
           <t>M | 307呎 (1房)
 $547万
 $17,805/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -71735,7 +71735,7 @@
           <t>A | 508呎 (2房)
 $1083万
 $21,315/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -71743,7 +71743,7 @@
           <t>B | 482呎 (2房)
 $1009万
 $20,932/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -71751,7 +71751,7 @@
           <t>C | 551呎 (2房)
 $1210万
 $21,956/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -71759,7 +71759,7 @@
           <t>D | 307呎 (1房)
 $649万
 $21,134/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -71767,7 +71767,7 @@
           <t>E | 315呎 (1房)
 $640万
 $20,305/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -71775,7 +71775,7 @@
           <t>F | 439呎 (2房)
 $818万
 $18,633/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -71783,7 +71783,7 @@
           <t>G | 306呎 (1房)
 $555万
 $18,124/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -71791,7 +71791,7 @@
           <t>H | 305呎 (1房)
 $562万
 $18,443/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -71799,7 +71799,7 @@
           <t>J | 308呎 (1房)
 $616万
 $19,984/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -71807,7 +71807,7 @@
           <t>K | 306呎 (1房)
 $598万
 $19,542/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -71815,7 +71815,7 @@
           <t>L | 429呎 (2房)
 $837万
 $19,510/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -71823,7 +71823,7 @@
           <t>M | 307呎 (1房)
 $540万
 $17,590/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -71838,7 +71838,7 @@
           <t>A | 508呎 (2房)
 $1037万
 $20,409/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -71846,7 +71846,7 @@
           <t>B | 482呎 (2房)
 $1008万
 $20,913/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -71854,7 +71854,7 @@
           <t>C | 551呎 (2房)
 $1199万
 $21,757/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -71862,7 +71862,7 @@
           <t>D | 307呎 (1房)
 $642万
 $20,906/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -71870,7 +71870,7 @@
           <t>E | 315呎 (1房)
 $633万
 $20,105/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -71878,7 +71878,7 @@
           <t>F | 439呎 (2房)
 $791万
 $18,009/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -71886,7 +71886,7 @@
           <t>G | 306呎 (1房)
 $553万
 $18,078/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -71894,7 +71894,7 @@
           <t>H | 305呎 (1房)
 $561万
 $18,393/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -71902,7 +71902,7 @@
           <t>J | 308呎 (1房)
 $590万
 $19,169/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -71910,7 +71910,7 @@
           <t>K | 306呎 (1房)
 $607万
 $19,830/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -71918,7 +71918,7 @@
           <t>L | 429呎 (2房)
 $847万
 $19,739/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -71926,7 +71926,7 @@
           <t>M | 307呎 (1房)
 $534万
 $17,404/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -71941,7 +71941,7 @@
           <t>A | 508呎 (2房)
 $1061万
 $20,882/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -71949,7 +71949,7 @@
           <t>B | 482呎 (2房)
 $1029万
 $21,344/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -71957,7 +71957,7 @@
           <t>C | 551呎 (2房)
 $1169万
 $21,212/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -71965,7 +71965,7 @@
           <t>D | 307呎 (1房)
 $660万
 $21,511/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -71973,7 +71973,7 @@
           <t>E | 315呎 (1房)
 $627万
 $19,905/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -71981,7 +71981,7 @@
           <t>F | 439呎 (2房)
 $786万
 $17,911/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -71989,7 +71989,7 @@
           <t>G | 306呎 (1房)
 $550万
 $17,974/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -71997,7 +71997,7 @@
           <t>H | 305呎 (1房)
 $558万
 $18,305/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -72005,7 +72005,7 @@
           <t>J | 308呎 (1房)
 $577万
 $18,727/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -72013,7 +72013,7 @@
           <t>K | 306呎 (1房)
 $572万
 $18,686/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -72021,7 +72021,7 @@
           <t>L | 430呎 (2房)
 $821万
 $19,091/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -72029,7 +72029,7 @@
           <t>M | 307呎 (1房)
 $528万
 $17,199/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -72044,7 +72044,7 @@
           <t>A | 508呎 (2房)
 $1051万
 $20,685/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -72052,7 +72052,7 @@
           <t>B | 482呎 (2房)
 $1021万
 $21,178/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -72060,7 +72060,7 @@
           <t>C | 551呎 (2房)
 $1158万
 $21,013/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -72068,7 +72068,7 @@
           <t>D | 307呎 (1房)
 $629万
 $20,482/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -72076,7 +72076,7 @@
           <t>E | 315呎 (1房)
 $621万
 $19,711/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -72084,7 +72084,7 @@
           <t>F | 439呎 (2房)
 $782万
 $17,809/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -72092,7 +72092,7 @@
           <t>G | 306呎 (1房)
 $549万
 $17,941/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -72100,7 +72100,7 @@
           <t>H | 305呎 (1房)
 $557万
 $18,259/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -72108,7 +72108,7 @@
           <t>J | 308呎 (1房)
 $575万
 $18,662/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -72116,7 +72116,7 @@
           <t>K | 306呎 (1房)
 $570万
 $18,621/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -72124,7 +72124,7 @@
           <t>L | 429呎 (2房)
 $814万
 $18,979/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -72132,7 +72132,7 @@
           <t>M | 307呎 (1房)
 $521万
 $16,971/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -72147,7 +72147,7 @@
           <t>A | 508呎 (2房)
 $1025万
 $20,173/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -72155,7 +72155,7 @@
           <t>B | 482呎 (2房)
 $997万
 $20,680/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -72163,7 +72163,7 @@
           <t>C | 551呎 (2房)
 $1147万
 $20,813/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -72171,7 +72171,7 @@
           <t>D | 307呎 (1房)
 $623万
 $20,287/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -72179,7 +72179,7 @@
           <t>E | 315呎 (1房)
 $615万
 $19,517/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -72187,7 +72187,7 @@
           <t>F | 439呎 (2房)
 $778万
 $17,711/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -72195,7 +72195,7 @@
           <t>G | 306呎 (1房)
 $548万
 $17,899/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -72203,7 +72203,7 @@
           <t>H | 305呎 (1房)
 $556万
 $18,216/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -72211,7 +72211,7 @@
           <t>J | 308呎 (1房)
 $573万
 $18,597/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -72219,7 +72219,7 @@
           <t>K | 305呎 (1房)
 $568万
 $18,616/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -72227,7 +72227,7 @@
           <t>L | 430呎 (2房)
 $812万
 $18,881/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -72235,7 +72235,7 @@
           <t>M | 307呎 (1房)
 $520万
 $16,954/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -72250,7 +72250,7 @@
           <t>A | 508呎 (2房)
 $1053万
 $20,724/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -72258,7 +72258,7 @@
           <t>B | 482呎 (2房)
 $994万
 $20,627/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -72266,7 +72266,7 @@
           <t>C | 551呎 (2房)
 $1102万
 $19,998/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -72274,7 +72274,7 @@
           <t>D | 307呎 (1房)
 $618万
 $20,130/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -72282,7 +72282,7 @@
           <t>E | 315呎 (1房)
 $609万
 $19,340/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -72290,7 +72290,7 @@
           <t>F | 439呎 (2房)
 $773万
 $17,608/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -72298,7 +72298,7 @@
           <t>G | 306呎 (1房)
 $546万
 $17,853/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -72306,7 +72306,7 @@
           <t>H | 305呎 (1房)
 $554万
 $18,174/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -72314,7 +72314,7 @@
           <t>J | 308呎 (1房)
 $571万
 $18,532/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -72322,7 +72322,7 @@
           <t>K | 306呎 (1房)
 $566万
 $18,490/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -72330,7 +72330,7 @@
           <t>L | 429呎 (2房)
 $809万
 $18,865/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -72338,7 +72338,7 @@
           <t>M | 307呎 (1房)
 $520万
 $16,938/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -72353,7 +72353,7 @@
           <t>A | 508呎 (2房)
 $1020万
 $20,085/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -72361,7 +72361,7 @@
           <t>B | 482呎 (2房)
 $992万
 $20,585/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -72369,7 +72369,7 @@
           <t>C | 551呎 (2房)
 $1091万
 $19,800/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -72377,7 +72377,7 @@
           <t>D | 307呎 (1房)
 $653万
 $21,264/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -72385,7 +72385,7 @@
           <t>E | 315呎 (1房)
 $604万
 $19,168/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -72393,7 +72393,7 @@
           <t>F | 439呎 (2房)
 $769万
 $17,510/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -72401,7 +72401,7 @@
           <t>G | 306呎 (1房)
 $545万
 $17,810/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -72409,7 +72409,7 @@
           <t>H | 306呎 (1房)
 $553万
 $18,065/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -72417,7 +72417,7 @@
           <t>J | 308呎 (1房)
 $569万
 $18,468/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -72425,7 +72425,7 @@
           <t>K | 306呎 (1房)
 $564万
 $18,425/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -72433,7 +72433,7 @@
           <t>L | 430呎 (2房)
 $807万
 $18,763/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -72441,7 +72441,7 @@
           <t>M | 307呎 (1房)
 $519万
 $16,915/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -72456,7 +72456,7 @@
           <t>A | 508呎 (2房)
 $1091万
 $21,472/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -72464,7 +72464,7 @@
           <t>B | 482呎 (2房)
 $990万
 $20,539/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -72472,7 +72472,7 @@
           <t>C | 551呎 (2房)
 $1159万
 $21,031/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -72480,7 +72480,7 @@
           <t>D | 307呎 (1房)
 $611万
 $19,896/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -72488,7 +72488,7 @@
           <t>E | 315呎 (1房)
 $603万
 $19,137/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -72496,7 +72496,7 @@
           <t>F | 439呎 (2房)
 $787万
 $17,923/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -72504,7 +72504,7 @@
           <t>G | 306呎 (1房)
 $544万
 $17,765/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -72512,7 +72512,7 @@
           <t>H | 305呎 (1房)
 $552万
 $18,092/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -72520,7 +72520,7 @@
           <t>J | 308呎 (1房)
 $567万
 $18,403/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -72528,7 +72528,7 @@
           <t>K | 306呎 (1房)
 $562万
 $18,359/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -72536,7 +72536,7 @@
           <t>L | 429呎 (2房)
 $804万
 $18,748/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -72544,7 +72544,7 @@
           <t>M | 307呎 (1房)
 $519万
 $16,899/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -72559,7 +72559,7 @@
           <t>A | 508呎 (2房)
 $1044万
 $20,547/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -72567,7 +72567,7 @@
           <t>B | 482呎 (2房)
 $1009万
 $20,929/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -72575,7 +72575,7 @@
           <t>C | 551呎 (2房)
 $1151万
 $20,886/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -72583,7 +72583,7 @@
           <t>D | 307呎 (1房)
 $649万
 $21,134/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -72591,7 +72591,7 @@
           <t>E | 315呎 (1房)
 $602万
 $19,105/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -72599,7 +72599,7 @@
           <t>F | 439呎 (2房)
 $782万
 $17,809/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -72607,7 +72607,7 @@
           <t>G | 306呎 (1房)
 $542万
 $17,722/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -72615,7 +72615,7 @@
           <t>H | 305呎 (1房)
 $550万
 $18,033/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -72623,7 +72623,7 @@
           <t>J | 308呎 (1房)
 $566万
 $18,370/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -72631,7 +72631,7 @@
           <t>K | 306呎 (1房)
 $560万
 $18,301/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -72639,7 +72639,7 @@
           <t>L | 430呎 (2房)
 $790万
 $18,367/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -72647,7 +72647,7 @@
           <t>M | 307呎 (1房)
 $518万
 $16,883/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -72662,7 +72662,7 @@
           <t>A | 508呎 (2房)
 $1068万
 $21,020/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -72670,7 +72670,7 @@
           <t>B | 482呎 (2房)
 $986万
 $20,456/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -72678,7 +72678,7 @@
           <t>C | 551呎 (2房)
 $1213万
 $22,011/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -72686,7 +72686,7 @@
           <t>D | 307呎 (1房)
 $607万
 $19,765/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -72694,7 +72694,7 @@
           <t>E | 315呎 (1房)
 $600万
 $19,048/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -72702,7 +72702,7 @@
           <t>F | 439呎 (2房)
 $778万
 $17,718/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -72710,7 +72710,7 @@
           <t>G | 306呎 (1房)
 $541万
 $17,676/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -72718,7 +72718,7 @@
           <t>H | 305呎 (1房)
 $549万
 $17,990/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -72726,7 +72726,7 @@
           <t>J | 308呎 (1房)
 $565万
 $18,331/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -72734,7 +72734,7 @@
           <t>K | 306呎 (1房)
 $559万
 $18,268/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -72742,7 +72742,7 @@
           <t>L | 430呎 (2房)
 $782万
 $18,179/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -72750,7 +72750,7 @@
           <t>M | 307呎 (1房)
 $518万
 $16,866/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -72765,7 +72765,7 @@
           <t>A | 508呎 (2房)
 $1093万
 $21,512/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -72773,7 +72773,7 @@
           <t>B | 482呎 (2房)
 $1027万
 $21,303/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -72781,7 +72781,7 @@
           <t>C | 551呎 (2房)
 $1181万
 $21,432/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -72789,7 +72789,7 @@
           <t>D | 307呎 (1房)
 $604万
 $19,668/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -72797,7 +72797,7 @@
           <t>E | 315呎 (1房)
 $589万
 $18,698/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -72805,7 +72805,7 @@
           <t>F | 439呎 (2房)
 $774万
 $17,626/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -72813,7 +72813,7 @@
           <t>G | 306呎 (1房)
 $536万
 $17,500/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -72821,7 +72821,7 @@
           <t>H | 305呎 (1房)
 $543万
 $17,810/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -72829,7 +72829,7 @@
           <t>J | 308呎 (1房)
 $572万
 $18,578/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -72837,7 +72837,7 @@
           <t>K | 306呎 (1房)
 $549万
 $17,935/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -72845,7 +72845,7 @@
           <t>L | 430呎 (2房)
 $774万
 $17,998/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -72853,7 +72853,7 @@
           <t>M | 307呎 (1房)
 $510万
 $16,612/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -72868,7 +72868,7 @@
           <t>A | 508呎 (2房)
 $1033万
 $20,331/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -72876,7 +72876,7 @@
           <t>B | 482呎 (2房)
 $1004万
 $20,826/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -72884,7 +72884,7 @@
           <t>C | 551呎 (2房)
 $1114万
 $20,214/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -72892,7 +72892,7 @@
           <t>D | 307呎 (1房)
 $639万
 $20,808/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -72900,7 +72900,7 @@
           <t>E | 315呎 (1房)
 $586万
 $18,610/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -72908,7 +72908,7 @@
           <t>F | 439呎 (2房)
 $747万
 $17,009/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -72916,7 +72916,7 @@
           <t>G | 306呎 (1房)
 $534万
 $17,461/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -72924,7 +72924,7 @@
           <t>H | 306呎 (1房)
 $542万
 $17,709/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -72932,7 +72932,7 @@
           <t>J | 308呎 (1房)
 $569万
 $18,487/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -72940,7 +72940,7 @@
           <t>K | 306呎 (1房)
 $546万
 $17,830/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -72948,7 +72948,7 @@
           <t>L | 430呎 (2房)
 $762万
 $17,719/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -72956,7 +72956,7 @@
           <t>M | 307呎 (1房)
 $501万
 $16,313/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -72971,7 +72971,7 @@
           <t>A | 508呎 (2房)
 $1028万
 $20,236/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -72979,7 +72979,7 @@
           <t>B | 482呎 (2房)
 $999万
 $20,722/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -72987,7 +72987,7 @@
           <t>C | 551呎 (2房)
 $1103万
 $20,015/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -72995,7 +72995,7 @@
           <t>D | 307呎 (1房)
 $647万
 $21,068/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -73003,7 +73003,7 @@
           <t>E | 315呎 (1房)
 $603万
 $19,152/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -73011,7 +73011,7 @@
           <t>F | 439呎 (2房)
 $741万
 $16,884/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -73019,7 +73019,7 @@
           <t>G | 306呎 (1房)
 $533万
 $17,415/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -73027,7 +73027,7 @@
           <t>H | 306呎 (1房)
 $540万
 $17,663/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -73035,7 +73035,7 @@
           <t>J | 308呎 (1房)
 $548万
 $17,792/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -73043,7 +73043,7 @@
           <t>K | 305呎 (1房)
 $564万
 $18,502/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -73051,7 +73051,7 @@
           <t>L | 430呎 (2房)
 $748万
 $17,393/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -73059,7 +73059,7 @@
           <t>M | 307呎 (1房)
 $498万
 $16,221/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -73074,7 +73074,7 @@
           <t>A | 508呎 (2房)
 $919万
 $18,087/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -73082,7 +73082,7 @@
           <t>B | 482呎 (2房)
 $893万
 $18,527/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -73090,7 +73090,7 @@
           <t>C | 551呎 (2房)
 $1099万
 $19,942/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -73098,7 +73098,7 @@
           <t>D | 307呎 (1房)
 $637万
 $20,743/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -73106,7 +73106,7 @@
           <t>E | 315呎 (1房)
 $598万
 $18,978/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -73114,7 +73114,7 @@
           <t>F | 439呎 (2房)
 $732万
 $16,670/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -73122,7 +73122,7 @@
           <t>G | 306呎 (1房)
 $526万
 $17,196/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -73130,7 +73130,7 @@
           <t>H | 305呎 (1房)
 $534万
 $17,498/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -73138,7 +73138,7 @@
           <t>J | 308呎 (1房)
 $540万
 $17,526/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -73146,7 +73146,7 @@
           <t>K | 306呎 (1房)
 $534万
 $17,444/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -73154,7 +73154,7 @@
           <t>L | 430呎 (2房)
 $735万
 $17,088/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -73162,7 +73162,7 @@
           <t>M | 307呎 (1房)
 $495万
 $16,117/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -73177,7 +73177,7 @@
           <t>A | 508呎 (2房)
 $889万
 $17,500/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -73185,7 +73185,7 @@
           <t>B | 482呎 (2房)
 $844万
 $17,502/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -73193,7 +73193,7 @@
           <t>C | 551呎 (2房)
 $1122万
 $20,363/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -73201,7 +73201,7 @@
           <t>D | 307呎 (1房)
 $570万
 $18,560/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -73209,7 +73209,7 @@
           <t>E | 315呎 (1房)
 $552万
 $17,517/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -73217,7 +73217,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -73225,7 +73225,7 @@
           <t>G | 306呎 (1房)
 $518万
 $16,915/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -73233,7 +73233,7 @@
           <t>H | 306呎 (1房)
 $525万
 $17,157/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
@@ -73241,7 +73241,7 @@
           <t>J | 308呎 (1房)
 $531万
 $17,240/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -73249,7 +73249,7 @@
           <t>K | 306呎 (1房)
 $526万
 $17,190/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -73257,7 +73257,7 @@
           <t>L | 430呎 (2房)
 $738万
 $17,160/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -73265,7 +73265,7 @@
           <t>M | 307呎 (1房)
 $491万
 $16,003/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -73280,7 +73280,7 @@
           <t>A | 508呎 (2房)
 $864万
 $17,002/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -73288,7 +73288,7 @@
           <t>B | 482呎 (2房)
 $820万
 $17,002/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -73296,7 +73296,7 @@
           <t>C | 551呎 (2房)
 $1060万
 $19,234/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -73304,7 +73304,7 @@
           <t>D | 307呎 (1房)
 $553万
 $18,007/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -73312,7 +73312,7 @@
           <t>E | 315呎 (1房)
 $536万
 $17,000/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -73320,7 +73320,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -73328,7 +73328,7 @@
           <t>G | 306呎 (1房)
 $505万
 $16,503/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -73336,7 +73336,7 @@
           <t>H | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
@@ -73344,7 +73344,7 @@
           <t>J | 308呎 (1房)
 $524万
 $17,006/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
@@ -73352,7 +73352,7 @@
           <t>K | 305呎 (1房)
 $519万
 $17,010/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -73360,7 +73360,7 @@
           <t>L | 430呎 (2房)
 $710万
 $16,512/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -73368,7 +73368,7 @@
           <t>M | 307呎 (1房)
 $492万
 $16,020/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -73391,7 +73391,7 @@
           <t>B | 445呎 (2房)
 $1066万
 $23,946/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -73399,7 +73399,7 @@
           <t>C | 513呎 (2房)
 $1313万
 $25,591/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -73416,7 +73416,7 @@
           <t>F | 439呎 (2房)
 $725万
 $16,510/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -73424,7 +73424,7 @@
           <t>G | 306呎 (1房)
 $505万
 $16,503/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -73432,7 +73432,7 @@
           <t>H | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
@@ -73440,7 +73440,7 @@
           <t>J | 308呎 (1房)
 $524万
 $17,006/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -73448,7 +73448,7 @@
           <t>K | 306呎 (1房)
 $519万
 $16,954/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -73456,7 +73456,7 @@
           <t>L | 429呎 (2房)
 $710万
 $16,550/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -73464,7 +73464,7 @@
           <t>M | 269呎 (1房)
 $600万
 $22,305/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.75%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -49448,7 +49448,7 @@
         </is>
       </c>
       <c r="E782" s="4" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F782" s="3" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>9088000</v>
       </c>
       <c r="I782" s="5" t="n">
-        <v>21135</v>
+        <v>21184</v>
       </c>
       <c r="J782" s="3" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>9088000</v>
       </c>
       <c r="L782" s="5" t="n">
-        <v>21135</v>
+        <v>21184</v>
       </c>
       <c r="M782" s="3" t="inlineStr">
         <is>
@@ -71503,9 +71503,9 @@
       </c>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t>L | 430呎 (2房)
+          <t>L | 429呎 (2房)
 $909万
-$21,135/呎
+$21,184/呎
 (26年-04月-08日)</t>
         </is>
       </c>
